--- a/M044_ETE_tables.xlsx
+++ b/M044_ETE_tables.xlsx
@@ -1368,11 +1368,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -513.1710224690692,
-  "aic": 1068.3420449381383,
-  "pseudo_r2_mcfadden": 0.13698819433050213,
-  "lr_vs_null_chi2": 162.91404425514202,
+  "n_events": 215,
+  "llf": -709.1297224214745,
+  "aic": 1460.259444842949,
+  "pseudo_r2_mcfadden": 0.13912052005817865,
+  "lr_vs_null_chi2": 229.19467375074282,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "strict-DTC primary \u2014 without RAI covariate"
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>0.01988594511462615</v>
+        <v>0.02852887875313093</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>0.009863719699586606</v>
+        <v>0.01609471932509537</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>0.04009144877854725</v>
+        <v>0.05056919020897697</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>6.536582072095258e-28</v>
+        <v>4.047461154556698e-34</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="19">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>0.5206463545221218</v>
+        <v>0.8679286099430543</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>0.2208502401334555</v>
+        <v>0.4371570253485023</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>1.227404716940181</v>
+        <v>1.723179608876583</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.1357850626236083</v>
+        <v>0.6856224175786536</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="19">
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>1.803142473049095</v>
+        <v>2.123642026911864</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>1.216513912993914</v>
+        <v>1.533370870140629</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>2.672655646092781</v>
+        <v>2.941138080999752</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.003324166076161699</v>
+        <v>5.825549371409613e-06</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="19">
@@ -1444,16 +1444,16 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>1.415612656293561</v>
+        <v>1.16544897652856</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>0.9581423942358207</v>
+        <v>0.8398800321125361</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>2.091504566246436</v>
+        <v>1.617220632659917</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.08094065547071114</v>
+        <v>0.3596684419975973</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="19">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>0.9499944309815281</v>
+        <v>0.8690043784773853</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>0.6030069709102067</v>
+        <v>0.6042699958265132</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>1.496648401151413</v>
+        <v>1.2497205140559</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.8249314914809697</v>
+        <v>0.4487954545213408</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="19">
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>4.064670487927987</v>
+        <v>4.397015389057731</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>1.916630062128161</v>
+        <v>2.326080233319977</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>8.620101761885014</v>
+        <v>8.311727194386481</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0.0002560862557023112</v>
+        <v>5.152961060231732e-06</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="19">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>0.4032548237157969</v>
+        <v>0.4294096849113297</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>0.09349528866863331</v>
+        <v>0.1483860822294949</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>1.739279648907205</v>
+        <v>1.242654801078072</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.223298329848847</v>
+        <v>0.1189385695345342</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="19">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>0.9999999999688559</v>
+        <v>1.000000000077513</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>0.9999997709597415</v>
+        <v>0.9999996684323157</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1.000000228978023</v>
+        <v>1.00000033172282</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>0.9997873278281352</v>
+        <v>0.9996344992021077</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="19">
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>0.4025658212119963</v>
+        <v>0.4981391512004436</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>0.1790133646743263</v>
+        <v>0.2688062120348371</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>0.905291293211088</v>
+        <v>0.9231282717772138</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.02776413268177217</v>
+        <v>0.0268221065984008</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="19">
@@ -1558,16 +1558,16 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>9.263262405819596</v>
+        <v>9.179036364441508</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>4.810900420995349</v>
+        <v>5.174699297923713</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>17.83616846954347</v>
+        <v>16.28204920304177</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2.751261191735409e-11</v>
+        <v>3.424138831731132e-14</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="19">
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>1.865793604816147</v>
+        <v>1.529009881734143</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>0.5997323531271759</v>
+        <v>0.5494736550444274</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>5.804565582665226</v>
+        <v>4.254746696184426</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0.2814594132836437</v>
+        <v>0.4161035542764218</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="19">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>8.234027567608161e-10</v>
+        <v>4.753608602848542e-10</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -1605,7 +1605,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0.9992368963221444</v>
+        <v>0.9992050878233492</v>
       </c>
     </row>
     <row r="15">
@@ -1615,16 +1615,16 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>0.8900578758120722</v>
+        <v>0.8869742759961744</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>0.4972517251809978</v>
+        <v>0.547161887363565</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1.593162943792179</v>
+        <v>1.437825595034902</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.6949870010775374</v>
+        <v>0.6265209498249684</v>
       </c>
     </row>
     <row r="16">
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>2.47107536511665</v>
+        <v>1.871844245674674</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>0.9552563654630051</v>
+        <v>0.7807492309684739</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>6.392224831840564</v>
+        <v>4.487741698725889</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0.06210208227991191</v>
+        <v>0.1599597164104432</v>
       </c>
     </row>
     <row r="17">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>1.149473429389386e-09</v>
+        <v>7.024314372146672e-10</v>
       </c>
       <c r="C17" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -1662,7 +1662,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.9994853005318667</v>
+        <v>0.9994713992834721</v>
       </c>
     </row>
     <row r="18">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>0.8994143043047916</v>
+        <v>0.6314560528350701</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>0.3327371250746828</v>
+        <v>0.2568131584400292</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>2.431186753226003</v>
+        <v>1.552633630940525</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0.8344867055868793</v>
+        <v>0.316574843170173</v>
       </c>
     </row>
     <row r="19">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>1.730704538765681</v>
+        <v>1.750121052252119</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>0.9825439306167997</v>
+        <v>1.088258406762066</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>3.048553970125062</v>
+        <v>2.814518756302825</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.05756478400617664</v>
+        <v>0.02095037504959985</v>
       </c>
     </row>
     <row r="20">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2.295459213080083</v>
+        <v>2.061082258861333</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>1.149102116321469</v>
+        <v>1.141426139715414</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>4.585434944443316</v>
+        <v>3.721712627723844</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.01859114256048079</v>
+        <v>0.0164542393137029</v>
       </c>
     </row>
     <row r="21">
@@ -1729,16 +1729,16 @@
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>2.426078408991358</v>
+        <v>2.351957211059262</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1.06057102469977</v>
+        <v>1.168892655195049</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>5.549705120635581</v>
+        <v>4.732430046564549</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.03579426143389201</v>
+        <v>0.01651095330410831</v>
       </c>
     </row>
     <row r="22">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>1.123627441098395</v>
+        <v>1.202640879497502</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>0.2422511546911807</v>
+        <v>0.3351725935101096</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>5.211692914317777</v>
+        <v>4.315224791775526</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>0.8816355286876478</v>
+        <v>0.7771269536574649</v>
       </c>
     </row>
     <row r="23">
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>0.959087647158345</v>
+        <v>0.9896872203242973</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>0.8558577777367269</v>
+        <v>0.9020897724978332</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1.074768657666727</v>
+        <v>1.085790820309502</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.4721693311377841</v>
+        <v>0.8264666665097463</v>
       </c>
     </row>
     <row r="24">
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="B24" s="18" t="n">
-        <v>1.05396825090431</v>
+        <v>1.056396758774761</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>0.9751068751851637</v>
+        <v>0.9897420624996792</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1.139207508616274</v>
+        <v>1.127540350393245</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>0.1852806869483936</v>
+        <v>0.09896551303985371</v>
       </c>
     </row>
     <row r="25"/>
@@ -1811,11 +1811,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -487.83458546737666,
-  "aic": 1019.6691709347533,
-  "pseudo_r2_mcfadden": 0.1795970777020881,
-  "lr_vs_null_chi2": 213.58691825852702,
+  "n_events": 215,
+  "llf": -667.0629896456544,
+  "aic": 1378.1259792913088,
+  "pseudo_r2_mcfadden": 0.19018929617891134,
+  "lr_vs_null_chi2": 313.3281393023831,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))"
 }</t>
@@ -1829,16 +1829,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>0.01243735367104329</v>
+        <v>0.01732142100306289</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.006019563051503306</v>
+        <v>0.009523766333135741</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>0.02569750744615639</v>
+        <v>0.03150346355322237</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>2.186170219602714e-32</v>
+        <v>2.658613289307774e-40</v>
       </c>
     </row>
     <row r="29">
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>0.5247295914671045</v>
+        <v>0.8698697087040531</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>0.219558917888193</v>
+        <v>0.4314830892472102</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1.254064953542209</v>
+        <v>1.753656931123325</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.1468679320291506</v>
+        <v>0.6967398108202889</v>
       </c>
     </row>
     <row r="30">
@@ -1867,16 +1867,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>1.39918097065779</v>
+        <v>1.627832921137797</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.9319903090618363</v>
+        <v>1.161546625310144</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>2.10056625011643</v>
+        <v>2.281303187835856</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.1051856235318323</v>
+        <v>0.004660208861568816</v>
       </c>
     </row>
     <row r="31">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>1.495807058820033</v>
+        <v>1.231760633120051</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>1.006369220819683</v>
+        <v>0.8809868644167071</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>2.223278207369511</v>
+        <v>1.722198501005862</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>0.0464410225140183</v>
+        <v>0.2228585821121216</v>
       </c>
     </row>
     <row r="32">
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="B32" s="18" t="n">
-        <v>0.8993458401500425</v>
+        <v>0.8166836929697339</v>
       </c>
       <c r="C32" s="18" t="n">
-        <v>0.5677923957007558</v>
+        <v>0.5645066374437279</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>1.424504706860253</v>
+        <v>1.181513573308815</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>0.6511941300107792</v>
+        <v>0.2824933097041959</v>
       </c>
     </row>
     <row r="33">
@@ -1924,16 +1924,16 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>3.135690419140047</v>
+        <v>3.627653391174386</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>1.422526745204697</v>
+        <v>1.839011100616859</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>6.912034826643493</v>
+        <v>7.155948717267022</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>0.004598600726392332</v>
+        <v>0.0002011234480261955</v>
       </c>
     </row>
     <row r="34">
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="B34" s="18" t="n">
-        <v>0.4027848314215922</v>
+        <v>0.4305174384813189</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>0.09155304331996764</v>
+        <v>0.1443067428430905</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1.77203962359094</v>
+        <v>1.284383953132726</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>0.2289571348823807</v>
+        <v>0.1307417511497043</v>
       </c>
     </row>
     <row r="35">
@@ -1962,16 +1962,16 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>0.999999999907793</v>
+        <v>1.000000000005553</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.9999997215088084</v>
+        <v>0.999999981671495</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1.000000278306855</v>
+        <v>1.000000018339611</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.9994820540818611</v>
+        <v>0.9995263629663276</v>
       </c>
     </row>
     <row r="36">
@@ -1981,16 +1981,16 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>0.4045534434906503</v>
+        <v>0.5087226189714406</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>0.1780840267776986</v>
+        <v>0.2712877996228867</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>0.9190239663911192</v>
+        <v>0.9539636629915307</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.03064363216471249</v>
+        <v>0.03512755785228815</v>
       </c>
     </row>
     <row r="37">
@@ -2000,16 +2000,16 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>7.508894512361071</v>
+        <v>7.903581487288889</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>3.825406307449721</v>
+        <v>4.37186775877147</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>14.73921781536334</v>
+        <v>14.28830965915796</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>4.656099624166338e-09</v>
+        <v>7.759845191379394e-12</v>
       </c>
     </row>
     <row r="38">
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="B38" s="18" t="n">
-        <v>1.909544811489748</v>
+        <v>1.593316600907308</v>
       </c>
       <c r="C38" s="18" t="n">
-        <v>0.6094850006112742</v>
+        <v>0.5626763859443698</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>5.982692573944151</v>
+        <v>4.511754632222662</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>0.2669215222801925</v>
+        <v>0.3804112586798645</v>
       </c>
     </row>
     <row r="39">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B39" s="18" t="n">
-        <v>1.077090630903668e-09</v>
+        <v>6.565802357673746e-10</v>
       </c>
       <c r="C39" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2047,7 +2047,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>0.999253127703539</v>
+        <v>0.9992276282018152</v>
       </c>
     </row>
     <row r="40">
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="B40" s="18" t="n">
-        <v>0.8692340403524884</v>
+        <v>0.8737109775300643</v>
       </c>
       <c r="C40" s="18" t="n">
-        <v>0.4784468745879556</v>
+        <v>0.5296743140056287</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>1.579209431680823</v>
+        <v>1.441208025519675</v>
       </c>
       <c r="E40" s="18" t="n">
-        <v>0.6454873097501013</v>
+        <v>0.5970155698167071</v>
       </c>
     </row>
     <row r="41">
@@ -2076,16 +2076,16 @@
         </is>
       </c>
       <c r="B41" s="18" t="n">
-        <v>2.402986648763962</v>
+        <v>1.822104668485675</v>
       </c>
       <c r="C41" s="18" t="n">
-        <v>0.9167869948081019</v>
+        <v>0.7427377887865647</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>6.298458493454655</v>
+        <v>4.470037034659828</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.07454589178825917</v>
+        <v>0.1900588962213718</v>
       </c>
     </row>
     <row r="42">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B42" s="18" t="n">
-        <v>1.738799075705625e-09</v>
+        <v>1.100684466152514e-09</v>
       </c>
       <c r="C42" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2104,7 +2104,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>0.9994975570920213</v>
+        <v>0.9994849606105676</v>
       </c>
     </row>
     <row r="43">
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="B43" s="18" t="n">
-        <v>0.9393529280851761</v>
+        <v>0.6620765338048663</v>
       </c>
       <c r="C43" s="18" t="n">
-        <v>0.3445997066246398</v>
+        <v>0.2661544371829631</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>2.560605556357433</v>
+        <v>1.646958590112604</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.9026773658212039</v>
+        <v>0.3751312494061049</v>
       </c>
     </row>
     <row r="44">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="B44" s="18" t="n">
-        <v>1.744516643641331</v>
+        <v>1.757846831670369</v>
       </c>
       <c r="C44" s="18" t="n">
-        <v>0.9741142391444185</v>
+        <v>1.072012176676356</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>3.12421089605941</v>
+        <v>2.882453717264489</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0.06124136822890355</v>
+        <v>0.02538137453842053</v>
       </c>
     </row>
     <row r="45">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B45" s="18" t="n">
-        <v>2.011792359717567</v>
+        <v>1.767559561507376</v>
       </c>
       <c r="C45" s="18" t="n">
-        <v>1.006452458439709</v>
+        <v>0.9735261414493686</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>4.021360834959328</v>
+        <v>3.209227436691934</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.04791008918686233</v>
+        <v>0.06123505110375684</v>
       </c>
     </row>
     <row r="46">
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>2.361508813625382</v>
+        <v>2.301971520067652</v>
       </c>
       <c r="C46" s="18" t="n">
-        <v>1.0196319676644</v>
+        <v>1.126821728671687</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>5.469349778827132</v>
+        <v>4.702671899528595</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.04492726244467977</v>
+        <v>0.02216326816011768</v>
       </c>
     </row>
     <row r="47">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>0.9991545856558439</v>
+        <v>1.056475533822651</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>0.2019767086438207</v>
+        <v>0.2713048236005229</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>4.942698060287673</v>
+        <v>4.113972389998097</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>0.9991727079719589</v>
+        <v>0.9368684008147224</v>
       </c>
     </row>
     <row r="48">
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>0.9917146052517897</v>
+        <v>1.027372586285429</v>
       </c>
       <c r="C48" s="18" t="n">
-        <v>0.8833885879583029</v>
+        <v>0.9343023576150642</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1.113324160710276</v>
+        <v>1.129713975832307</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>0.8878888867769279</v>
+        <v>0.5772718153126091</v>
       </c>
     </row>
     <row r="49">
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="B49" s="18" t="n">
-        <v>1.0684336730161</v>
+        <v>1.066804243486723</v>
       </c>
       <c r="C49" s="18" t="n">
-        <v>0.9865597660959141</v>
+        <v>0.9974623651372037</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1.1571022383693</v>
+        <v>1.14096665067131</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>0.1036716254647811</v>
+        <v>0.05931299609333798</v>
       </c>
     </row>
     <row r="50">
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="B50" s="18" t="n">
-        <v>4.045155914882584</v>
+        <v>4.422065465782088</v>
       </c>
       <c r="C50" s="18" t="n">
-        <v>2.780534009197924</v>
+        <v>3.24361725881098</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>5.884943799133652</v>
+        <v>6.028659186142928</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>2.739210328395782e-13</v>
+        <v>5.378356570327354e-21</v>
       </c>
     </row>
     <row r="51">
@@ -2274,11 +2274,11 @@
         <is>
           <t>{
   "n_obs": 4028,
-  "n_events": 144,
-  "llf": -523.6470212148317,
-  "aic": 1091.2940424296635,
-  "pseudo_r2_mcfadden": 0.15718550828722821,
-  "lr_vs_null_chi2": 195.32109141947967,
+  "n_events": 227,
+  "llf": -726.1069166756,
+  "aic": 1496.2138333512,
+  "pseudo_r2_mcfadden": 0.1689257788134121,
+  "lr_vs_null_chi2": 295.1798365881273,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "full cohort sensitivity \u2014 includes non-DTC histologies (RAI covariate)"
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B54" s="18" t="n">
-        <v>0.01270332224925263</v>
+        <v>0.0166077781995362</v>
       </c>
       <c r="C54" s="18" t="n">
-        <v>0.006259101047817435</v>
+        <v>0.009311083705383638</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0.0257823599484192</v>
+        <v>0.02962257729092397</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>1.206018657243811e-33</v>
+        <v>8.409625500469957e-44</v>
       </c>
     </row>
     <row r="55">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B55" s="18" t="n">
-        <v>1.025049938589366</v>
+        <v>1.564216493991319</v>
       </c>
       <c r="C55" s="18" t="n">
-        <v>0.4683176194958094</v>
+        <v>0.8457991913982197</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2.243621279364367</v>
+        <v>2.892853605156147</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.9506396590407793</v>
+        <v>0.1538352161719879</v>
       </c>
     </row>
     <row r="56">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B56" s="18" t="n">
-        <v>1.393944822862141</v>
+        <v>1.635941570677835</v>
       </c>
       <c r="C56" s="18" t="n">
-        <v>0.9410113793459441</v>
+        <v>1.183517106772544</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2.064887005441653</v>
+        <v>2.261314861743028</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0.09758118595054122</v>
+        <v>0.002881862436851421</v>
       </c>
     </row>
     <row r="57">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B57" s="18" t="n">
-        <v>1.394437366502062</v>
+        <v>1.206683904333544</v>
       </c>
       <c r="C57" s="18" t="n">
-        <v>0.9501430309170151</v>
+        <v>0.8768257472603137</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>2.04648721910905</v>
+        <v>1.660633312294103</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.0893797811198527</v>
+        <v>0.2488450998171344</v>
       </c>
     </row>
     <row r="58">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B58" s="18" t="n">
-        <v>1.124476587154787</v>
+        <v>1.045286466103029</v>
       </c>
       <c r="C58" s="18" t="n">
-        <v>0.7193888068432835</v>
+        <v>0.7312178578087242</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1.757669264563263</v>
+        <v>1.494252068039583</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0.6067050029762702</v>
+        <v>0.8080566431729559</v>
       </c>
     </row>
     <row r="59">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B59" s="18" t="n">
-        <v>3.624879465068517</v>
+        <v>4.547381907785477</v>
       </c>
       <c r="C59" s="18" t="n">
-        <v>1.715186957471688</v>
+        <v>2.416283054780562</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>7.660827339571414</v>
+        <v>8.558054560016208</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.000743285167779062</v>
+        <v>2.671878931753017e-06</v>
       </c>
     </row>
     <row r="60">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B60" s="18" t="n">
-        <v>0.426840474016942</v>
+        <v>0.4601569840219628</v>
       </c>
       <c r="C60" s="18" t="n">
-        <v>0.09818096425209297</v>
+        <v>0.1573524660586431</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1.855683447874915</v>
+        <v>1.34566972636625</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>0.2562009655028388</v>
+        <v>0.1562797240246736</v>
       </c>
     </row>
     <row r="61">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B61" s="18" t="n">
-        <v>2.795833775900977e-09</v>
+        <v>1.45585367427135e-09</v>
       </c>
       <c r="C61" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2439,7 +2439,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.9988837449101355</v>
+        <v>0.9988540135551914</v>
       </c>
     </row>
     <row r="62">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B62" s="18" t="n">
-        <v>0.5300008549744346</v>
+        <v>0.7266093854941721</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>0.254776321232212</v>
+        <v>0.4169980839720688</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1.10253929766734</v>
+        <v>1.26609982007395</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.08936281649689017</v>
+        <v>0.2596550223031601</v>
       </c>
     </row>
     <row r="63">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B63" s="18" t="n">
-        <v>1.011167251748234</v>
+        <v>1.875916552194508</v>
       </c>
       <c r="C63" s="18" t="n">
-        <v>0.353024229326487</v>
+        <v>0.9269631515839638</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>2.896286220803491</v>
+        <v>3.796335274799296</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.9834978583234898</v>
+        <v>0.08027381558699881</v>
       </c>
     </row>
     <row r="64">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B64" s="18" t="n">
-        <v>3.346147516101704</v>
+        <v>3.6460284551705</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1.87947057450108</v>
+        <v>2.232826960497087</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>5.957370842310664</v>
+        <v>5.953673854311347</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4.060796033651886e-05</v>
+        <v>2.334003728098989e-07</v>
       </c>
     </row>
     <row r="65">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B65" s="18" t="n">
-        <v>0.6993857076936871</v>
+        <v>0.8197586486896278</v>
       </c>
       <c r="C65" s="18" t="n">
-        <v>0.3972178880373146</v>
+        <v>0.5143024029242229</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>1.231415761619099</v>
+        <v>1.306632514801719</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.215432641863233</v>
+        <v>0.4034063394675031</v>
       </c>
     </row>
     <row r="66">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B66" s="18" t="n">
-        <v>1.867041169548178</v>
+        <v>1.550257461308041</v>
       </c>
       <c r="C66" s="18" t="n">
-        <v>0.7291459923331521</v>
+        <v>0.6404190586716134</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>4.780719863293334</v>
+        <v>3.752696244434517</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0.1930889255205552</v>
+        <v>0.3310565404061224</v>
       </c>
     </row>
     <row r="67">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.967499466340078e-09</v>
+        <v>1.448089300654138e-09</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2553,7 +2553,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.9995051108016468</v>
+        <v>0.9994969796046037</v>
       </c>
     </row>
     <row r="68">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B68" s="18" t="n">
-        <v>0.7822666912992599</v>
+        <v>0.7182142279738923</v>
       </c>
       <c r="C68" s="18" t="n">
-        <v>0.2907571989680846</v>
+        <v>0.3094583918948697</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>2.104646689705737</v>
+        <v>1.666885406162695</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.6267592813543801</v>
+        <v>0.4409996109864299</v>
       </c>
     </row>
     <row r="69">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1.951533944343512</v>
+        <v>1.650947448574578</v>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1.127259713107547</v>
+        <v>1.043338414006224</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>3.378533528379185</v>
+        <v>2.612409781299061</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>0.01695159136087427</v>
+        <v>0.03226158280874388</v>
       </c>
     </row>
     <row r="70">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1.84646163863408</v>
+        <v>1.569908295404497</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>0.9392237780518167</v>
+        <v>0.8879650875102204</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3.630040744942848</v>
+        <v>2.775573151068834</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>0.0753771378553825</v>
+        <v>0.120836281416917</v>
       </c>
     </row>
     <row r="71">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>1.767427766572174</v>
+        <v>1.489581518001715</v>
       </c>
       <c r="C71" s="18" t="n">
-        <v>0.8150472828021214</v>
+        <v>0.7798472549195241</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>3.832662197597566</v>
+        <v>2.845240634976995</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.1492690751587251</v>
+        <v>0.2274777896300942</v>
       </c>
     </row>
     <row r="72">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>1.157281133992589</v>
+        <v>1.06283418572021</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>0.2485972594914993</v>
+        <v>0.2898832963987442</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>5.387427141532791</v>
+        <v>3.896797505647641</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0.8523266587803517</v>
+        <v>0.9267527275479167</v>
       </c>
     </row>
     <row r="73">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>0.9613849807648458</v>
+        <v>1.00196171365996</v>
       </c>
       <c r="C73" s="18" t="n">
-        <v>0.8593633576239019</v>
+        <v>0.9145844562706281</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1.075518374201758</v>
+        <v>1.097686789620376</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.4914410663063964</v>
+        <v>0.9664216315274249</v>
       </c>
     </row>
     <row r="74">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>1.068719542189801</v>
+        <v>1.060570403396047</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>0.9888601932405232</v>
+        <v>0.9938430292893878</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1.155028251380494</v>
+        <v>1.131777903965287</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0.09349251578155029</v>
+        <v>0.07611475462990556</v>
       </c>
     </row>
     <row r="75">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B75" s="18" t="n">
-        <v>4.51645326676598</v>
+        <v>4.829623210188446</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3.132621844155952</v>
+        <v>3.57206050109927</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>6.511590330934817</v>
+        <v>6.529917493058363</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>6.628142749372525e-16</v>
+        <v>1.413116117895227e-24</v>
       </c>
     </row>
     <row r="76">
@@ -2722,9 +2722,9 @@
       <c r="A78" s="18" t="inlineStr">
         <is>
           <t>{
-  "lr_chi2": 6.295421355438862,
+  "lr_chi2": 3.6517106295957547,
   "df": 6,
-  "p_value": 0.39092335445937887,
+  "p_value": 0.723687960256885,
   "formula_full": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) * C(ajcc8_n_fac, Treatment(reference='N0')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "formula_reduced": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + C(ajcc8_n_fac, Treatment(reference='N0')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))"
 }</t>
@@ -2758,12 +2758,12 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 164,
-  "llf": -622.5570074555555,
-  "aic": 1287.114014911111,
-  "pseudo_r2_mcfadden": 0.07617446500325986,
-  "lr_vs_null_chi2": 102.6664563393449,
-  "lr_vs_null_pvalue": 4.18554080283684e-13
+  "n_events": 14,
+  "llf": -81.0638843247846,
+  "aic": 204.1277686495692,
+  "pseudo_r2_mcfadden": 0.12137881887901447,
+  "lr_vs_null_chi2": 22.39745352037565,
+  "lr_vs_null_pvalue": 0.31933887897609237
 }</t>
         </is>
       </c>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="B82" s="18" t="n">
-        <v>0.01011442697240845</v>
+        <v>0.001786923068411454</v>
       </c>
       <c r="C82" s="18" t="n">
-        <v>0.005247331152928767</v>
+        <v>0.0002115687708741055</v>
       </c>
       <c r="D82" s="18" t="n">
-        <v>0.0194959361242304</v>
+        <v>0.01509246397390598</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>7.704796697329552e-43</v>
+        <v>6.170743635778745e-09</v>
       </c>
     </row>
     <row r="83">
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="B83" s="18" t="n">
-        <v>1.11234600275388</v>
+        <v>2.355604278444697</v>
       </c>
       <c r="C83" s="18" t="n">
-        <v>0.5157852313966556</v>
+        <v>0.1946082032947651</v>
       </c>
       <c r="D83" s="18" t="n">
-        <v>2.398893094500026</v>
+        <v>28.513040163175</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.7859841270048</v>
+        <v>0.5006607963547791</v>
       </c>
     </row>
     <row r="84">
@@ -2817,16 +2817,16 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>1.45823618682736</v>
+        <v>2.375717141246138</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>1.016637791648724</v>
+        <v>0.7381737066014609</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>2.091652301380849</v>
+        <v>7.645940087998728</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0.04040156790282036</v>
+        <v>0.1467995693644507</v>
       </c>
     </row>
     <row r="85">
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="B85" s="18" t="n">
-        <v>0.9210188500376351</v>
+        <v>0.9193439069638312</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>0.6378273246208893</v>
+        <v>0.2684093137257994</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>1.329945722580707</v>
+        <v>3.148896763451923</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>0.6607377976150157</v>
+        <v>0.8934992612409755</v>
       </c>
     </row>
     <row r="86">
@@ -2855,16 +2855,16 @@
         </is>
       </c>
       <c r="B86" s="18" t="n">
-        <v>0.9443510963277059</v>
+        <v>0.8377688957101103</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>0.6403355095363872</v>
+        <v>0.2386806653638656</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>1.392705823515888</v>
+        <v>2.940567982535855</v>
       </c>
       <c r="E86" s="18" t="n">
-        <v>0.7726916805735701</v>
+        <v>0.7823100301725159</v>
       </c>
     </row>
     <row r="87">
@@ -2874,16 +2874,16 @@
         </is>
       </c>
       <c r="B87" s="18" t="n">
-        <v>2.260483412399704</v>
+        <v>2.691336535594656</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>1.047981474908726</v>
+        <v>0.2557976385597303</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>4.875835479991901</v>
+        <v>28.31649419678006</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0.03757540366265054</v>
+        <v>0.4096422478169726</v>
       </c>
     </row>
     <row r="88">
@@ -2893,16 +2893,16 @@
         </is>
       </c>
       <c r="B88" s="18" t="n">
-        <v>0.4804491592959669</v>
+        <v>1.767155055363416</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>0.1661081913916161</v>
+        <v>0.1811306545993918</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>1.389644861787665</v>
+        <v>17.24079779098289</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>0.1761389910725132</v>
+        <v>0.6242047862455105</v>
       </c>
     </row>
     <row r="89">
@@ -2912,16 +2912,16 @@
         </is>
       </c>
       <c r="B89" s="18" t="n">
-        <v>0.9999999999801856</v>
+        <v>0.9999999999960187</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>0.9999999747862053</v>
+        <v>0.9999997899039276</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>1.000000025174167</v>
+        <v>1.000000210088154</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.9987700920646339</v>
+        <v>0.9999703654559708</v>
       </c>
     </row>
     <row r="90">
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="B90" s="18" t="n">
-        <v>1.050618861452904</v>
+        <v>2.878946803441325</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>0.6029305182472614</v>
+        <v>0.5889034971326118</v>
       </c>
       <c r="D90" s="18" t="n">
-        <v>1.830725031549869</v>
+        <v>14.07418148712169</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0.8616476402837221</v>
+        <v>0.1915526072694045</v>
       </c>
     </row>
     <row r="91">
@@ -2950,16 +2950,16 @@
         </is>
       </c>
       <c r="B91" s="18" t="n">
-        <v>4.836014686208723</v>
+        <v>2.380401768922977</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>2.439273004658983</v>
+        <v>0.1785689893148111</v>
       </c>
       <c r="D91" s="18" t="n">
-        <v>9.587708305121028</v>
+        <v>31.7317839073509</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>6.372993394383339e-06</v>
+        <v>0.5116393020940575</v>
       </c>
     </row>
     <row r="92">
@@ -2969,16 +2969,16 @@
         </is>
       </c>
       <c r="B92" s="18" t="n">
-        <v>2.269681815883825</v>
+        <v>9.117152013220499</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>0.7883398076778341</v>
+        <v>0.6821678137134559</v>
       </c>
       <c r="D92" s="18" t="n">
-        <v>6.534562247374054</v>
+        <v>121.8504584373226</v>
       </c>
       <c r="E92" s="18" t="n">
-        <v>0.1287211332116574</v>
+        <v>0.09475729860505173</v>
       </c>
     </row>
     <row r="93">
@@ -2988,16 +2988,16 @@
         </is>
       </c>
       <c r="B93" s="18" t="n">
-        <v>3.418923711874631</v>
+        <v>2.477532991957287e-09</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>0.6613762473322524</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D93" s="18" t="n">
-        <v>17.67381183519649</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0.142457541720635</v>
+        <v>0.9997357907928893</v>
       </c>
     </row>
     <row r="94">
@@ -3007,16 +3007,16 @@
         </is>
       </c>
       <c r="B94" s="18" t="n">
-        <v>1.858868116491178</v>
+        <v>2.100268075359052</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>1.107979986381062</v>
+        <v>0.4591337909409427</v>
       </c>
       <c r="D94" s="18" t="n">
-        <v>3.118639972725163</v>
+        <v>9.607495844146682</v>
       </c>
       <c r="E94" s="18" t="n">
-        <v>0.01885585952083281</v>
+        <v>0.3387921663504317</v>
       </c>
     </row>
     <row r="95">
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B95" s="18" t="n">
-        <v>4.645579194783794</v>
+        <v>2.011022141784835e-09</v>
       </c>
       <c r="C95" s="18" t="n">
-        <v>1.811177361925228</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D95" s="18" t="n">
-        <v>11.91567789477429</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E95" s="18" t="n">
-        <v>0.001393967102755832</v>
+        <v>0.9994414708553463</v>
       </c>
     </row>
     <row r="96">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B96" s="18" t="n">
-        <v>1.214094896344485e-08</v>
+        <v>1.976731211879618e-09</v>
       </c>
       <c r="C96" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3054,7 +3054,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E96" s="18" t="n">
-        <v>0.9987700734231472</v>
+        <v>0.9998126242745856</v>
       </c>
     </row>
     <row r="97">
@@ -3064,16 +3064,16 @@
         </is>
       </c>
       <c r="B97" s="18" t="n">
-        <v>1.118793904964754</v>
+        <v>2.968183959850206e-09</v>
       </c>
       <c r="C97" s="18" t="n">
-        <v>0.4291663195525052</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D97" s="18" t="n">
-        <v>2.916584421376403</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E97" s="18" t="n">
-        <v>0.8183909384795416</v>
+        <v>0.9990297347742679</v>
       </c>
     </row>
     <row r="98">
@@ -3083,16 +3083,16 @@
         </is>
       </c>
       <c r="B98" s="18" t="n">
-        <v>0.7535902522229895</v>
+        <v>1.594915489366299</v>
       </c>
       <c r="C98" s="18" t="n">
-        <v>0.4398546600548602</v>
+        <v>0.2687277948110208</v>
       </c>
       <c r="D98" s="18" t="n">
-        <v>1.291104357459072</v>
+        <v>9.465918551556614</v>
       </c>
       <c r="E98" s="18" t="n">
-        <v>0.3030710714444501</v>
+        <v>0.6074164792059515</v>
       </c>
     </row>
     <row r="99">
@@ -3102,16 +3102,16 @@
         </is>
       </c>
       <c r="B99" s="18" t="n">
-        <v>1.205770931891842</v>
+        <v>7.992098005631019</v>
       </c>
       <c r="C99" s="18" t="n">
-        <v>0.6349173758540275</v>
+        <v>1.753182671062876</v>
       </c>
       <c r="D99" s="18" t="n">
-        <v>2.28987832982158</v>
+        <v>36.43295794892131</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.5674511906641355</v>
+        <v>0.007245923079154247</v>
       </c>
     </row>
     <row r="100">
@@ -3121,16 +3121,16 @@
         </is>
       </c>
       <c r="B100" s="18" t="n">
-        <v>1.166818766849705</v>
+        <v>1.650396770245106</v>
       </c>
       <c r="C100" s="18" t="n">
-        <v>0.5509732658789832</v>
+        <v>0.121632055434126</v>
       </c>
       <c r="D100" s="18" t="n">
-        <v>2.471020136522744</v>
+        <v>22.39384584527266</v>
       </c>
       <c r="E100" s="18" t="n">
-        <v>0.6869538871434016</v>
+        <v>0.7065032591764135</v>
       </c>
     </row>
     <row r="101">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="B101" s="18" t="n">
-        <v>0.3811431586791804</v>
+        <v>5.38394050011315e-09</v>
       </c>
       <c r="C101" s="18" t="n">
-        <v>0.05004921576376178</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D101" s="18" t="n">
-        <v>2.902545128651665</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.351737413394908</v>
+        <v>0.9994607925343963</v>
       </c>
     </row>
     <row r="102">
@@ -3159,16 +3159,16 @@
         </is>
       </c>
       <c r="B102" s="18" t="n">
-        <v>1.189984662056924</v>
+        <v>0.9461255572965408</v>
       </c>
       <c r="C102" s="18" t="n">
-        <v>1.073099930910414</v>
+        <v>0.6711845132547247</v>
       </c>
       <c r="D102" s="18" t="n">
-        <v>1.319600770758926</v>
+        <v>1.333692229918847</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0.0009757554982066074</v>
+        <v>0.751891675586252</v>
       </c>
     </row>
     <row r="103">
@@ -3178,16 +3178,16 @@
         </is>
       </c>
       <c r="B103" s="18" t="n">
-        <v>1.081225534087192</v>
+        <v>0.8932782057804017</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>1.007725173214805</v>
+        <v>0.6529378085699872</v>
       </c>
       <c r="D103" s="18" t="n">
-        <v>1.160086784209906</v>
+        <v>1.222085690932574</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0.02968933634341852</v>
+        <v>0.4803384917184649</v>
       </c>
     </row>
     <row r="104">
@@ -3213,11 +3213,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 303,
-  "llf": -925.5042689800755,
-  "aic": 1893.008537960151,
-  "pseudo_r2_mcfadden": 0.12124632139453095,
-  "lr_vs_null_chi2": 255.3934982709734,
+  "n_events": 229,
+  "llf": -745.3098565317043,
+  "aic": 1532.6197130634087,
+  "pseudo_r2_mcfadden": 0.13584706772909427,
+  "lr_vs_null_chi2": 234.32925996872837,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="B107" s="18" t="n">
-        <v>0.02676698402471146</v>
+        <v>0.0308660630888207</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>0.01629113621897721</v>
+        <v>0.01772014227810561</v>
       </c>
       <c r="D107" s="18" t="n">
-        <v>0.04397921815573275</v>
+        <v>0.05376445830122932</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>2.486438197937405e-46</v>
+        <v>1.107081921187218e-34</v>
       </c>
     </row>
     <row r="108">
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B108" s="18" t="n">
-        <v>0.6094490406365383</v>
+        <v>0.9121049568028911</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>0.3211991318489873</v>
+        <v>0.4667918473901025</v>
       </c>
       <c r="D108" s="18" t="n">
-        <v>1.156379629654245</v>
+        <v>1.782240750081368</v>
       </c>
       <c r="E108" s="18" t="n">
-        <v>0.1296832465925776</v>
+        <v>0.787789958504173</v>
       </c>
     </row>
     <row r="109">
@@ -3272,16 +3272,16 @@
         </is>
       </c>
       <c r="B109" s="18" t="n">
-        <v>1.652402622603325</v>
+        <v>2.159054006210905</v>
       </c>
       <c r="C109" s="18" t="n">
-        <v>1.25479796261591</v>
+        <v>1.57518402362271</v>
       </c>
       <c r="D109" s="18" t="n">
-        <v>2.175995266595857</v>
+        <v>2.959345785525748</v>
       </c>
       <c r="E109" s="18" t="n">
-        <v>0.0003487040661778825</v>
+        <v>1.714615781370003e-06</v>
       </c>
     </row>
     <row r="110">
@@ -3291,16 +3291,16 @@
         </is>
       </c>
       <c r="B110" s="18" t="n">
-        <v>1.138567777855221</v>
+        <v>1.146338175420031</v>
       </c>
       <c r="C110" s="18" t="n">
-        <v>0.8618856797131073</v>
+        <v>0.8337188535225089</v>
       </c>
       <c r="D110" s="18" t="n">
-        <v>1.504070221008524</v>
+        <v>1.576180275728704</v>
       </c>
       <c r="E110" s="18" t="n">
-        <v>0.3609326077121583</v>
+        <v>0.4005653433857129</v>
       </c>
     </row>
     <row r="111">
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="B111" s="18" t="n">
-        <v>0.9434472120081623</v>
+        <v>0.8641389839639116</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>0.696564584087066</v>
+        <v>0.6085042534212625</v>
       </c>
       <c r="D111" s="18" t="n">
-        <v>1.277832181222005</v>
+        <v>1.227166744369858</v>
       </c>
       <c r="E111" s="18" t="n">
-        <v>0.7068478015651114</v>
+        <v>0.4144972794830678</v>
       </c>
     </row>
     <row r="112">
@@ -3329,16 +3329,16 @@
         </is>
       </c>
       <c r="B112" s="18" t="n">
-        <v>3.808166948586015</v>
+        <v>4.390849169737566</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>2.109123989508771</v>
+        <v>2.354079948000706</v>
       </c>
       <c r="D112" s="18" t="n">
-        <v>6.875904679117779</v>
+        <v>8.189847778007278</v>
       </c>
       <c r="E112" s="18" t="n">
-        <v>9.190604927805676e-06</v>
+        <v>3.290345085397565e-06</v>
       </c>
     </row>
     <row r="113">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B113" s="18" t="n">
-        <v>0.4385666122407763</v>
+        <v>0.5073296814225355</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>0.182779445963439</v>
+        <v>0.1939165575475286</v>
       </c>
       <c r="D113" s="18" t="n">
-        <v>1.052310189247564</v>
+        <v>1.327289473923377</v>
       </c>
       <c r="E113" s="18" t="n">
-        <v>0.0649236714255535</v>
+        <v>0.1666829223107431</v>
       </c>
     </row>
     <row r="114">
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="B114" s="18" t="n">
-        <v>1.00000000005951</v>
+        <v>0.9999999998520169</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>0.9999999283116556</v>
+        <v>0.9999997567457336</v>
       </c>
       <c r="D114" s="18" t="n">
-        <v>1.00000007180737</v>
+        <v>1.000000242958359</v>
       </c>
       <c r="E114" s="18" t="n">
-        <v>0.9987029107207218</v>
+        <v>0.9990480729050271</v>
       </c>
     </row>
     <row r="115">
@@ -3386,16 +3386,16 @@
         </is>
       </c>
       <c r="B115" s="18" t="n">
-        <v>0.7037503491326073</v>
+        <v>0.6025486322183058</v>
       </c>
       <c r="C115" s="18" t="n">
-        <v>0.4401584663917285</v>
+        <v>0.3429542330921916</v>
       </c>
       <c r="D115" s="18" t="n">
-        <v>1.125196018525508</v>
+        <v>1.058639372707651</v>
       </c>
       <c r="E115" s="18" t="n">
-        <v>0.1422888195966236</v>
+        <v>0.07810548377592348</v>
       </c>
     </row>
     <row r="116">
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="B116" s="18" t="n">
-        <v>9.86418929754262</v>
+        <v>9.012919109188681</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>5.764262811619173</v>
+        <v>5.1250026869876</v>
       </c>
       <c r="D116" s="18" t="n">
-        <v>16.88025575475492</v>
+        <v>15.85027673742077</v>
       </c>
       <c r="E116" s="18" t="n">
-        <v>6.796049567735243e-17</v>
+        <v>2.285642333521437e-14</v>
       </c>
     </row>
     <row r="117">
@@ -3424,16 +3424,16 @@
         </is>
       </c>
       <c r="B117" s="18" t="n">
-        <v>2.319868377516867</v>
+        <v>1.85513508414942</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>0.9925544067281732</v>
+        <v>0.70587792285936</v>
       </c>
       <c r="D117" s="18" t="n">
-        <v>5.422160490670843</v>
+        <v>4.875526020846766</v>
       </c>
       <c r="E117" s="18" t="n">
-        <v>0.05205111302128794</v>
+        <v>0.2100409556942971</v>
       </c>
     </row>
     <row r="118">
@@ -3443,16 +3443,16 @@
         </is>
       </c>
       <c r="B118" s="18" t="n">
-        <v>1.380089245863187</v>
+        <v>4.685794492779359e-10</v>
       </c>
       <c r="C118" s="18" t="n">
-        <v>0.2649504785633158</v>
+        <v>1.388794386496402e-11</v>
       </c>
       <c r="D118" s="18" t="n">
-        <v>7.188688002660331</v>
+        <v>72004899337.38588</v>
       </c>
       <c r="E118" s="18" t="n">
-        <v>0.702029457253707</v>
+        <v>0.9992082894040065</v>
       </c>
     </row>
     <row r="119">
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="B119" s="18" t="n">
-        <v>1.29356720084236</v>
+        <v>0.93563299537324</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>0.8606279796575615</v>
+        <v>0.5887964873347733</v>
       </c>
       <c r="D119" s="18" t="n">
-        <v>1.944296656217173</v>
+        <v>1.48677704582393</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.21569684981851</v>
+        <v>0.7782845197035019</v>
       </c>
     </row>
     <row r="120">
@@ -3481,16 +3481,16 @@
         </is>
       </c>
       <c r="B120" s="18" t="n">
-        <v>3.963714889943167</v>
+        <v>1.763496642251678</v>
       </c>
       <c r="C120" s="18" t="n">
-        <v>1.90467547062833</v>
+        <v>0.7377081995501475</v>
       </c>
       <c r="D120" s="18" t="n">
-        <v>8.248668064998117</v>
+        <v>4.215651132967428</v>
       </c>
       <c r="E120" s="18" t="n">
-        <v>0.0002304235725128403</v>
+        <v>0.2020189038444107</v>
       </c>
     </row>
     <row r="121">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="B121" s="18" t="n">
-        <v>4.72365675344494e-09</v>
+        <v>6.552257941215875e-10</v>
       </c>
       <c r="C121" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3509,7 +3509,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.9987029188842879</v>
+        <v>0.9994714423679432</v>
       </c>
     </row>
     <row r="122">
@@ -3519,16 +3519,16 @@
         </is>
       </c>
       <c r="B122" s="18" t="n">
-        <v>1.000552665897021</v>
+        <v>0.592343147980395</v>
       </c>
       <c r="C122" s="18" t="n">
-        <v>0.4939565760187744</v>
+        <v>0.242317996181078</v>
       </c>
       <c r="D122" s="18" t="n">
-        <v>2.026707783308435</v>
+        <v>1.447975018319018</v>
       </c>
       <c r="E122" s="18" t="n">
-        <v>0.9987759138531119</v>
+        <v>0.2508531697276715</v>
       </c>
     </row>
     <row r="123">
@@ -3538,16 +3538,16 @@
         </is>
       </c>
       <c r="B123" s="18" t="n">
-        <v>1.158570994669663</v>
+        <v>1.756967391204634</v>
       </c>
       <c r="C123" s="18" t="n">
-        <v>0.7672208324234071</v>
+        <v>1.108466765804642</v>
       </c>
       <c r="D123" s="18" t="n">
-        <v>1.749544189839051</v>
+        <v>2.784868711436373</v>
       </c>
       <c r="E123" s="18" t="n">
-        <v>0.4839813498194103</v>
+        <v>0.01647819317941627</v>
       </c>
     </row>
     <row r="124">
@@ -3557,16 +3557,16 @@
         </is>
       </c>
       <c r="B124" s="18" t="n">
-        <v>1.691859126937734</v>
+        <v>2.542326596698262</v>
       </c>
       <c r="C124" s="18" t="n">
-        <v>1.028703517240612</v>
+        <v>1.479281251950912</v>
       </c>
       <c r="D124" s="18" t="n">
-        <v>2.782519217082646</v>
+        <v>4.369300642291817</v>
       </c>
       <c r="E124" s="18" t="n">
-        <v>0.03831712044985566</v>
+        <v>0.0007324255614526801</v>
       </c>
     </row>
     <row r="125">
@@ -3576,16 +3576,16 @@
         </is>
       </c>
       <c r="B125" s="18" t="n">
-        <v>1.717888752018895</v>
+        <v>2.243221806591199</v>
       </c>
       <c r="C125" s="18" t="n">
-        <v>0.9508623916532143</v>
+        <v>1.136977598871244</v>
       </c>
       <c r="D125" s="18" t="n">
-        <v>3.103647583728746</v>
+        <v>4.425807578409583</v>
       </c>
       <c r="E125" s="18" t="n">
-        <v>0.07297249397204734</v>
+        <v>0.01979422895363047</v>
       </c>
     </row>
     <row r="126">
@@ -3595,16 +3595,16 @@
         </is>
       </c>
       <c r="B126" s="18" t="n">
-        <v>0.6566244968823464</v>
+        <v>1.159906813291713</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>0.187160134423503</v>
+        <v>0.325322066395783</v>
       </c>
       <c r="D126" s="18" t="n">
-        <v>2.303672901465128</v>
+        <v>4.135544294384749</v>
       </c>
       <c r="E126" s="18" t="n">
-        <v>0.5112767159965047</v>
+        <v>0.8191028065396831</v>
       </c>
     </row>
     <row r="127">
@@ -3614,16 +3614,16 @@
         </is>
       </c>
       <c r="B127" s="18" t="n">
-        <v>1.086433313008164</v>
+        <v>0.9838354183720965</v>
       </c>
       <c r="C127" s="18" t="n">
-        <v>1.003522359126626</v>
+        <v>0.8991659091296907</v>
       </c>
       <c r="D127" s="18" t="n">
-        <v>1.176194364658852</v>
+        <v>1.076477789710985</v>
       </c>
       <c r="E127" s="18" t="n">
-        <v>0.04067997878349377</v>
+        <v>0.7226393059660168</v>
       </c>
     </row>
     <row r="128">
@@ -3633,16 +3633,16 @@
         </is>
       </c>
       <c r="B128" s="18" t="n">
-        <v>1.080494405034959</v>
+        <v>1.047990518915657</v>
       </c>
       <c r="C128" s="18" t="n">
-        <v>1.02047785588654</v>
+        <v>0.9829799179292665</v>
       </c>
       <c r="D128" s="18" t="n">
-        <v>1.144040659557096</v>
+        <v>1.117300676956596</v>
       </c>
       <c r="E128" s="18" t="n">
-        <v>0.007926432924495646</v>
+        <v>0.1514055363445994</v>
       </c>
     </row>
     <row r="129">
@@ -3668,11 +3668,11 @@
         <is>
           <t>{
   "n_obs": 2521,
-  "n_events": 138,
-  "llf": -465.43619265721696,
-  "aic": 972.8723853144339,
-  "pseudo_r2_mcfadden": 0.13049510541536558,
-  "lr_vs_null_chi2": 139.70512507337696,
+  "n_events": 209,
+  "llf": -622.9482694250016,
+  "aic": 1287.8965388500033,
+  "pseudo_r2_mcfadden": 0.13582463026934888,
+  "lr_vs_null_chi2": 195.8207126360328,
   "lr_vs_null_pvalue": 0.0,
   "n": 2525
 }</t>
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="B132" s="18" t="n">
-        <v>0.02908836568246979</v>
+        <v>0.04115760288353638</v>
       </c>
       <c r="C132" s="18" t="n">
-        <v>0.01422363206737039</v>
+        <v>0.02272231645732748</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.05948783082052233</v>
+        <v>0.07454998165790526</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>3.295407773830457e-22</v>
+        <v>6.570579718217517e-26</v>
       </c>
     </row>
     <row r="133">
@@ -3709,16 +3709,16 @@
         </is>
       </c>
       <c r="B133" s="18" t="n">
-        <v>0.6967038672593815</v>
+        <v>1.134244179197613</v>
       </c>
       <c r="C133" s="18" t="n">
-        <v>0.2953856544843365</v>
+        <v>0.56281774724079</v>
       </c>
       <c r="D133" s="18" t="n">
-        <v>1.643262871047507</v>
+        <v>2.285837403583614</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.4091030468030411</v>
+        <v>0.724602606779164</v>
       </c>
     </row>
     <row r="134">
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="B134" s="18" t="n">
-        <v>1.560754832391781</v>
+        <v>1.8062070882653</v>
       </c>
       <c r="C134" s="18" t="n">
-        <v>1.047720718607233</v>
+        <v>1.292190777937013</v>
       </c>
       <c r="D134" s="18" t="n">
-        <v>2.325004749426436</v>
+        <v>2.524692252415098</v>
       </c>
       <c r="E134" s="18" t="n">
-        <v>0.02858136422021442</v>
+        <v>0.0005397672102306769</v>
       </c>
     </row>
     <row r="135">
@@ -3747,16 +3747,16 @@
         </is>
       </c>
       <c r="B135" s="18" t="n">
-        <v>1.458627255653701</v>
+        <v>1.176441414426438</v>
       </c>
       <c r="C135" s="18" t="n">
-        <v>0.9838836891875398</v>
+        <v>0.8396790541040537</v>
       </c>
       <c r="D135" s="18" t="n">
-        <v>2.162444092037695</v>
+        <v>1.648265959253248</v>
       </c>
       <c r="E135" s="18" t="n">
-        <v>0.06023258661637172</v>
+        <v>0.344960820630554</v>
       </c>
     </row>
     <row r="136">
@@ -3766,16 +3766,16 @@
         </is>
       </c>
       <c r="B136" s="18" t="n">
-        <v>0.9574647974563424</v>
+        <v>0.879323379073961</v>
       </c>
       <c r="C136" s="18" t="n">
-        <v>0.6021143874915205</v>
+        <v>0.6034483875252566</v>
       </c>
       <c r="D136" s="18" t="n">
-        <v>1.522532690486532</v>
+        <v>1.281318536879323</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>0.8542746153066803</v>
+        <v>0.5031853183207384</v>
       </c>
     </row>
     <row r="137">
@@ -3785,16 +3785,16 @@
         </is>
       </c>
       <c r="B137" s="18" t="n">
-        <v>4.109223330412471</v>
+        <v>4.392080109448165</v>
       </c>
       <c r="C137" s="18" t="n">
-        <v>1.887696337379916</v>
+        <v>2.226167980296552</v>
       </c>
       <c r="D137" s="18" t="n">
-        <v>8.945144430720877</v>
+        <v>8.665279466125689</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.0003696831296258795</v>
+        <v>1.970202830424997e-05</v>
       </c>
     </row>
     <row r="138">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B138" s="18" t="n">
-        <v>0.4068359110860253</v>
+        <v>0.4457987109503074</v>
       </c>
       <c r="C138" s="18" t="n">
-        <v>0.09281764416320727</v>
+        <v>0.150229915542725</v>
       </c>
       <c r="D138" s="18" t="n">
-        <v>1.783232703667416</v>
+        <v>1.322882263276222</v>
       </c>
       <c r="E138" s="18" t="n">
-        <v>0.2329486047848889</v>
+        <v>0.1454590249457592</v>
       </c>
     </row>
     <row r="139">
@@ -3823,16 +3823,16 @@
         </is>
       </c>
       <c r="B139" s="18" t="n">
-        <v>0.9999999999981873</v>
+        <v>1.000000000143479</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>0.9999999870704732</v>
+        <v>0.9999996859713646</v>
       </c>
       <c r="D139" s="18" t="n">
-        <v>1.000000012925902</v>
+        <v>1.000000314315691</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.9997807311029037</v>
+        <v>0.9992858208842804</v>
       </c>
     </row>
     <row r="140">
@@ -3842,16 +3842,16 @@
         </is>
       </c>
       <c r="B140" s="18" t="n">
-        <v>0.3686023654622701</v>
+        <v>0.416627892667198</v>
       </c>
       <c r="C140" s="18" t="n">
-        <v>0.1625998523490909</v>
+        <v>0.2192454551902727</v>
       </c>
       <c r="D140" s="18" t="n">
-        <v>0.8355954932399453</v>
+        <v>0.7917099161652834</v>
       </c>
       <c r="E140" s="18" t="n">
-        <v>0.01684402024437803</v>
+        <v>0.007517646827260235</v>
       </c>
     </row>
     <row r="141">
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="B141" s="18" t="n">
-        <v>7.264690280466521</v>
+        <v>7.356104628142049</v>
       </c>
       <c r="C141" s="18" t="n">
-        <v>3.809578983992667</v>
+        <v>4.150706961796681</v>
       </c>
       <c r="D141" s="18" t="n">
-        <v>13.85342713535043</v>
+        <v>13.03688161998065</v>
       </c>
       <c r="E141" s="18" t="n">
-        <v>1.732410226682985e-09</v>
+        <v>8.217862471402229e-12</v>
       </c>
     </row>
     <row r="142">
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="B142" s="18" t="n">
-        <v>1.526244356792837</v>
+        <v>0.9696103066174636</v>
       </c>
       <c r="C142" s="18" t="n">
-        <v>0.483442821544626</v>
+        <v>0.3221654891002712</v>
       </c>
       <c r="D142" s="18" t="n">
-        <v>4.81840195537365</v>
+        <v>2.918202534121215</v>
       </c>
       <c r="E142" s="18" t="n">
-        <v>0.4710124921846479</v>
+        <v>0.9562209452752073</v>
       </c>
     </row>
     <row r="143">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="B143" s="18" t="n">
-        <v>1.342942858013644e-09</v>
+        <v>7.877893781387173e-10</v>
       </c>
       <c r="C143" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3908,7 +3908,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E143" s="18" t="n">
-        <v>0.9990038688340173</v>
+        <v>0.9989558097683963</v>
       </c>
     </row>
     <row r="144">
@@ -3918,16 +3918,16 @@
         </is>
       </c>
       <c r="B144" s="18" t="n">
-        <v>0.7976062383549233</v>
+        <v>0.8225119517642643</v>
       </c>
       <c r="C144" s="18" t="n">
-        <v>0.4449690053260292</v>
+        <v>0.5031661120398612</v>
       </c>
       <c r="D144" s="18" t="n">
-        <v>1.429707920884432</v>
+        <v>1.344537906283849</v>
       </c>
       <c r="E144" s="18" t="n">
-        <v>0.4475795226531371</v>
+        <v>0.4358263332361597</v>
       </c>
     </row>
     <row r="145">
@@ -3937,16 +3937,16 @@
         </is>
       </c>
       <c r="B145" s="18" t="n">
-        <v>2.298546506418875</v>
+        <v>1.828197989053828</v>
       </c>
       <c r="C145" s="18" t="n">
-        <v>0.8733351751023012</v>
+        <v>0.7436250777518226</v>
       </c>
       <c r="D145" s="18" t="n">
-        <v>6.049585763623385</v>
+        <v>4.494614271596583</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>0.09186168903436497</v>
+        <v>0.1886595553526482</v>
       </c>
     </row>
     <row r="146">
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="B146" s="18" t="n">
-        <v>2.696103328323763e-09</v>
+        <v>1.602625843888724e-09</v>
       </c>
       <c r="C146" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -3965,7 +3965,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E146" s="18" t="n">
-        <v>0.9993452656465017</v>
+        <v>0.9993265128881849</v>
       </c>
     </row>
     <row r="147">
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="B147" s="18" t="n">
-        <v>0.9198714516263986</v>
+        <v>0.6698145030317432</v>
       </c>
       <c r="C147" s="18" t="n">
-        <v>0.3407862767436722</v>
+        <v>0.2716049355182685</v>
       </c>
       <c r="D147" s="18" t="n">
-        <v>2.48297406692146</v>
+        <v>1.651853150663694</v>
       </c>
       <c r="E147" s="18" t="n">
-        <v>0.8690570239934944</v>
+        <v>0.3842054402693326</v>
       </c>
     </row>
     <row r="148">
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="B148" s="18" t="n">
-        <v>1.670515128410177</v>
+        <v>1.698002802230466</v>
       </c>
       <c r="C148" s="18" t="n">
-        <v>0.9483483889786701</v>
+        <v>1.046840457454953</v>
       </c>
       <c r="D148" s="18" t="n">
-        <v>2.94261141441137</v>
+        <v>2.754205281091349</v>
       </c>
       <c r="E148" s="18" t="n">
-        <v>0.07567162892133202</v>
+        <v>0.03191602661094837</v>
       </c>
     </row>
     <row r="149">
@@ -4013,16 +4013,16 @@
         </is>
       </c>
       <c r="B149" s="18" t="n">
-        <v>2.017062696856321</v>
+        <v>1.858733268954767</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>1.007396366826737</v>
+        <v>1.021748376069088</v>
       </c>
       <c r="D149" s="18" t="n">
-        <v>4.03867043501959</v>
+        <v>3.381350483189477</v>
       </c>
       <c r="E149" s="18" t="n">
-        <v>0.04761736256325892</v>
+        <v>0.04231222668395848</v>
       </c>
     </row>
     <row r="150">
@@ -4032,16 +4032,16 @@
         </is>
       </c>
       <c r="B150" s="18" t="n">
-        <v>2.226052214747695</v>
+        <v>2.073463558781528</v>
       </c>
       <c r="C150" s="18" t="n">
-        <v>0.9737306036417385</v>
+        <v>1.014272047364149</v>
       </c>
       <c r="D150" s="18" t="n">
-        <v>5.088993243357388</v>
+        <v>4.238755411595626</v>
       </c>
       <c r="E150" s="18" t="n">
-        <v>0.05784607790697178</v>
+        <v>0.04562919554351996</v>
       </c>
     </row>
     <row r="151">
@@ -4051,16 +4051,16 @@
         </is>
       </c>
       <c r="B151" s="18" t="n">
-        <v>1.374306357101362</v>
+        <v>1.448017429497565</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>0.2865455654617806</v>
+        <v>0.3850033239597901</v>
       </c>
       <c r="D151" s="18" t="n">
-        <v>6.591335518054398</v>
+        <v>5.446068502898749</v>
       </c>
       <c r="E151" s="18" t="n">
-        <v>0.6910149479343599</v>
+        <v>0.5838812866744562</v>
       </c>
     </row>
     <row r="152">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="B152" s="18" t="n">
-        <v>0.9674994576527554</v>
+        <v>0.9928359144437698</v>
       </c>
       <c r="C152" s="18" t="n">
-        <v>0.8626119829158999</v>
+        <v>0.902704453180498</v>
       </c>
       <c r="D152" s="18" t="n">
-        <v>1.085140502447247</v>
+        <v>1.091966644826442</v>
       </c>
       <c r="E152" s="18" t="n">
-        <v>0.5725223452727237</v>
+        <v>0.882287226465308</v>
       </c>
     </row>
     <row r="153">
@@ -4089,16 +4089,16 @@
         </is>
       </c>
       <c r="B153" s="18" t="n">
-        <v>1.073737581618053</v>
+        <v>1.093575409737481</v>
       </c>
       <c r="C153" s="18" t="n">
-        <v>0.9875127997683898</v>
+        <v>1.0182382795952</v>
       </c>
       <c r="D153" s="18" t="n">
-        <v>1.167491089178173</v>
+        <v>1.174486562475269</v>
       </c>
       <c r="E153" s="18" t="n">
-        <v>0.09576197272368778</v>
+        <v>0.01403947808048361</v>
       </c>
     </row>
     <row r="154">
@@ -4123,14 +4123,14 @@
       <c r="A156" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 2937,
-  "n_events": 78,
-  "llf": -311.58207763500735,
-  "aic": 665.1641552700147,
-  "pseudo_r2_mcfadden": 0.13481681728703465,
-  "lr_vs_null_chi2": 97.10430084577729,
-  "lr_vs_null_pvalue": 4.138800413500121e-12,
-  "n": 2943
+  "n_obs": 3717,
+  "n_events": 214,
+  "llf": -705.8155439536623,
+  "aic": 1453.6310879073246,
+  "pseudo_r2_mcfadden": 0.1381755989661111,
+  "lr_vs_null_chi2": 226.32565387656928,
+  "lr_vs_null_pvalue": 0.0,
+  "n": 3723
 }</t>
         </is>
       </c>
@@ -4146,16 +4146,16 @@
         </is>
       </c>
       <c r="B157" s="18" t="n">
-        <v>0.006502386128745995</v>
+        <v>0.02961641333599032</v>
       </c>
       <c r="C157" s="18" t="n">
-        <v>0.002483292138222203</v>
+        <v>0.01670284886691841</v>
       </c>
       <c r="D157" s="18" t="n">
-        <v>0.0170261986966936</v>
+        <v>0.05251391220005998</v>
       </c>
       <c r="E157" s="18" t="n">
-        <v>1.144884845538456e-24</v>
+        <v>2.096738172505787e-33</v>
       </c>
     </row>
     <row r="158">
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="B158" s="18" t="n">
-        <v>1.039491980508767</v>
+        <v>0.8740880657773543</v>
       </c>
       <c r="C158" s="18" t="n">
-        <v>0.3413370167749384</v>
+        <v>0.4383865328675483</v>
       </c>
       <c r="D158" s="18" t="n">
-        <v>3.165620851061981</v>
+        <v>1.742822576543966</v>
       </c>
       <c r="E158" s="18" t="n">
-        <v>0.9456515439061608</v>
+        <v>0.7023002746012247</v>
       </c>
     </row>
     <row r="159">
@@ -4184,16 +4184,16 @@
         </is>
       </c>
       <c r="B159" s="18" t="n">
-        <v>2.506147697411604</v>
+        <v>2.120503564647267</v>
       </c>
       <c r="C159" s="18" t="n">
-        <v>1.454459174816056</v>
+        <v>1.5308814334992</v>
       </c>
       <c r="D159" s="18" t="n">
-        <v>4.318289842707897</v>
+        <v>2.937219871694339</v>
       </c>
       <c r="E159" s="18" t="n">
-        <v>0.0009348131726604655</v>
+        <v>6.134563065951397e-06</v>
       </c>
     </row>
     <row r="160">
@@ -4203,16 +4203,16 @@
         </is>
       </c>
       <c r="B160" s="18" t="n">
-        <v>1.432107419559416</v>
+        <v>1.165317014084253</v>
       </c>
       <c r="C160" s="18" t="n">
-        <v>0.8590537645802618</v>
+        <v>0.8393964778437122</v>
       </c>
       <c r="D160" s="18" t="n">
-        <v>2.387431084897493</v>
+        <v>1.617785848711982</v>
       </c>
       <c r="E160" s="18" t="n">
-        <v>0.1684089568398224</v>
+        <v>0.3607017594895553</v>
       </c>
     </row>
     <row r="161">
@@ -4222,16 +4222,16 @@
         </is>
       </c>
       <c r="B161" s="18" t="n">
-        <v>0.9349081971309325</v>
+        <v>0.8735426992135542</v>
       </c>
       <c r="C161" s="18" t="n">
-        <v>0.5124098854763646</v>
+        <v>0.6074636400820136</v>
       </c>
       <c r="D161" s="18" t="n">
-        <v>1.705769856976983</v>
+        <v>1.256168759740549</v>
       </c>
       <c r="E161" s="18" t="n">
-        <v>0.8263529696478176</v>
+        <v>0.4657259243377452</v>
       </c>
     </row>
     <row r="162">
@@ -4241,16 +4241,16 @@
         </is>
       </c>
       <c r="B162" s="18" t="n">
-        <v>4.270051806130776</v>
+        <v>4.49458435256201</v>
       </c>
       <c r="C162" s="18" t="n">
-        <v>1.489743097647357</v>
+        <v>2.352629077515152</v>
       </c>
       <c r="D162" s="18" t="n">
-        <v>12.23925283213951</v>
+        <v>8.586686569236777</v>
       </c>
       <c r="E162" s="18" t="n">
-        <v>0.006894966928026183</v>
+        <v>5.357446465921862e-06</v>
       </c>
     </row>
     <row r="163">
@@ -4260,16 +4260,16 @@
         </is>
       </c>
       <c r="B163" s="18" t="n">
-        <v>0.5892028459037042</v>
+        <v>0.4288379624801826</v>
       </c>
       <c r="C163" s="18" t="n">
-        <v>0.1282319714749477</v>
+        <v>0.1481963378435651</v>
       </c>
       <c r="D163" s="18" t="n">
-        <v>2.707281106481686</v>
+        <v>1.240934835098828</v>
       </c>
       <c r="E163" s="18" t="n">
-        <v>0.4965713353907472</v>
+        <v>0.1183399917293768</v>
       </c>
     </row>
     <row r="164">
@@ -4279,16 +4279,16 @@
         </is>
       </c>
       <c r="B164" s="18" t="n">
-        <v>1.000000000018436</v>
+        <v>1.000000000105693</v>
       </c>
       <c r="C164" s="18" t="n">
-        <v>0.9999999407736053</v>
+        <v>0.9999998257194764</v>
       </c>
       <c r="D164" s="18" t="n">
-        <v>1.000000059263269</v>
+        <v>1.00000017449194</v>
       </c>
       <c r="E164" s="18" t="n">
-        <v>0.999513374209284</v>
+        <v>0.9990521897054926</v>
       </c>
     </row>
     <row r="165">
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="B165" s="18" t="n">
-        <v>0.2273963112968222</v>
+        <v>0.5022971485958667</v>
       </c>
       <c r="C165" s="18" t="n">
-        <v>0.06313252446005795</v>
+        <v>0.2709204731794294</v>
       </c>
       <c r="D165" s="18" t="n">
-        <v>0.8190561494830775</v>
+        <v>0.9312785502203056</v>
       </c>
       <c r="E165" s="18" t="n">
-        <v>0.02349721362966498</v>
+        <v>0.02881605688413196</v>
       </c>
     </row>
     <row r="166">
@@ -4317,16 +4317,16 @@
         </is>
       </c>
       <c r="B166" s="18" t="n">
-        <v>5.511069525240767</v>
+        <v>9.144064570827394</v>
       </c>
       <c r="C166" s="18" t="n">
-        <v>2.427593499139761</v>
+        <v>5.154038125161203</v>
       </c>
       <c r="D166" s="18" t="n">
-        <v>12.51110917985241</v>
+        <v>16.22299153498124</v>
       </c>
       <c r="E166" s="18" t="n">
-        <v>4.499699787636427e-05</v>
+        <v>3.857552488581282e-14</v>
       </c>
     </row>
     <row r="167">
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="B167" s="18" t="n">
-        <v>0.8047511377402793</v>
+        <v>1.535383671419794</v>
       </c>
       <c r="C167" s="18" t="n">
-        <v>0.1473111243650166</v>
+        <v>0.551403004866781</v>
       </c>
       <c r="D167" s="18" t="n">
-        <v>4.396303378212971</v>
+        <v>4.275281414239076</v>
       </c>
       <c r="E167" s="18" t="n">
-        <v>0.8020175877862523</v>
+        <v>0.4118505541788997</v>
       </c>
     </row>
     <row r="168">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="B168" s="18" t="n">
-        <v>3.627304409955499e-09</v>
+        <v>4.791429254136652e-10</v>
       </c>
       <c r="C168" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4364,7 +4364,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E168" s="18" t="n">
-        <v>0.9994078977163173</v>
+        <v>0.9992053842352451</v>
       </c>
     </row>
     <row r="169">
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="B169" s="18" t="n">
-        <v>0.6544769775633412</v>
+        <v>0.9007197353429902</v>
       </c>
       <c r="C169" s="18" t="n">
-        <v>0.3039646223368078</v>
+        <v>0.5541818907373862</v>
       </c>
       <c r="D169" s="18" t="n">
-        <v>1.409177524895724</v>
+        <v>1.463952639370528</v>
       </c>
       <c r="E169" s="18" t="n">
-        <v>0.2786430202448145</v>
+        <v>0.6730698860019917</v>
       </c>
     </row>
     <row r="170">
@@ -4393,16 +4393,16 @@
         </is>
       </c>
       <c r="B170" s="18" t="n">
-        <v>1.422492904658981</v>
+        <v>1.946245790267211</v>
       </c>
       <c r="C170" s="18" t="n">
-        <v>0.2864644973892302</v>
+        <v>0.8075847607819454</v>
       </c>
       <c r="D170" s="18" t="n">
-        <v>7.063653898639163</v>
+        <v>4.690371661378586</v>
       </c>
       <c r="E170" s="18" t="n">
-        <v>0.6664624974393105</v>
+        <v>0.1378680671088663</v>
       </c>
     </row>
     <row r="171">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="B171" s="18" t="n">
-        <v>2.604428293731541e-09</v>
+        <v>7.090249897597785e-10</v>
       </c>
       <c r="C171" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4421,7 +4421,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>0.9992422617608214</v>
+        <v>0.9994717092920201</v>
       </c>
     </row>
     <row r="172">
@@ -4431,16 +4431,16 @@
         </is>
       </c>
       <c r="B172" s="18" t="n">
-        <v>0.5566285153286276</v>
+        <v>0.630003769384718</v>
       </c>
       <c r="C172" s="18" t="n">
-        <v>0.1528545047597941</v>
+        <v>0.2558190660296787</v>
       </c>
       <c r="D172" s="18" t="n">
-        <v>2.026994916269221</v>
+        <v>1.551505740361456</v>
       </c>
       <c r="E172" s="18" t="n">
-        <v>0.3742920992143618</v>
+        <v>0.315003997845168</v>
       </c>
     </row>
     <row r="173">
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="B173" s="18" t="n">
-        <v>2.663589003054471</v>
+        <v>1.733364934856402</v>
       </c>
       <c r="C173" s="18" t="n">
-        <v>1.268853652465289</v>
+        <v>1.074930580082491</v>
       </c>
       <c r="D173" s="18" t="n">
-        <v>5.591429999360619</v>
+        <v>2.795114450236561</v>
       </c>
       <c r="E173" s="18" t="n">
-        <v>0.009616984338207854</v>
+        <v>0.02404825321265525</v>
       </c>
     </row>
     <row r="174">
@@ -4469,16 +4469,16 @@
         </is>
       </c>
       <c r="B174" s="18" t="n">
-        <v>3.11341676666997</v>
+        <v>2.033798950768252</v>
       </c>
       <c r="C174" s="18" t="n">
-        <v>1.24604905885045</v>
+        <v>1.125472341786368</v>
       </c>
       <c r="D174" s="18" t="n">
-        <v>7.779279550938675</v>
+        <v>3.67520197393814</v>
       </c>
       <c r="E174" s="18" t="n">
-        <v>0.01506626457807391</v>
+        <v>0.01869785991218164</v>
       </c>
     </row>
     <row r="175">
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="B175" s="18" t="n">
-        <v>4.092504815044139</v>
+        <v>2.319260062663922</v>
       </c>
       <c r="C175" s="18" t="n">
-        <v>1.404453852000103</v>
+        <v>1.149572499518873</v>
       </c>
       <c r="D175" s="18" t="n">
-        <v>11.92534424488746</v>
+        <v>4.67910222323438</v>
       </c>
       <c r="E175" s="18" t="n">
-        <v>0.00981162932763517</v>
+        <v>0.01881299137841413</v>
       </c>
     </row>
     <row r="176">
@@ -4507,16 +4507,16 @@
         </is>
       </c>
       <c r="B176" s="18" t="n">
-        <v>2.712979000475439</v>
+        <v>1.259926287856132</v>
       </c>
       <c r="C176" s="18" t="n">
-        <v>0.562420223457016</v>
+        <v>0.348876291864293</v>
       </c>
       <c r="D176" s="18" t="n">
-        <v>13.08675390756683</v>
+        <v>4.550077743455293</v>
       </c>
       <c r="E176" s="18" t="n">
-        <v>0.2138186518143942</v>
+        <v>0.7243384356783489</v>
       </c>
     </row>
     <row r="177">
@@ -4526,16 +4526,16 @@
         </is>
       </c>
       <c r="B177" s="18" t="n">
-        <v>1.082385853805393</v>
+        <v>0.9834266773090687</v>
       </c>
       <c r="C177" s="18" t="n">
-        <v>0.9306294844737772</v>
+        <v>0.896172002772856</v>
       </c>
       <c r="D177" s="18" t="n">
-        <v>1.258888909134966</v>
+        <v>1.079176794912978</v>
       </c>
       <c r="E177" s="18" t="n">
-        <v>0.3043411616052949</v>
+        <v>0.7244288195025133</v>
       </c>
     </row>
     <row r="178">
@@ -4545,16 +4545,16 @@
         </is>
       </c>
       <c r="B178" s="18" t="n">
-        <v>1.037916303799495</v>
+        <v>1.055864211627583</v>
       </c>
       <c r="C178" s="18" t="n">
-        <v>0.9399201287406929</v>
+        <v>0.9890792227877306</v>
       </c>
       <c r="D178" s="18" t="n">
-        <v>1.146129570749947</v>
+        <v>1.127158682247638</v>
       </c>
       <c r="E178" s="18" t="n">
-        <v>0.4620549727048777</v>
+        <v>0.1029788774497652</v>
       </c>
     </row>
     <row r="179">
@@ -4580,11 +4580,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -514.3309410872571,
-  "aic": 1068.6618821745142,
-  "pseudo_r2_mcfadden": 0.13503753184707556,
-  "lr_vs_null_chi2": 160.59420701876616,
+  "n_events": 215,
+  "llf": -714.135316973247,
+  "aic": 1468.270633946494,
+  "pseudo_r2_mcfadden": 0.13304375652919453,
+  "lr_vs_null_chi2": 219.18348464719793,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="B182" s="18" t="n">
-        <v>0.01558270619948308</v>
+        <v>0.02193579616370823</v>
       </c>
       <c r="C182" s="18" t="n">
-        <v>0.007958222128147056</v>
+        <v>0.01266900247429857</v>
       </c>
       <c r="D182" s="18" t="n">
-        <v>0.03051193201061671</v>
+        <v>0.03798082400819784</v>
       </c>
       <c r="E182" s="18" t="n">
-        <v>6.598402949012798e-34</v>
+        <v>2.403279557726206e-42</v>
       </c>
     </row>
     <row r="183">
@@ -4620,16 +4620,16 @@
         </is>
       </c>
       <c r="B183" s="18" t="n">
-        <v>0.4561132506767128</v>
+        <v>0.7592267712231656</v>
       </c>
       <c r="C183" s="18" t="n">
-        <v>0.193473546532226</v>
+        <v>0.3829853777869559</v>
       </c>
       <c r="D183" s="18" t="n">
-        <v>1.075285490816315</v>
+        <v>1.505084328474291</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>0.07280117755237137</v>
+        <v>0.43014120898417</v>
       </c>
     </row>
     <row r="184">
@@ -4639,16 +4639,16 @@
         </is>
       </c>
       <c r="B184" s="18" t="n">
-        <v>1.775640143294268</v>
+        <v>2.099158656270016</v>
       </c>
       <c r="C184" s="18" t="n">
-        <v>1.198689496902142</v>
+        <v>1.517939544964664</v>
       </c>
       <c r="D184" s="18" t="n">
-        <v>2.630287431921563</v>
+        <v>2.902926588091435</v>
       </c>
       <c r="E184" s="18" t="n">
-        <v>0.004184044109714288</v>
+        <v>7.352251579183788e-06</v>
       </c>
     </row>
     <row r="185">
@@ -4658,16 +4658,16 @@
         </is>
       </c>
       <c r="B185" s="18" t="n">
-        <v>1.322052159491929</v>
+        <v>1.090291139533363</v>
       </c>
       <c r="C185" s="18" t="n">
-        <v>0.8953467408035662</v>
+        <v>0.7866047404091961</v>
       </c>
       <c r="D185" s="18" t="n">
-        <v>1.952117356063212</v>
+        <v>1.511222483005345</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.1603090431561007</v>
+        <v>0.6037852357525764</v>
       </c>
     </row>
     <row r="186">
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="B186" s="18" t="n">
-        <v>0.5284257222228959</v>
+        <v>0.6447629698448469</v>
       </c>
       <c r="C186" s="18" t="n">
-        <v>0.2341764352175732</v>
+        <v>0.3477451420409276</v>
       </c>
       <c r="D186" s="18" t="n">
-        <v>1.19240752660426</v>
+        <v>1.195471156960747</v>
       </c>
       <c r="E186" s="18" t="n">
-        <v>0.1244991954150519</v>
+        <v>0.1635619256870726</v>
       </c>
     </row>
     <row r="187">
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="B187" s="18" t="n">
-        <v>7.562267570680419</v>
+        <v>7.529555248755741</v>
       </c>
       <c r="C187" s="18" t="n">
-        <v>3.88752360721035</v>
+        <v>4.210272233710179</v>
       </c>
       <c r="D187" s="18" t="n">
-        <v>14.71062213088455</v>
+        <v>13.46568561294788</v>
       </c>
       <c r="E187" s="18" t="n">
-        <v>2.532466925013544e-09</v>
+        <v>9.980070247097369e-12</v>
       </c>
     </row>
     <row r="188">
@@ -4715,16 +4715,16 @@
         </is>
       </c>
       <c r="B188" s="18" t="n">
-        <v>2.198079686525436</v>
+        <v>1.783923929054079</v>
       </c>
       <c r="C188" s="18" t="n">
-        <v>0.6958696997203115</v>
+        <v>0.6345453438155381</v>
       </c>
       <c r="D188" s="18" t="n">
-        <v>6.94318822943101</v>
+        <v>5.01522013464945</v>
       </c>
       <c r="E188" s="18" t="n">
-        <v>0.1795680857507256</v>
+        <v>0.2724172327766363</v>
       </c>
     </row>
     <row r="189">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="B189" s="18" t="n">
-        <v>9.103951326479391e-10</v>
+        <v>5.932352999519329e-10</v>
       </c>
       <c r="C189" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4743,7 +4743,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E189" s="18" t="n">
-        <v>0.9992449015869814</v>
+        <v>0.9992300035528022</v>
       </c>
     </row>
     <row r="190">
@@ -4753,16 +4753,16 @@
         </is>
       </c>
       <c r="B190" s="18" t="n">
-        <v>0.7894421567339879</v>
+        <v>0.8157222309044633</v>
       </c>
       <c r="C190" s="18" t="n">
-        <v>0.4387083777085529</v>
+        <v>0.502566496774226</v>
       </c>
       <c r="D190" s="18" t="n">
-        <v>1.42057674413237</v>
+        <v>1.324009384355522</v>
       </c>
       <c r="E190" s="18" t="n">
-        <v>0.4302504600248344</v>
+        <v>0.4098138887986076</v>
       </c>
     </row>
     <row r="191">
@@ -4772,16 +4772,16 @@
         </is>
       </c>
       <c r="B191" s="18" t="n">
-        <v>1.71941403192158</v>
+        <v>1.352159141519583</v>
       </c>
       <c r="C191" s="18" t="n">
-        <v>0.6455881769315401</v>
+        <v>0.5533476215793116</v>
       </c>
       <c r="D191" s="18" t="n">
-        <v>4.579366101808782</v>
+        <v>3.304133374201048</v>
       </c>
       <c r="E191" s="18" t="n">
-        <v>0.278180735790181</v>
+        <v>0.5080800962256082</v>
       </c>
     </row>
     <row r="192">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="B192" s="18" t="n">
-        <v>1.4393615222529e-09</v>
+        <v>8.93397572595958e-10</v>
       </c>
       <c r="C192" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -4800,7 +4800,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E192" s="18" t="n">
-        <v>0.9994934671243756</v>
+        <v>0.9994808793222792</v>
       </c>
     </row>
     <row r="193">
@@ -4810,16 +4810,16 @@
         </is>
       </c>
       <c r="B193" s="18" t="n">
-        <v>0.9463750321896652</v>
+        <v>0.6788091254357314</v>
       </c>
       <c r="C193" s="18" t="n">
-        <v>0.3562539897213807</v>
+        <v>0.280250383111273</v>
       </c>
       <c r="D193" s="18" t="n">
-        <v>2.514008902054519</v>
+        <v>1.644179121752957</v>
       </c>
       <c r="E193" s="18" t="n">
-        <v>0.9119575645804083</v>
+        <v>0.3907147707227822</v>
       </c>
     </row>
     <row r="194">
@@ -4829,16 +4829,16 @@
         </is>
       </c>
       <c r="B194" s="18" t="n">
-        <v>1.493459267068762</v>
+        <v>1.485512051019599</v>
       </c>
       <c r="C194" s="18" t="n">
-        <v>0.8532484804030811</v>
+        <v>0.9287281189651839</v>
       </c>
       <c r="D194" s="18" t="n">
-        <v>2.614034051768713</v>
+        <v>2.376094799609683</v>
       </c>
       <c r="E194" s="18" t="n">
-        <v>0.1602266615639826</v>
+        <v>0.09865089870038776</v>
       </c>
     </row>
     <row r="195">
@@ -4848,16 +4848,16 @@
         </is>
       </c>
       <c r="B195" s="18" t="n">
-        <v>2.050143865100007</v>
+        <v>1.825888345256042</v>
       </c>
       <c r="C195" s="18" t="n">
-        <v>1.02702371229363</v>
+        <v>1.011880932015127</v>
       </c>
       <c r="D195" s="18" t="n">
-        <v>4.092495448055939</v>
+        <v>3.29472385916252</v>
       </c>
       <c r="E195" s="18" t="n">
-        <v>0.04179352348710239</v>
+        <v>0.04558861119520994</v>
       </c>
     </row>
     <row r="196">
@@ -4867,16 +4867,16 @@
         </is>
       </c>
       <c r="B196" s="18" t="n">
-        <v>2.265299968370823</v>
+        <v>2.183416253554489</v>
       </c>
       <c r="C196" s="18" t="n">
-        <v>0.9984223640147887</v>
+        <v>1.094907055993128</v>
       </c>
       <c r="D196" s="18" t="n">
-        <v>5.139692510558431</v>
+        <v>4.354074174781681</v>
       </c>
       <c r="E196" s="18" t="n">
-        <v>0.05044314669462611</v>
+        <v>0.02659368235407789</v>
       </c>
     </row>
     <row r="197">
@@ -4886,16 +4886,16 @@
         </is>
       </c>
       <c r="B197" s="18" t="n">
-        <v>0.9375532466402648</v>
+        <v>0.9872900584676241</v>
       </c>
       <c r="C197" s="18" t="n">
-        <v>0.2041948671644206</v>
+        <v>0.2785810681223005</v>
       </c>
       <c r="D197" s="18" t="n">
-        <v>4.304741360505957</v>
+        <v>3.498951547996366</v>
       </c>
       <c r="E197" s="18" t="n">
-        <v>0.933917603975719</v>
+        <v>0.9841911615659291</v>
       </c>
     </row>
     <row r="198">
@@ -4905,16 +4905,16 @@
         </is>
       </c>
       <c r="B198" s="18" t="n">
-        <v>0.9804731615872898</v>
+        <v>1.006945562717337</v>
       </c>
       <c r="C198" s="18" t="n">
-        <v>0.8739526713807529</v>
+        <v>0.9172786925790674</v>
       </c>
       <c r="D198" s="18" t="n">
-        <v>1.099976751686312</v>
+        <v>1.105377650739157</v>
       </c>
       <c r="E198" s="18" t="n">
-        <v>0.7368219511609719</v>
+        <v>0.8843511029534761</v>
       </c>
     </row>
     <row r="199">
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="B199" s="18" t="n">
-        <v>1.035860268228134</v>
+        <v>1.040547995089876</v>
       </c>
       <c r="C199" s="18" t="n">
-        <v>0.9576991842918307</v>
+        <v>0.9749023462756607</v>
       </c>
       <c r="D199" s="18" t="n">
-        <v>1.120400343754177</v>
+        <v>1.110613934023099</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.3787584860491614</v>
+        <v>0.2319016666789824</v>
       </c>
     </row>
     <row r="200">
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="B200" s="18" t="n">
-        <v>1.697450756056017</v>
+        <v>1.661448591969847</v>
       </c>
       <c r="C200" s="18" t="n">
-        <v>1.109168728788738</v>
+        <v>1.169994376690488</v>
       </c>
       <c r="D200" s="18" t="n">
-        <v>2.597746397323784</v>
+        <v>2.359337342771544</v>
       </c>
       <c r="E200" s="18" t="n">
-        <v>0.01480133540652553</v>
+        <v>0.004548120032129202</v>
       </c>
     </row>
     <row r="201">
@@ -4962,16 +4962,16 @@
         </is>
       </c>
       <c r="B201" s="18" t="n">
-        <v>1.852318989337813</v>
+        <v>1.746660325285298</v>
       </c>
       <c r="C201" s="18" t="n">
-        <v>1.161468867415143</v>
+        <v>1.181538383080506</v>
       </c>
       <c r="D201" s="18" t="n">
-        <v>2.954091783706061</v>
+        <v>2.582076329989081</v>
       </c>
       <c r="E201" s="18" t="n">
-        <v>0.009639067461523146</v>
+        <v>0.005167422331225389</v>
       </c>
     </row>
     <row r="202">
@@ -4997,11 +4997,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -516.6771864168462,
-  "aic": 1061.3543728336924,
-  "pseudo_r2_mcfadden": 0.13109179576733743,
-  "lr_vs_null_chi2": 155.9017163595879,
+  "n_events": 215,
+  "llf": -712.1996046084913,
+  "aic": 1452.3992092169826,
+  "pseudo_r2_mcfadden": 0.13539370041280085,
+  "lr_vs_null_chi2": 223.05490937670925,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + lvi_pooled"
 }</t>
@@ -5019,16 +5019,16 @@
         </is>
       </c>
       <c r="B205" s="18" t="n">
-        <v>0.02021087491374193</v>
+        <v>0.0282043653121083</v>
       </c>
       <c r="C205" s="18" t="n">
-        <v>0.01007384412305387</v>
+        <v>0.01595285073222471</v>
       </c>
       <c r="D205" s="18" t="n">
-        <v>0.04054851949159335</v>
+        <v>0.04986483206114239</v>
       </c>
       <c r="E205" s="18" t="n">
-        <v>4.639862840917422e-28</v>
+        <v>1.263125848351358e-34</v>
       </c>
     </row>
     <row r="206">
@@ -5038,16 +5038,16 @@
         </is>
       </c>
       <c r="B206" s="18" t="n">
-        <v>0.4989896103159552</v>
+        <v>0.8298942546474736</v>
       </c>
       <c r="C206" s="18" t="n">
-        <v>0.2155895438926285</v>
+        <v>0.4225617846244109</v>
       </c>
       <c r="D206" s="18" t="n">
-        <v>1.154929068950001</v>
+        <v>1.629878751361888</v>
       </c>
       <c r="E206" s="18" t="n">
-        <v>0.1044692101109838</v>
+        <v>0.5882071744861469</v>
       </c>
     </row>
     <row r="207">
@@ -5057,16 +5057,16 @@
         </is>
       </c>
       <c r="B207" s="18" t="n">
-        <v>1.785223429482206</v>
+        <v>2.093069550548686</v>
       </c>
       <c r="C207" s="18" t="n">
-        <v>1.208688057254049</v>
+        <v>1.515559944614788</v>
       </c>
       <c r="D207" s="18" t="n">
-        <v>2.636761961901592</v>
+        <v>2.89064128344167</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>0.003585891927572074</v>
+        <v>7.320681499166082e-06</v>
       </c>
     </row>
     <row r="208">
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="B208" s="18" t="n">
-        <v>1.450582494586032</v>
+        <v>1.190006467246747</v>
       </c>
       <c r="C208" s="18" t="n">
-        <v>0.9837675594159131</v>
+        <v>0.8589453870736911</v>
       </c>
       <c r="D208" s="18" t="n">
-        <v>2.138909291589921</v>
+        <v>1.648667556052188</v>
       </c>
       <c r="E208" s="18" t="n">
-        <v>0.06046819558825961</v>
+        <v>0.295634976816598</v>
       </c>
     </row>
     <row r="209">
@@ -5095,16 +5095,16 @@
         </is>
       </c>
       <c r="B209" s="18" t="n">
-        <v>0.9586351885531028</v>
+        <v>0.8709174545468802</v>
       </c>
       <c r="C209" s="18" t="n">
-        <v>0.6102427771461318</v>
+        <v>0.6068328582419783</v>
       </c>
       <c r="D209" s="18" t="n">
-        <v>1.505927573661686</v>
+        <v>1.249927722819455</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>0.8545453785793159</v>
+        <v>0.4534005796244309</v>
       </c>
     </row>
     <row r="210">
@@ -5114,16 +5114,16 @@
         </is>
       </c>
       <c r="B210" s="18" t="n">
-        <v>3.754784499347152</v>
+        <v>4.02483933354569</v>
       </c>
       <c r="C210" s="18" t="n">
-        <v>1.793322837679357</v>
+        <v>2.150199696127421</v>
       </c>
       <c r="D210" s="18" t="n">
-        <v>7.861611049788244</v>
+        <v>7.533873104917662</v>
       </c>
       <c r="E210" s="18" t="n">
-        <v>0.0004496119807850231</v>
+        <v>1.340731831064834e-05</v>
       </c>
     </row>
     <row r="211">
@@ -5133,16 +5133,16 @@
         </is>
       </c>
       <c r="B211" s="18" t="n">
-        <v>0.4118148680669095</v>
+        <v>0.4355096019050894</v>
       </c>
       <c r="C211" s="18" t="n">
-        <v>0.0955116463255176</v>
+        <v>0.1505849021265845</v>
       </c>
       <c r="D211" s="18" t="n">
-        <v>1.775610536363006</v>
+        <v>1.259546014726566</v>
       </c>
       <c r="E211" s="18" t="n">
-        <v>0.2340824456473867</v>
+        <v>0.1250053160872032</v>
       </c>
     </row>
     <row r="212">
@@ -5152,16 +5152,16 @@
         </is>
       </c>
       <c r="B212" s="18" t="n">
-        <v>1.00000000000327</v>
+        <v>1.000000000001177</v>
       </c>
       <c r="C212" s="18" t="n">
-        <v>0.9999999956643517</v>
+        <v>0.9999999984947672</v>
       </c>
       <c r="D212" s="18" t="n">
-        <v>1.000000004342188</v>
+        <v>1.000000001507586</v>
       </c>
       <c r="E212" s="18" t="n">
-        <v>0.9988214123415327</v>
+        <v>0.9987785812941992</v>
       </c>
     </row>
     <row r="213">
@@ -5171,16 +5171,16 @@
         </is>
       </c>
       <c r="B213" s="18" t="n">
-        <v>0.4717581387369719</v>
+        <v>0.5743450945529802</v>
       </c>
       <c r="C213" s="18" t="n">
-        <v>0.2189528681764931</v>
+        <v>0.3221750807703656</v>
       </c>
       <c r="D213" s="18" t="n">
-        <v>1.016455017548228</v>
+        <v>1.023891378713403</v>
       </c>
       <c r="E213" s="18" t="n">
-        <v>0.05507415145672048</v>
+        <v>0.06011883316538222</v>
       </c>
     </row>
     <row r="214">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="B214" s="18" t="n">
-        <v>9.8201402853639</v>
+        <v>9.976252761719667</v>
       </c>
       <c r="C214" s="18" t="n">
-        <v>5.395221760316788</v>
+        <v>5.817409196678264</v>
       </c>
       <c r="D214" s="18" t="n">
-        <v>17.8741782096024</v>
+        <v>17.10823767091171</v>
       </c>
       <c r="E214" s="18" t="n">
-        <v>7.67431478608694e-14</v>
+        <v>6.337539613111559e-17</v>
       </c>
     </row>
     <row r="215">
@@ -5209,16 +5209,16 @@
         </is>
       </c>
       <c r="B215" s="18" t="n">
-        <v>2.552818777147555</v>
+        <v>2.020047290290464</v>
       </c>
       <c r="C215" s="18" t="n">
-        <v>0.8931136058738828</v>
+        <v>0.7739751825708665</v>
       </c>
       <c r="D215" s="18" t="n">
-        <v>7.296813827598761</v>
+        <v>5.272250515133563</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.08029011518904421</v>
+        <v>0.1508586470327974</v>
       </c>
     </row>
     <row r="216">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="B216" s="18" t="n">
-        <v>2.77554256357657e-09</v>
+        <v>1.660170479810267e-09</v>
       </c>
       <c r="C216" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5237,7 +5237,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E216" s="18" t="n">
-        <v>0.998821533441568</v>
+        <v>0.9987785443531838</v>
       </c>
     </row>
     <row r="217">
@@ -5247,16 +5247,16 @@
         </is>
       </c>
       <c r="B217" s="18" t="n">
-        <v>0.9497976034238311</v>
+        <v>0.9831267030436431</v>
       </c>
       <c r="C217" s="18" t="n">
-        <v>0.848063408220661</v>
+        <v>0.8964529886867645</v>
       </c>
       <c r="D217" s="18" t="n">
-        <v>1.063735893713891</v>
+        <v>1.078180480666776</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.3729002445685488</v>
+        <v>0.7178096979466315</v>
       </c>
     </row>
     <row r="218">
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="B218" s="18" t="n">
-        <v>1.055658601574149</v>
+        <v>1.058600486229593</v>
       </c>
       <c r="C218" s="18" t="n">
-        <v>0.9768026587729246</v>
+        <v>0.9919192256488029</v>
       </c>
       <c r="D218" s="18" t="n">
-        <v>1.140880476797058</v>
+        <v>1.129764360311231</v>
       </c>
       <c r="E218" s="18" t="n">
-        <v>0.1714903283776943</v>
+        <v>0.08624574236341118</v>
       </c>
     </row>
     <row r="219">
@@ -5285,16 +5285,16 @@
         </is>
       </c>
       <c r="B219" s="18" t="n">
-        <v>1.798068443931119</v>
+        <v>1.736019918952562</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>1.20577367633964</v>
+        <v>1.248760103747459</v>
       </c>
       <c r="D219" s="18" t="n">
-        <v>2.681307605649035</v>
+        <v>2.413406025669718</v>
       </c>
       <c r="E219" s="18" t="n">
-        <v>0.004004853466394754</v>
+        <v>0.001032163052633909</v>
       </c>
     </row>
     <row r="220">
@@ -5320,11 +5320,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -514.0770137496083,
-  "aic": 1064.1540274992167,
-  "pseudo_r2_mcfadden": 0.13546456743672897,
-  "lr_vs_null_chi2": 161.10206169406365,
+  "n_events": 215,
+  "llf": -709.8259564119642,
+  "aic": 1455.6519128239283,
+  "pseudo_r2_mcfadden": 0.138275295924005,
+  "lr_vs_null_chi2": 227.80220576976353,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + vasc_ord",
   "ordering_note": "vasc_ord: missing=0 indeterminate=1 focal=2 present_ungraded=3 extensive=4; single linear coefficient"
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="B223" s="18" t="n">
-        <v>0.02021578303280587</v>
+        <v>0.02890017066023267</v>
       </c>
       <c r="C223" s="18" t="n">
-        <v>0.01004315881694216</v>
+        <v>0.0163328939196919</v>
       </c>
       <c r="D223" s="18" t="n">
-        <v>0.0406921657895192</v>
+        <v>0.05113728579254304</v>
       </c>
       <c r="E223" s="18" t="n">
-        <v>8.275750841785054e-28</v>
+        <v>4.402842348642961e-34</v>
       </c>
     </row>
     <row r="224">
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="B224" s="18" t="n">
-        <v>0.5076149945951421</v>
+        <v>0.8491520652088658</v>
       </c>
       <c r="C224" s="18" t="n">
-        <v>0.2165706734857252</v>
+        <v>0.4293395226368517</v>
       </c>
       <c r="D224" s="18" t="n">
-        <v>1.189787050068024</v>
+        <v>1.679461572556821</v>
       </c>
       <c r="E224" s="18" t="n">
-        <v>0.1187320275647923</v>
+        <v>0.6384052923205573</v>
       </c>
     </row>
     <row r="225">
@@ -5381,16 +5381,16 @@
         </is>
       </c>
       <c r="B225" s="18" t="n">
-        <v>1.779513087702086</v>
+        <v>2.104485219365471</v>
       </c>
       <c r="C225" s="18" t="n">
-        <v>1.200855012945102</v>
+        <v>1.520171568820456</v>
       </c>
       <c r="D225" s="18" t="n">
-        <v>2.637010126257248</v>
+        <v>2.913393546732496</v>
       </c>
       <c r="E225" s="18" t="n">
-        <v>0.004077829649028558</v>
+        <v>7.331844050631755e-06</v>
       </c>
     </row>
     <row r="226">
@@ -5400,16 +5400,16 @@
         </is>
       </c>
       <c r="B226" s="18" t="n">
-        <v>1.408371982916118</v>
+        <v>1.162906335321241</v>
       </c>
       <c r="C226" s="18" t="n">
-        <v>0.9531309146755466</v>
+        <v>0.8379750504253313</v>
       </c>
       <c r="D226" s="18" t="n">
-        <v>2.081048481087493</v>
+        <v>1.613832230498826</v>
       </c>
       <c r="E226" s="18" t="n">
-        <v>0.08561568676498212</v>
+        <v>0.3666896402242579</v>
       </c>
     </row>
     <row r="227">
@@ -5419,16 +5419,16 @@
         </is>
       </c>
       <c r="B227" s="18" t="n">
-        <v>0.9556421948568169</v>
+        <v>0.8725915084373611</v>
       </c>
       <c r="C227" s="18" t="n">
-        <v>0.6069274813015296</v>
+        <v>0.6069995046643396</v>
       </c>
       <c r="D227" s="18" t="n">
-        <v>1.504713549355724</v>
+        <v>1.25439301802732</v>
       </c>
       <c r="E227" s="18" t="n">
-        <v>0.8446998873950659</v>
+        <v>0.4617381277658357</v>
       </c>
     </row>
     <row r="228">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="B228" s="18" t="n">
-        <v>4.066874901013504</v>
+        <v>4.402180562178683</v>
       </c>
       <c r="C228" s="18" t="n">
-        <v>1.917534829722519</v>
+        <v>2.32808411401924</v>
       </c>
       <c r="D228" s="18" t="n">
-        <v>8.625382550619422</v>
+        <v>8.3240951584723</v>
       </c>
       <c r="E228" s="18" t="n">
-        <v>0.000255018136839859</v>
+        <v>5.119384931465885e-06</v>
       </c>
     </row>
     <row r="229">
@@ -5457,16 +5457,16 @@
         </is>
       </c>
       <c r="B229" s="18" t="n">
-        <v>0.4003701459361611</v>
+        <v>0.4275000825408111</v>
       </c>
       <c r="C229" s="18" t="n">
-        <v>0.09287256622300004</v>
+        <v>0.1477958113069454</v>
       </c>
       <c r="D229" s="18" t="n">
-        <v>1.725980666584028</v>
+        <v>1.236546008687947</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.2195039942711237</v>
+        <v>0.1168436989081877</v>
       </c>
     </row>
     <row r="230">
@@ -5476,16 +5476,16 @@
         </is>
       </c>
       <c r="B230" s="18" t="n">
-        <v>0.9999999999482392</v>
+        <v>0.9999999999864125</v>
       </c>
       <c r="C230" s="18" t="n">
-        <v>0.9999998616657745</v>
+        <v>0.9999998998641648</v>
       </c>
       <c r="D230" s="18" t="n">
-        <v>1.000000138230723</v>
+        <v>1.00000010010867</v>
       </c>
       <c r="E230" s="18" t="n">
-        <v>0.9994146412575946</v>
+        <v>0.9997877758356626</v>
       </c>
     </row>
     <row r="231">
@@ -5495,16 +5495,16 @@
         </is>
       </c>
       <c r="B231" s="18" t="n">
-        <v>0.4380380453631007</v>
+        <v>0.5290437825841563</v>
       </c>
       <c r="C231" s="18" t="n">
-        <v>0.1979211564198063</v>
+        <v>0.2893894298663757</v>
       </c>
       <c r="D231" s="18" t="n">
-        <v>0.9694634603818654</v>
+        <v>0.9671649860196647</v>
       </c>
       <c r="E231" s="18" t="n">
-        <v>0.04170265716477136</v>
+        <v>0.038599856736349</v>
       </c>
     </row>
     <row r="232">
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="B232" s="18" t="n">
-        <v>9.240682230034299</v>
+        <v>9.202476455822191</v>
       </c>
       <c r="C232" s="18" t="n">
-        <v>4.816939662489399</v>
+        <v>5.200857582901821</v>
       </c>
       <c r="D232" s="18" t="n">
-        <v>17.72706615808882</v>
+        <v>16.28300171078928</v>
       </c>
       <c r="E232" s="18" t="n">
-        <v>2.235779085816426e-11</v>
+        <v>2.477514511383969e-14</v>
       </c>
     </row>
     <row r="233">
@@ -5533,16 +5533,16 @@
         </is>
       </c>
       <c r="B233" s="18" t="n">
-        <v>1.999491236306959</v>
+        <v>1.609530347682741</v>
       </c>
       <c r="C233" s="18" t="n">
-        <v>0.6687322678615895</v>
+        <v>0.5963344824349917</v>
       </c>
       <c r="D233" s="18" t="n">
-        <v>5.978424245703977</v>
+        <v>4.34418605064337</v>
       </c>
       <c r="E233" s="18" t="n">
-        <v>0.2150033636246387</v>
+        <v>0.3474719016025141</v>
       </c>
     </row>
     <row r="234">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="B234" s="18" t="n">
-        <v>8.759297823946155e-10</v>
+        <v>4.96648932409047e-10</v>
       </c>
       <c r="C234" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5561,7 +5561,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E234" s="18" t="n">
-        <v>0.9992348976493073</v>
+        <v>0.9992033016551882</v>
       </c>
     </row>
     <row r="235">
@@ -5571,16 +5571,16 @@
         </is>
       </c>
       <c r="B235" s="18" t="n">
-        <v>0.8685151775231328</v>
+        <v>0.8711803043646615</v>
       </c>
       <c r="C235" s="18" t="n">
-        <v>0.4892619510418486</v>
+        <v>0.5420489929615676</v>
       </c>
       <c r="D235" s="18" t="n">
-        <v>1.541747957268639</v>
+        <v>1.400159639751818</v>
       </c>
       <c r="E235" s="18" t="n">
-        <v>0.6301983911821611</v>
+        <v>0.5689198035538321</v>
       </c>
     </row>
     <row r="236">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="B236" s="18" t="n">
-        <v>2.389099544200504</v>
+        <v>1.823775901686652</v>
       </c>
       <c r="C236" s="18" t="n">
-        <v>0.9315880517442182</v>
+        <v>0.7658049442747247</v>
       </c>
       <c r="D236" s="18" t="n">
-        <v>6.126953454815474</v>
+        <v>4.343349523191033</v>
       </c>
       <c r="E236" s="18" t="n">
-        <v>0.06991113841275953</v>
+        <v>0.1746929074535691</v>
       </c>
     </row>
     <row r="237">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="B237" s="18" t="n">
-        <v>1.231945251982972e-09</v>
+        <v>7.369087259254642e-10</v>
       </c>
       <c r="C237" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5618,7 +5618,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E237" s="18" t="n">
-        <v>0.9994855173397333</v>
+        <v>0.9994706976073712</v>
       </c>
     </row>
     <row r="238">
@@ -5628,16 +5628,16 @@
         </is>
       </c>
       <c r="B238" s="18" t="n">
-        <v>0.8528192223852246</v>
+        <v>0.6093198451580134</v>
       </c>
       <c r="C238" s="18" t="n">
-        <v>0.3220682522275975</v>
+        <v>0.252162483952816</v>
       </c>
       <c r="D238" s="18" t="n">
-        <v>2.258218936636369</v>
+        <v>1.472346987876502</v>
       </c>
       <c r="E238" s="18" t="n">
-        <v>0.7486332890558427</v>
+        <v>0.2710887576932827</v>
       </c>
     </row>
     <row r="239">
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c r="B239" s="18" t="n">
-        <v>0.9595608500498829</v>
+        <v>0.9895876706405301</v>
       </c>
       <c r="C239" s="18" t="n">
-        <v>0.8563476739647639</v>
+        <v>0.9020798523421817</v>
       </c>
       <c r="D239" s="18" t="n">
-        <v>1.075214019891575</v>
+        <v>1.08558433639895</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.4771107034485677</v>
+        <v>0.8246431617771646</v>
       </c>
     </row>
     <row r="240">
@@ -5666,16 +5666,16 @@
         </is>
       </c>
       <c r="B240" s="18" t="n">
-        <v>1.055286575123502</v>
+        <v>1.057486563108572</v>
       </c>
       <c r="C240" s="18" t="n">
-        <v>0.9765435966192686</v>
+        <v>0.9909824818883749</v>
       </c>
       <c r="D240" s="18" t="n">
-        <v>1.140378944156929</v>
+        <v>1.128453682676848</v>
       </c>
       <c r="E240" s="18" t="n">
-        <v>0.1738108311663643</v>
+        <v>0.09167518201962434</v>
       </c>
     </row>
     <row r="241">
@@ -5685,16 +5685,16 @@
         </is>
       </c>
       <c r="B241" s="18" t="n">
-        <v>1.231242209331055</v>
+        <v>1.227503589370899</v>
       </c>
       <c r="C241" s="18" t="n">
-        <v>1.045468583210665</v>
+        <v>1.070449691677504</v>
       </c>
       <c r="D241" s="18" t="n">
-        <v>1.450026717572773</v>
+        <v>1.407600070917097</v>
       </c>
       <c r="E241" s="18" t="n">
-        <v>0.01267394131018272</v>
+        <v>0.003339715422725731</v>
       </c>
     </row>
     <row r="242">
@@ -5720,11 +5720,11 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -513.1710224690692,
-  "aic": 1068.3420449381383,
-  "pseudo_r2_mcfadden": 0.13698819433050213,
-  "lr_vs_null_chi2": 162.91404425514202,
+  "n_events": 215,
+  "llf": -709.1297224214745,
+  "aic": 1460.259444842949,
+  "pseudo_r2_mcfadden": 0.13912052005817865,
+  "lr_vs_null_chi2": 229.19467375074282,
   "lr_vs_null_pvalue": 0.0,
   "n": 3756,
   "n_removed": 0
@@ -5743,16 +5743,16 @@
         </is>
       </c>
       <c r="B245" s="18" t="n">
-        <v>0.01988594511462615</v>
+        <v>0.02852887875313093</v>
       </c>
       <c r="C245" s="18" t="n">
-        <v>0.009863719699586606</v>
+        <v>0.01609471932509537</v>
       </c>
       <c r="D245" s="18" t="n">
-        <v>0.04009144877854725</v>
+        <v>0.05056919020897697</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>6.536582072095258e-28</v>
+        <v>4.047461154556698e-34</v>
       </c>
     </row>
     <row r="246">
@@ -5762,16 +5762,16 @@
         </is>
       </c>
       <c r="B246" s="18" t="n">
-        <v>0.5206463545221218</v>
+        <v>0.8679286099430543</v>
       </c>
       <c r="C246" s="18" t="n">
-        <v>0.2208502401334555</v>
+        <v>0.4371570253485023</v>
       </c>
       <c r="D246" s="18" t="n">
-        <v>1.227404716940181</v>
+        <v>1.723179608876583</v>
       </c>
       <c r="E246" s="18" t="n">
-        <v>0.1357850626236083</v>
+        <v>0.6856224175786536</v>
       </c>
     </row>
     <row r="247">
@@ -5781,16 +5781,16 @@
         </is>
       </c>
       <c r="B247" s="18" t="n">
-        <v>1.803142473049095</v>
+        <v>2.123642026911864</v>
       </c>
       <c r="C247" s="18" t="n">
-        <v>1.216513912993914</v>
+        <v>1.533370870140629</v>
       </c>
       <c r="D247" s="18" t="n">
-        <v>2.672655646092781</v>
+        <v>2.941138080999752</v>
       </c>
       <c r="E247" s="18" t="n">
-        <v>0.003324166076161699</v>
+        <v>5.825549371409613e-06</v>
       </c>
     </row>
     <row r="248">
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="B248" s="18" t="n">
-        <v>1.415612656293561</v>
+        <v>1.16544897652856</v>
       </c>
       <c r="C248" s="18" t="n">
-        <v>0.9581423942358207</v>
+        <v>0.8398800321125361</v>
       </c>
       <c r="D248" s="18" t="n">
-        <v>2.091504566246436</v>
+        <v>1.617220632659917</v>
       </c>
       <c r="E248" s="18" t="n">
-        <v>0.08094065547071114</v>
+        <v>0.3596684419975973</v>
       </c>
     </row>
     <row r="249">
@@ -5819,16 +5819,16 @@
         </is>
       </c>
       <c r="B249" s="18" t="n">
-        <v>0.9499944309815281</v>
+        <v>0.8690043784773853</v>
       </c>
       <c r="C249" s="18" t="n">
-        <v>0.6030069709102067</v>
+        <v>0.6042699958265132</v>
       </c>
       <c r="D249" s="18" t="n">
-        <v>1.496648401151413</v>
+        <v>1.2497205140559</v>
       </c>
       <c r="E249" s="18" t="n">
-        <v>0.8249314914809697</v>
+        <v>0.4487954545213408</v>
       </c>
     </row>
     <row r="250">
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="B250" s="18" t="n">
-        <v>4.064670487927987</v>
+        <v>4.397015389057731</v>
       </c>
       <c r="C250" s="18" t="n">
-        <v>1.916630062128161</v>
+        <v>2.326080233319977</v>
       </c>
       <c r="D250" s="18" t="n">
-        <v>8.620101761885014</v>
+        <v>8.311727194386481</v>
       </c>
       <c r="E250" s="18" t="n">
-        <v>0.0002560862557023112</v>
+        <v>5.152961060231732e-06</v>
       </c>
     </row>
     <row r="251">
@@ -5857,16 +5857,16 @@
         </is>
       </c>
       <c r="B251" s="18" t="n">
-        <v>0.4032548237157969</v>
+        <v>0.4294096849113297</v>
       </c>
       <c r="C251" s="18" t="n">
-        <v>0.09349528866863331</v>
+        <v>0.1483860822294949</v>
       </c>
       <c r="D251" s="18" t="n">
-        <v>1.739279648907205</v>
+        <v>1.242654801078072</v>
       </c>
       <c r="E251" s="18" t="n">
-        <v>0.223298329848847</v>
+        <v>0.1189385695345342</v>
       </c>
     </row>
     <row r="252">
@@ -5876,16 +5876,16 @@
         </is>
       </c>
       <c r="B252" s="18" t="n">
-        <v>0.9999999999688559</v>
+        <v>1.000000000077513</v>
       </c>
       <c r="C252" s="18" t="n">
-        <v>0.9999997709597415</v>
+        <v>0.9999996684323157</v>
       </c>
       <c r="D252" s="18" t="n">
-        <v>1.000000228978023</v>
+        <v>1.00000033172282</v>
       </c>
       <c r="E252" s="18" t="n">
-        <v>0.9997873278281352</v>
+        <v>0.9996344992021077</v>
       </c>
     </row>
     <row r="253">
@@ -5895,16 +5895,16 @@
         </is>
       </c>
       <c r="B253" s="18" t="n">
-        <v>0.4025658212119963</v>
+        <v>0.4981391512004436</v>
       </c>
       <c r="C253" s="18" t="n">
-        <v>0.1790133646743263</v>
+        <v>0.2688062120348371</v>
       </c>
       <c r="D253" s="18" t="n">
-        <v>0.905291293211088</v>
+        <v>0.9231282717772138</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.02776413268177217</v>
+        <v>0.0268221065984008</v>
       </c>
     </row>
     <row r="254">
@@ -5914,16 +5914,16 @@
         </is>
       </c>
       <c r="B254" s="18" t="n">
-        <v>9.263262405819596</v>
+        <v>9.179036364441508</v>
       </c>
       <c r="C254" s="18" t="n">
-        <v>4.810900420995349</v>
+        <v>5.174699297923713</v>
       </c>
       <c r="D254" s="18" t="n">
-        <v>17.83616846954347</v>
+        <v>16.28204920304177</v>
       </c>
       <c r="E254" s="18" t="n">
-        <v>2.751261191735409e-11</v>
+        <v>3.424138831731132e-14</v>
       </c>
     </row>
     <row r="255">
@@ -5933,16 +5933,16 @@
         </is>
       </c>
       <c r="B255" s="18" t="n">
-        <v>1.865793604816147</v>
+        <v>1.529009881734143</v>
       </c>
       <c r="C255" s="18" t="n">
-        <v>0.5997323531271759</v>
+        <v>0.5494736550444274</v>
       </c>
       <c r="D255" s="18" t="n">
-        <v>5.804565582665226</v>
+        <v>4.254746696184426</v>
       </c>
       <c r="E255" s="18" t="n">
-        <v>0.2814594132836437</v>
+        <v>0.4161035542764218</v>
       </c>
     </row>
     <row r="256">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="B256" s="18" t="n">
-        <v>8.234027567608161e-10</v>
+        <v>4.753608602848542e-10</v>
       </c>
       <c r="C256" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -5961,7 +5961,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E256" s="18" t="n">
-        <v>0.9992368963221444</v>
+        <v>0.9992050878233492</v>
       </c>
     </row>
     <row r="257">
@@ -5971,16 +5971,16 @@
         </is>
       </c>
       <c r="B257" s="18" t="n">
-        <v>0.8900578758120722</v>
+        <v>0.8869742759961744</v>
       </c>
       <c r="C257" s="18" t="n">
-        <v>0.4972517251809978</v>
+        <v>0.547161887363565</v>
       </c>
       <c r="D257" s="18" t="n">
-        <v>1.593162943792179</v>
+        <v>1.437825595034902</v>
       </c>
       <c r="E257" s="18" t="n">
-        <v>0.6949870010775374</v>
+        <v>0.6265209498249684</v>
       </c>
     </row>
     <row r="258">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="B258" s="18" t="n">
-        <v>2.47107536511665</v>
+        <v>1.871844245674674</v>
       </c>
       <c r="C258" s="18" t="n">
-        <v>0.9552563654630051</v>
+        <v>0.7807492309684739</v>
       </c>
       <c r="D258" s="18" t="n">
-        <v>6.392224831840564</v>
+        <v>4.487741698725889</v>
       </c>
       <c r="E258" s="18" t="n">
-        <v>0.06210208227991191</v>
+        <v>0.1599597164104432</v>
       </c>
     </row>
     <row r="259">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B259" s="18" t="n">
-        <v>1.149473429389386e-09</v>
+        <v>7.024314372146672e-10</v>
       </c>
       <c r="C259" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6018,7 +6018,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E259" s="18" t="n">
-        <v>0.9994853005318667</v>
+        <v>0.9994713992834721</v>
       </c>
     </row>
     <row r="260">
@@ -6028,16 +6028,16 @@
         </is>
       </c>
       <c r="B260" s="18" t="n">
-        <v>0.8994143043047916</v>
+        <v>0.6314560528350701</v>
       </c>
       <c r="C260" s="18" t="n">
-        <v>0.3327371250746828</v>
+        <v>0.2568131584400292</v>
       </c>
       <c r="D260" s="18" t="n">
-        <v>2.431186753226003</v>
+        <v>1.552633630940525</v>
       </c>
       <c r="E260" s="18" t="n">
-        <v>0.8344867055868793</v>
+        <v>0.316574843170173</v>
       </c>
     </row>
     <row r="261">
@@ -6047,16 +6047,16 @@
         </is>
       </c>
       <c r="B261" s="18" t="n">
-        <v>1.730704538765681</v>
+        <v>1.750121052252119</v>
       </c>
       <c r="C261" s="18" t="n">
-        <v>0.9825439306167997</v>
+        <v>1.088258406762066</v>
       </c>
       <c r="D261" s="18" t="n">
-        <v>3.048553970125062</v>
+        <v>2.814518756302825</v>
       </c>
       <c r="E261" s="18" t="n">
-        <v>0.05756478400617664</v>
+        <v>0.02095037504959985</v>
       </c>
     </row>
     <row r="262">
@@ -6066,16 +6066,16 @@
         </is>
       </c>
       <c r="B262" s="18" t="n">
-        <v>2.295459213080083</v>
+        <v>2.061082258861333</v>
       </c>
       <c r="C262" s="18" t="n">
-        <v>1.149102116321469</v>
+        <v>1.141426139715414</v>
       </c>
       <c r="D262" s="18" t="n">
-        <v>4.585434944443316</v>
+        <v>3.721712627723844</v>
       </c>
       <c r="E262" s="18" t="n">
-        <v>0.01859114256048079</v>
+        <v>0.0164542393137029</v>
       </c>
     </row>
     <row r="263">
@@ -6085,16 +6085,16 @@
         </is>
       </c>
       <c r="B263" s="18" t="n">
-        <v>2.426078408991358</v>
+        <v>2.351957211059262</v>
       </c>
       <c r="C263" s="18" t="n">
-        <v>1.06057102469977</v>
+        <v>1.168892655195049</v>
       </c>
       <c r="D263" s="18" t="n">
-        <v>5.549705120635581</v>
+        <v>4.732430046564549</v>
       </c>
       <c r="E263" s="18" t="n">
-        <v>0.03579426143389201</v>
+        <v>0.01651095330410831</v>
       </c>
     </row>
     <row r="264">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="B264" s="18" t="n">
-        <v>1.123627441098395</v>
+        <v>1.202640879497502</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>0.2422511546911807</v>
+        <v>0.3351725935101096</v>
       </c>
       <c r="D264" s="18" t="n">
-        <v>5.211692914317777</v>
+        <v>4.315224791775526</v>
       </c>
       <c r="E264" s="18" t="n">
-        <v>0.8816355286876478</v>
+        <v>0.7771269536574649</v>
       </c>
     </row>
     <row r="265">
@@ -6123,16 +6123,16 @@
         </is>
       </c>
       <c r="B265" s="18" t="n">
-        <v>0.959087647158345</v>
+        <v>0.9896872203242973</v>
       </c>
       <c r="C265" s="18" t="n">
-        <v>0.8558577777367269</v>
+        <v>0.9020897724978332</v>
       </c>
       <c r="D265" s="18" t="n">
-        <v>1.074768657666727</v>
+        <v>1.085790820309502</v>
       </c>
       <c r="E265" s="18" t="n">
-        <v>0.4721693311377841</v>
+        <v>0.8264666665097463</v>
       </c>
     </row>
     <row r="266">
@@ -6142,16 +6142,16 @@
         </is>
       </c>
       <c r="B266" s="18" t="n">
-        <v>1.05396825090431</v>
+        <v>1.056396758774761</v>
       </c>
       <c r="C266" s="18" t="n">
-        <v>0.9751068751851637</v>
+        <v>0.9897420624996792</v>
       </c>
       <c r="D266" s="18" t="n">
-        <v>1.139207508616274</v>
+        <v>1.127540350393245</v>
       </c>
       <c r="E266" s="18" t="n">
-        <v>0.1852806869483936</v>
+        <v>0.09896551303985371</v>
       </c>
     </row>
     <row r="267">
@@ -6177,14 +6177,14 @@
         <is>
           <t>{
   "n_obs": 3750,
-  "n_events": 139,
-  "llf": -482.8453480017321,
-  "aic": 1025.6906960034642,
-  "pseudo_r2_mcfadden": 0.18798759596132864,
-  "lr_vs_null_chi2": 223.56539318981618,
+  "n_events": 215,
+  "llf": -692.5012069707084,
+  "aic": 1443.0024139414168,
+  "pseudo_r2_mcfadden": 0.15930744394648788,
+  "lr_vs_null_chi2": 262.4517046522751,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing')) + C(multifocal_flag_path_fac, Treatment(reference='missing')) + C(bilateral_disease_fac, Treatment(reference='missing')) + C(margin_involved_fac, Treatment(reference='missing')) + C(aggressive_variant_fac, Treatment(reference='missing')) + C(braf_positive_fac, Treatment(reference='missing')) + C(surg_tt_fac, Treatment(reference='missing'))",
-  "change_note": "coefficient strengthened vs primary"
+  "change_note": "coefficient attenuated vs primary"
 }</t>
         </is>
       </c>
@@ -6200,16 +6200,16 @@
         </is>
       </c>
       <c r="B270" s="18" t="n">
-        <v>0.1463789671726385</v>
+        <v>0.3076166732608049</v>
       </c>
       <c r="C270" s="18" t="n">
-        <v>0.07044512056190044</v>
+        <v>0.1872093476955183</v>
       </c>
       <c r="D270" s="18" t="n">
-        <v>0.3041630401029772</v>
+        <v>0.5054663072805001</v>
       </c>
       <c r="E270" s="18" t="n">
-        <v>2.611485682955128e-07</v>
+        <v>3.277863622799974e-06</v>
       </c>
     </row>
     <row r="271">
@@ -6219,16 +6219,16 @@
         </is>
       </c>
       <c r="B271" s="18" t="n">
-        <v>2.093308999756993</v>
+        <v>1.173806509403316</v>
       </c>
       <c r="C271" s="18" t="n">
-        <v>0.6572750450418312</v>
+        <v>0.4071753434764451</v>
       </c>
       <c r="D271" s="18" t="n">
-        <v>6.666832403753808</v>
+        <v>3.383853525495468</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.211325654944455</v>
+        <v>0.7667295361533636</v>
       </c>
     </row>
     <row r="272">
@@ -6238,16 +6238,16 @@
         </is>
       </c>
       <c r="B272" s="18" t="n">
-        <v>2.199961647532628</v>
+        <v>1.870441201518156</v>
       </c>
       <c r="C272" s="18" t="n">
-        <v>1.450525328321081</v>
+        <v>1.339006685874726</v>
       </c>
       <c r="D272" s="18" t="n">
-        <v>3.336605818676991</v>
+        <v>2.612795234888017</v>
       </c>
       <c r="E272" s="18" t="n">
-        <v>0.0002071680705361463</v>
+        <v>0.0002408660068691799</v>
       </c>
     </row>
     <row r="273">
@@ -6257,16 +6257,16 @@
         </is>
       </c>
       <c r="B273" s="18" t="n">
-        <v>1.475828424465192</v>
+        <v>1.187745388647448</v>
       </c>
       <c r="C273" s="18" t="n">
-        <v>0.992609771691925</v>
+        <v>0.8533434324723265</v>
       </c>
       <c r="D273" s="18" t="n">
-        <v>2.194285811580159</v>
+        <v>1.653190327094978</v>
       </c>
       <c r="E273" s="18" t="n">
-        <v>0.05444114111128693</v>
+        <v>0.3077826675318844</v>
       </c>
     </row>
     <row r="274">
@@ -6276,16 +6276,16 @@
         </is>
       </c>
       <c r="B274" s="18" t="n">
-        <v>0.976008739844279</v>
+        <v>0.8440719698135348</v>
       </c>
       <c r="C274" s="18" t="n">
-        <v>0.6141139225885103</v>
+        <v>0.5853428001752655</v>
       </c>
       <c r="D274" s="18" t="n">
-        <v>1.551166689459191</v>
+        <v>1.217162814698625</v>
       </c>
       <c r="E274" s="18" t="n">
-        <v>0.9181749364676639</v>
+        <v>0.3640459512977414</v>
       </c>
     </row>
     <row r="275">
@@ -6295,16 +6295,16 @@
         </is>
       </c>
       <c r="B275" s="18" t="n">
-        <v>3.052647630201212</v>
+        <v>3.718896508163191</v>
       </c>
       <c r="C275" s="18" t="n">
-        <v>1.3895339265004</v>
+        <v>1.954329671179818</v>
       </c>
       <c r="D275" s="18" t="n">
-        <v>6.706318842924914</v>
+        <v>7.076693068922792</v>
       </c>
       <c r="E275" s="18" t="n">
-        <v>0.005449425522714218</v>
+        <v>6.30309176914805e-05</v>
       </c>
     </row>
     <row r="276">
@@ -6314,16 +6314,16 @@
         </is>
       </c>
       <c r="B276" s="18" t="n">
-        <v>0.5414019352890191</v>
+        <v>0.5310768730556535</v>
       </c>
       <c r="C276" s="18" t="n">
-        <v>0.1177688846657347</v>
+        <v>0.1816048982370952</v>
       </c>
       <c r="D276" s="18" t="n">
-        <v>2.488909157683298</v>
+        <v>1.55305637586024</v>
       </c>
       <c r="E276" s="18" t="n">
-        <v>0.4304759499465243</v>
+        <v>0.2477240500761266</v>
       </c>
     </row>
     <row r="277">
@@ -6333,16 +6333,16 @@
         </is>
       </c>
       <c r="B277" s="18" t="n">
-        <v>1.000000000112971</v>
+        <v>1.000000000238257</v>
       </c>
       <c r="C277" s="18" t="n">
-        <v>0.9999996516921731</v>
+        <v>0.9999995722011328</v>
       </c>
       <c r="D277" s="18" t="n">
-        <v>1.00000034853389</v>
+        <v>1.000000428275565</v>
       </c>
       <c r="E277" s="18" t="n">
-        <v>0.9994929514623558</v>
+        <v>0.9991295317109123</v>
       </c>
     </row>
     <row r="278">
@@ -6352,16 +6352,16 @@
         </is>
       </c>
       <c r="B278" s="18" t="n">
-        <v>0.3435658888541995</v>
+        <v>0.594909916961759</v>
       </c>
       <c r="C278" s="18" t="n">
-        <v>0.1497586256161338</v>
+        <v>0.3155113262344381</v>
       </c>
       <c r="D278" s="18" t="n">
-        <v>0.78818511787584</v>
+        <v>1.121727747537251</v>
       </c>
       <c r="E278" s="18" t="n">
-        <v>0.01167591467733043</v>
+        <v>0.1084999412489136</v>
       </c>
     </row>
     <row r="279">
@@ -6371,16 +6371,16 @@
         </is>
       </c>
       <c r="B279" s="18" t="n">
-        <v>10.10131361815434</v>
+        <v>9.156536818855699</v>
       </c>
       <c r="C279" s="18" t="n">
-        <v>5.137229794782425</v>
+        <v>5.014044369803462</v>
       </c>
       <c r="D279" s="18" t="n">
-        <v>19.86217103154362</v>
+        <v>16.72146481590598</v>
       </c>
       <c r="E279" s="18" t="n">
-        <v>2.031572870659635e-11</v>
+        <v>5.716963364311959e-13</v>
       </c>
     </row>
     <row r="280">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="B280" s="18" t="n">
-        <v>1.9406684042337</v>
+        <v>1.901910747509941</v>
       </c>
       <c r="C280" s="18" t="n">
-        <v>0.6016227151100951</v>
+        <v>0.6708427995488256</v>
       </c>
       <c r="D280" s="18" t="n">
-        <v>6.260059270703858</v>
+        <v>5.392119426379191</v>
       </c>
       <c r="E280" s="18" t="n">
-        <v>0.267170070765159</v>
+        <v>0.2266235978042084</v>
       </c>
     </row>
     <row r="281">
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="B281" s="18" t="n">
-        <v>4.262249092246015e-10</v>
+        <v>4.984180923952849e-10</v>
       </c>
       <c r="C281" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6418,7 +6418,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E281" s="18" t="n">
-        <v>0.999191024953179</v>
+        <v>0.9992109595712718</v>
       </c>
     </row>
     <row r="282">
@@ -6428,16 +6428,16 @@
         </is>
       </c>
       <c r="B282" s="18" t="n">
-        <v>0.6578623546294411</v>
+        <v>0.759069893167616</v>
       </c>
       <c r="C282" s="18" t="n">
-        <v>0.3619097025163545</v>
+        <v>0.4639935552223378</v>
       </c>
       <c r="D282" s="18" t="n">
-        <v>1.195831099938624</v>
+        <v>1.241799797062692</v>
       </c>
       <c r="E282" s="18" t="n">
-        <v>0.169623630460519</v>
+        <v>0.2723594243483669</v>
       </c>
     </row>
     <row r="283">
@@ -6447,16 +6447,16 @@
         </is>
       </c>
       <c r="B283" s="18" t="n">
-        <v>1.444777986852777</v>
+        <v>1.53823348180424</v>
       </c>
       <c r="C283" s="18" t="n">
-        <v>0.5347829379559831</v>
+        <v>0.6309071320044761</v>
       </c>
       <c r="D283" s="18" t="n">
-        <v>3.903234907367538</v>
+        <v>3.750412896785588</v>
       </c>
       <c r="E283" s="18" t="n">
-        <v>0.4680579267732285</v>
+        <v>0.3436202393795618</v>
       </c>
     </row>
     <row r="284">
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="B284" s="18" t="n">
-        <v>1.022957930683029e-09</v>
+        <v>4.578261552235781e-10</v>
       </c>
       <c r="C284" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -6475,7 +6475,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E284" s="18" t="n">
-        <v>0.9994819302728273</v>
+        <v>0.999455339280243</v>
       </c>
     </row>
     <row r="285">
@@ -6485,16 +6485,16 @@
         </is>
       </c>
       <c r="B285" s="18" t="n">
-        <v>0.9395186960457329</v>
+        <v>0.6287065683863695</v>
       </c>
       <c r="C285" s="18" t="n">
-        <v>0.3464732630371267</v>
+        <v>0.2541006413792519</v>
       </c>
       <c r="D285" s="18" t="n">
-        <v>2.54765799958679</v>
+        <v>1.555572418025545</v>
       </c>
       <c r="E285" s="18" t="n">
-        <v>0.9024426987503433</v>
+        <v>0.3153557534299571</v>
       </c>
     </row>
     <row r="286">
@@ -6504,16 +6504,16 @@
         </is>
       </c>
       <c r="B286" s="18" t="n">
-        <v>1.594399132813267</v>
+        <v>1.657393847622531</v>
       </c>
       <c r="C286" s="18" t="n">
-        <v>0.9061443340040335</v>
+        <v>1.025768142527177</v>
       </c>
       <c r="D286" s="18" t="n">
-        <v>2.805412448459213</v>
+        <v>2.677948604807874</v>
       </c>
       <c r="E286" s="18" t="n">
-        <v>0.1056395436455627</v>
+        <v>0.03902800748676825</v>
       </c>
     </row>
     <row r="287">
@@ -6523,16 +6523,16 @@
         </is>
       </c>
       <c r="B287" s="18" t="n">
-        <v>2.048908823020549</v>
+        <v>1.857599136282107</v>
       </c>
       <c r="C287" s="18" t="n">
-        <v>1.016246174513079</v>
+        <v>1.019720951607372</v>
       </c>
       <c r="D287" s="18" t="n">
-        <v>4.130915786288577</v>
+        <v>3.383940033473646</v>
       </c>
       <c r="E287" s="18" t="n">
-        <v>0.04496195733039759</v>
+        <v>0.04299242679453086</v>
       </c>
     </row>
     <row r="288">
@@ -6542,16 +6542,16 @@
         </is>
       </c>
       <c r="B288" s="18" t="n">
-        <v>2.354088735909698</v>
+        <v>1.963291119160643</v>
       </c>
       <c r="C288" s="18" t="n">
-        <v>0.9999723934118724</v>
+        <v>0.9483411458027879</v>
       </c>
       <c r="D288" s="18" t="n">
-        <v>5.541886769122407</v>
+        <v>4.064478311032403</v>
       </c>
       <c r="E288" s="18" t="n">
-        <v>0.050007387642182</v>
+        <v>0.06920212963968421</v>
       </c>
     </row>
     <row r="289">
@@ -6561,16 +6561,16 @@
         </is>
       </c>
       <c r="B289" s="18" t="n">
-        <v>0.9535346602554323</v>
+        <v>1.120256487887755</v>
       </c>
       <c r="C289" s="18" t="n">
-        <v>0.2001618907267474</v>
+        <v>0.3009294364518659</v>
       </c>
       <c r="D289" s="18" t="n">
-        <v>4.542464826881971</v>
+        <v>4.170328477836836</v>
       </c>
       <c r="E289" s="18" t="n">
-        <v>0.9523642284288786</v>
+        <v>0.8655398953576504</v>
       </c>
     </row>
     <row r="290">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="B290" s="18" t="n">
-        <v>0.2843336818833474</v>
+        <v>0.4418308774845732</v>
       </c>
       <c r="C290" s="18" t="n">
-        <v>0.1897996633188375</v>
+        <v>0.3317109346512437</v>
       </c>
       <c r="D290" s="18" t="n">
-        <v>0.4259525082377567</v>
+        <v>0.5885079564954161</v>
       </c>
       <c r="E290" s="18" t="n">
-        <v>1.071079693311093e-09</v>
+        <v>2.339850905544589e-08</v>
       </c>
     </row>
     <row r="291">
@@ -6599,16 +6599,16 @@
         </is>
       </c>
       <c r="B291" s="18" t="n">
-        <v>0.5148140249233055</v>
+        <v>0.6962317234118087</v>
       </c>
       <c r="C291" s="18" t="n">
-        <v>0.3377993029735788</v>
+        <v>0.5155026456390776</v>
       </c>
       <c r="D291" s="18" t="n">
-        <v>0.7845885942472286</v>
+        <v>0.9403222598092364</v>
       </c>
       <c r="E291" s="18" t="n">
-        <v>0.002012241988471714</v>
+        <v>0.01821357789435867</v>
       </c>
     </row>
     <row r="292">
@@ -6618,16 +6618,16 @@
         </is>
       </c>
       <c r="B292" s="18" t="n">
-        <v>1.098659013378303</v>
+        <v>1.599216412402652</v>
       </c>
       <c r="C292" s="18" t="n">
-        <v>0.662204090850441</v>
+        <v>1.072566648162998</v>
       </c>
       <c r="D292" s="18" t="n">
-        <v>1.822778874904292</v>
+        <v>2.38446080537584</v>
       </c>
       <c r="E292" s="18" t="n">
-        <v>0.7156651441260911</v>
+        <v>0.02124008196438381</v>
       </c>
     </row>
     <row r="293">
@@ -6637,16 +6637,16 @@
         </is>
       </c>
       <c r="B293" s="18" t="n">
-        <v>0.9574102607560763</v>
+        <v>1.272098937908265</v>
       </c>
       <c r="C293" s="18" t="n">
-        <v>0.5958349680857699</v>
+        <v>0.870862954709051</v>
       </c>
       <c r="D293" s="18" t="n">
-        <v>1.538403176211486</v>
+        <v>1.858197893339</v>
       </c>
       <c r="E293" s="18" t="n">
-        <v>0.8572588688161686</v>
+        <v>0.2132072691097866</v>
       </c>
     </row>
     <row r="294">
@@ -6656,16 +6656,16 @@
         </is>
       </c>
       <c r="B294" s="18" t="n">
-        <v>5.723885031437849</v>
+        <v>0.8137811038546567</v>
       </c>
       <c r="C294" s="18" t="n">
-        <v>1.404292478787422</v>
+        <v>0.2571284769280714</v>
       </c>
       <c r="D294" s="18" t="n">
-        <v>23.3305100953103</v>
+        <v>2.5755205837281</v>
       </c>
       <c r="E294" s="18" t="n">
-        <v>0.01495065296067126</v>
+        <v>0.7259235983748754</v>
       </c>
     </row>
     <row r="295">
@@ -6675,16 +6675,16 @@
         </is>
       </c>
       <c r="B295" s="18" t="n">
-        <v>8.250115762030385</v>
+        <v>1.403643122554928</v>
       </c>
       <c r="C295" s="18" t="n">
-        <v>1.996676019868637</v>
+        <v>0.4388029424366672</v>
       </c>
       <c r="D295" s="18" t="n">
-        <v>34.08886039077096</v>
+        <v>4.489974485027775</v>
       </c>
       <c r="E295" s="18" t="n">
-        <v>0.003554216972992647</v>
+        <v>0.567637055850553</v>
       </c>
     </row>
     <row r="296">
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="B296" s="18" t="n">
-        <v>0.424478889728311</v>
+        <v>0.6447629960918444</v>
       </c>
       <c r="C296" s="18" t="n">
-        <v>0.2109388341574736</v>
+        <v>0.3597664077578708</v>
       </c>
       <c r="D296" s="18" t="n">
-        <v>0.8541922996050454</v>
+        <v>1.155525674896024</v>
       </c>
       <c r="E296" s="18" t="n">
-        <v>0.0163200512682219</v>
+        <v>0.1403885774374216</v>
       </c>
     </row>
     <row r="297">
@@ -6713,16 +6713,16 @@
         </is>
       </c>
       <c r="B297" s="18" t="n">
-        <v>0.3448439267706367</v>
+        <v>0.4771003841672524</v>
       </c>
       <c r="C297" s="18" t="n">
-        <v>0.1259550210905915</v>
+        <v>0.2148535435281506</v>
       </c>
       <c r="D297" s="18" t="n">
-        <v>0.9441253933422994</v>
+        <v>1.059441575105862</v>
       </c>
       <c r="E297" s="18" t="n">
-        <v>0.03827917759056433</v>
+        <v>0.0690483277336532</v>
       </c>
     </row>
     <row r="298">
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="B298" s="18" t="n">
-        <v>0.3540546708441215</v>
+        <v>0.4677471960638356</v>
       </c>
       <c r="C298" s="18" t="n">
-        <v>0.2292062829498153</v>
+        <v>0.3400377880038166</v>
       </c>
       <c r="D298" s="18" t="n">
-        <v>0.5469078261436036</v>
+        <v>0.6434209583292683</v>
       </c>
       <c r="E298" s="18" t="n">
-        <v>2.867498261127365e-06</v>
+        <v>3.007146810629077e-06</v>
       </c>
     </row>
     <row r="299">
@@ -6751,16 +6751,16 @@
         </is>
       </c>
       <c r="B299" s="18" t="n">
-        <v>0.4134360572081573</v>
+        <v>0.6576558360033636</v>
       </c>
       <c r="C299" s="18" t="n">
-        <v>0.2491167900185005</v>
+        <v>0.4487620409220731</v>
       </c>
       <c r="D299" s="18" t="n">
-        <v>0.6861415217622739</v>
+        <v>0.9637873955216905</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0.0006324392680220307</v>
+        <v>0.03162508554259304</v>
       </c>
     </row>
     <row r="300">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="B300" s="18" t="n">
-        <v>0.3260262786148044</v>
+        <v>0.4504886204839262</v>
       </c>
       <c r="C300" s="18" t="n">
-        <v>0.1881836841994529</v>
+        <v>0.3276638249241812</v>
       </c>
       <c r="D300" s="18" t="n">
-        <v>0.5648371419636977</v>
+        <v>0.6193542947027174</v>
       </c>
       <c r="E300" s="18" t="n">
-        <v>6.410399541474762e-05</v>
+        <v>9.129982314047644e-07</v>
       </c>
     </row>
     <row r="301">
@@ -6789,16 +6789,16 @@
         </is>
       </c>
       <c r="B301" s="18" t="n">
-        <v>0.2447286890935103</v>
+        <v>0.6828511516105249</v>
       </c>
       <c r="C301" s="18" t="n">
-        <v>0.1533275886790415</v>
+        <v>0.4992524917151053</v>
       </c>
       <c r="D301" s="18" t="n">
-        <v>0.3906154905416231</v>
+        <v>0.93396768768037</v>
       </c>
       <c r="E301" s="18" t="n">
-        <v>3.626930764974026e-09</v>
+        <v>0.0169630217087995</v>
       </c>
     </row>
     <row r="302">
@@ -6808,16 +6808,16 @@
         </is>
       </c>
       <c r="B302" s="18" t="n">
-        <v>0.9493423572173416</v>
+        <v>0.9781708205691213</v>
       </c>
       <c r="C302" s="18" t="n">
-        <v>0.8434409722473438</v>
+        <v>0.8891641960314445</v>
       </c>
       <c r="D302" s="18" t="n">
-        <v>1.068540586551778</v>
+        <v>1.076087137205231</v>
       </c>
       <c r="E302" s="18" t="n">
-        <v>0.3889979726396278</v>
+        <v>0.6502393072970469</v>
       </c>
     </row>
     <row r="303">
@@ -6827,16 +6827,16 @@
         </is>
       </c>
       <c r="B303" s="18" t="n">
-        <v>1.053002798541731</v>
+        <v>1.058479783810605</v>
       </c>
       <c r="C303" s="18" t="n">
-        <v>0.970199155124861</v>
+        <v>0.9894006954475709</v>
       </c>
       <c r="D303" s="18" t="n">
-        <v>1.142873489303354</v>
+        <v>1.132381913506665</v>
       </c>
       <c r="E303" s="18" t="n">
-        <v>0.2164770490037656</v>
+        <v>0.0988393154008456</v>
       </c>
     </row>
     <row r="304">
@@ -6863,10 +6863,10 @@
           <t>{
   "n_obs": 3750,
   "n_events": 470,
-  "llf": -1257.2160427331455,
-  "aic": 2556.432085466291,
-  "pseudo_r2_mcfadden": 0.1122116624090379,
-  "lr_vs_null_chi2": 317.8106676760526,
+  "llf": -1257.2160427331457,
+  "aic": 2556.4320854662915,
+  "pseudo_r2_mcfadden": 0.11221166240903802,
+  "lr_vs_null_chi2": 317.8106676760531,
   "lr_vs_null_pvalue": 0.0
 }</t>
         </is>
@@ -6883,16 +6883,16 @@
         </is>
       </c>
       <c r="B307" s="18" t="n">
-        <v>0.2121465789650934</v>
+        <v>0.2121465789650938</v>
       </c>
       <c r="C307" s="18" t="n">
-        <v>0.1447620495987534</v>
+        <v>0.1447620495987536</v>
       </c>
       <c r="D307" s="18" t="n">
-        <v>0.3108975804870076</v>
+        <v>0.3108975804870083</v>
       </c>
       <c r="E307" s="18" t="n">
-        <v>1.845469936714709e-15</v>
+        <v>1.845469936715041e-15</v>
       </c>
     </row>
     <row r="308">
@@ -6902,16 +6902,16 @@
         </is>
       </c>
       <c r="B308" s="18" t="n">
-        <v>0.1481709302516656</v>
+        <v>0.1481709302516655</v>
       </c>
       <c r="C308" s="18" t="n">
-        <v>0.07281506778999987</v>
+        <v>0.0728150677899998</v>
       </c>
       <c r="D308" s="18" t="n">
         <v>0.301512107836822</v>
       </c>
       <c r="E308" s="18" t="n">
-        <v>1.382185754473282e-07</v>
+        <v>1.382185754473308e-07</v>
       </c>
     </row>
     <row r="309">
@@ -6930,7 +6930,7 @@
         <v>1.591594309401872</v>
       </c>
       <c r="E309" s="18" t="n">
-        <v>0.0421913482707998</v>
+        <v>0.04219134827079978</v>
       </c>
     </row>
     <row r="310">
@@ -6943,13 +6943,13 @@
         <v>1.000927484046316</v>
       </c>
       <c r="C310" s="18" t="n">
-        <v>0.7871210841082437</v>
+        <v>0.7871210841082436</v>
       </c>
       <c r="D310" s="18" t="n">
-        <v>1.272810306503636</v>
+        <v>1.272810306503635</v>
       </c>
       <c r="E310" s="18" t="n">
-        <v>0.9939669776747911</v>
+        <v>0.9939669776747947</v>
       </c>
     </row>
     <row r="311">
@@ -6959,16 +6959,16 @@
         </is>
       </c>
       <c r="B311" s="18" t="n">
-        <v>0.8684486853414533</v>
+        <v>0.868448685341453</v>
       </c>
       <c r="C311" s="18" t="n">
-        <v>0.6845751774163158</v>
+        <v>0.6845751774163154</v>
       </c>
       <c r="D311" s="18" t="n">
         <v>1.101709708373839</v>
       </c>
       <c r="E311" s="18" t="n">
-        <v>0.2452437467003598</v>
+        <v>0.2452437467003592</v>
       </c>
     </row>
     <row r="312">
@@ -6978,16 +6978,16 @@
         </is>
       </c>
       <c r="B312" s="18" t="n">
-        <v>2.773620309514962</v>
+        <v>2.773620309514969</v>
       </c>
       <c r="C312" s="18" t="n">
-        <v>1.549815930104469</v>
+        <v>1.549815930104473</v>
       </c>
       <c r="D312" s="18" t="n">
-        <v>4.963795681746096</v>
+        <v>4.963795681746108</v>
       </c>
       <c r="E312" s="18" t="n">
-        <v>0.0005916727631447622</v>
+        <v>0.0005916727631447432</v>
       </c>
     </row>
     <row r="313">
@@ -6997,16 +6997,16 @@
         </is>
       </c>
       <c r="B313" s="18" t="n">
-        <v>0.6926461139556235</v>
+        <v>0.6926461139556217</v>
       </c>
       <c r="C313" s="18" t="n">
-        <v>0.3940886371243371</v>
+        <v>0.394088637124336</v>
       </c>
       <c r="D313" s="18" t="n">
-        <v>1.217387648318467</v>
+        <v>1.217387648318464</v>
       </c>
       <c r="E313" s="18" t="n">
-        <v>0.201844127802193</v>
+        <v>0.20184412780219</v>
       </c>
     </row>
     <row r="314">
@@ -7016,16 +7016,16 @@
         </is>
       </c>
       <c r="B314" s="18" t="n">
-        <v>0.9999999999251061</v>
+        <v>1.000000000027197</v>
       </c>
       <c r="C314" s="18" t="n">
-        <v>0.9999999135824486</v>
+        <v>0.999999968673107</v>
       </c>
       <c r="D314" s="18" t="n">
-        <v>1.000000086267771</v>
+        <v>1.000000031381287</v>
       </c>
       <c r="E314" s="18" t="n">
-        <v>0.9986435339361804</v>
+        <v>0.998643529701507</v>
       </c>
     </row>
     <row r="315">
@@ -7035,16 +7035,16 @@
         </is>
       </c>
       <c r="B315" s="18" t="n">
-        <v>1.071424148750147</v>
+        <v>1.071424148750146</v>
       </c>
       <c r="C315" s="18" t="n">
-        <v>0.7691735683880996</v>
+        <v>0.7691735683880994</v>
       </c>
       <c r="D315" s="18" t="n">
         <v>1.492445598372094</v>
       </c>
       <c r="E315" s="18" t="n">
-        <v>0.6832889925151029</v>
+        <v>0.6832889925151044</v>
       </c>
     </row>
     <row r="316">
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B316" s="18" t="n">
-        <v>15.11279260106013</v>
+        <v>15.11279260106012</v>
       </c>
       <c r="C316" s="18" t="n">
-        <v>8.440112611810518</v>
+        <v>8.440112611810511</v>
       </c>
       <c r="D316" s="18" t="n">
-        <v>27.06083564371587</v>
+        <v>27.06083564371585</v>
       </c>
       <c r="E316" s="18" t="n">
         <v>6.457500862694149e-20</v>
@@ -7073,16 +7073,16 @@
         </is>
       </c>
       <c r="B317" s="18" t="n">
-        <v>1.321481870785392</v>
+        <v>1.321481870785394</v>
       </c>
       <c r="C317" s="18" t="n">
-        <v>0.5617281025374775</v>
+        <v>0.561728102537479</v>
       </c>
       <c r="D317" s="18" t="n">
-        <v>3.108824940261823</v>
+        <v>3.108824940261825</v>
       </c>
       <c r="E317" s="18" t="n">
-        <v>0.5230598484323481</v>
+        <v>0.5230598484323455</v>
       </c>
     </row>
     <row r="318">
@@ -7092,16 +7092,16 @@
         </is>
       </c>
       <c r="B318" s="18" t="n">
-        <v>0.3479305781815172</v>
+        <v>0.3479305781815146</v>
       </c>
       <c r="C318" s="18" t="n">
-        <v>0.04221587777756861</v>
+        <v>0.04221587777756792</v>
       </c>
       <c r="D318" s="18" t="n">
-        <v>2.867539267371286</v>
+        <v>2.86753926737129</v>
       </c>
       <c r="E318" s="18" t="n">
-        <v>0.3265682275253251</v>
+        <v>0.3265682275253238</v>
       </c>
     </row>
     <row r="319">
@@ -7111,16 +7111,16 @@
         </is>
       </c>
       <c r="B319" s="18" t="n">
-        <v>0.5839324058902096</v>
+        <v>0.5839324058902089</v>
       </c>
       <c r="C319" s="18" t="n">
-        <v>0.4060018849379348</v>
+        <v>0.4060018849379343</v>
       </c>
       <c r="D319" s="18" t="n">
-        <v>0.839841063055294</v>
+        <v>0.8398410630552934</v>
       </c>
       <c r="E319" s="18" t="n">
-        <v>0.003716508413346229</v>
+        <v>0.003716508413346185</v>
       </c>
     </row>
     <row r="320">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="B320" s="18" t="n">
-        <v>1.251285385774943</v>
+        <v>1.251285385774938</v>
       </c>
       <c r="C320" s="18" t="n">
-        <v>0.6170159457505983</v>
+        <v>0.6170159457505956</v>
       </c>
       <c r="D320" s="18" t="n">
-        <v>2.537560216129033</v>
+        <v>2.537560216129026</v>
       </c>
       <c r="E320" s="18" t="n">
-        <v>0.5343195291870251</v>
+        <v>0.5343195291870322</v>
       </c>
     </row>
     <row r="321">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="B321" s="18" t="n">
-        <v>2.014726208855371e-09</v>
+        <v>2.01472617828268e-09</v>
       </c>
       <c r="C321" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7158,7 +7158,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E321" s="18" t="n">
-        <v>0.998643525897418</v>
+        <v>0.9986435259058022</v>
       </c>
     </row>
     <row r="322">
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="B322" s="18" t="n">
-        <v>0.772901305005239</v>
+        <v>0.7729013050052385</v>
       </c>
       <c r="C322" s="18" t="n">
-        <v>0.4448679420783672</v>
+        <v>0.4448679420783668</v>
       </c>
       <c r="D322" s="18" t="n">
-        <v>1.342817431366113</v>
+        <v>1.342817431366112</v>
       </c>
       <c r="E322" s="18" t="n">
-        <v>0.3606933796773957</v>
+        <v>0.3606933796773942</v>
       </c>
     </row>
     <row r="323">
@@ -7187,16 +7187,16 @@
         </is>
       </c>
       <c r="B323" s="18" t="n">
-        <v>1.947800313575636</v>
+        <v>1.947800313575637</v>
       </c>
       <c r="C323" s="18" t="n">
-        <v>1.379229957871423</v>
+        <v>1.379229957871424</v>
       </c>
       <c r="D323" s="18" t="n">
-        <v>2.750756710230209</v>
+        <v>2.750756710230211</v>
       </c>
       <c r="E323" s="18" t="n">
-        <v>0.0001533139669903169</v>
+        <v>0.0001533139669903146</v>
       </c>
     </row>
     <row r="324">
@@ -7206,16 +7206,16 @@
         </is>
       </c>
       <c r="B324" s="18" t="n">
-        <v>2.102017488094825</v>
+        <v>2.102017488094829</v>
       </c>
       <c r="C324" s="18" t="n">
-        <v>1.416008527883009</v>
+        <v>1.416008527883012</v>
       </c>
       <c r="D324" s="18" t="n">
-        <v>3.120374936485927</v>
+        <v>3.120374936485933</v>
       </c>
       <c r="E324" s="18" t="n">
-        <v>0.0002280835182906519</v>
+        <v>0.0002280835182906418</v>
       </c>
     </row>
     <row r="325">
@@ -7225,16 +7225,16 @@
         </is>
       </c>
       <c r="B325" s="18" t="n">
-        <v>1.925961533572606</v>
+        <v>1.92596153357261</v>
       </c>
       <c r="C325" s="18" t="n">
-        <v>1.16460970811518</v>
+        <v>1.164609708115182</v>
       </c>
       <c r="D325" s="18" t="n">
-        <v>3.185039419604847</v>
+        <v>3.185039419604856</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.01065859349159816</v>
+        <v>0.010658593491598</v>
       </c>
     </row>
     <row r="326">
@@ -7244,16 +7244,16 @@
         </is>
       </c>
       <c r="B326" s="18" t="n">
-        <v>0.828656266207219</v>
+        <v>0.8286562662072231</v>
       </c>
       <c r="C326" s="18" t="n">
-        <v>0.2932358696188968</v>
+        <v>0.2932358696188989</v>
       </c>
       <c r="D326" s="18" t="n">
-        <v>2.341702631458149</v>
+        <v>2.341702631458156</v>
       </c>
       <c r="E326" s="18" t="n">
-        <v>0.7228846063053815</v>
+        <v>0.722884606305388</v>
       </c>
     </row>
     <row r="327">
@@ -7263,16 +7263,16 @@
         </is>
       </c>
       <c r="B327" s="18" t="n">
-        <v>0.8209842993608981</v>
+        <v>0.8209842993608983</v>
       </c>
       <c r="C327" s="18" t="n">
         <v>0.7675122378997297</v>
       </c>
       <c r="D327" s="18" t="n">
-        <v>0.8781817233840126</v>
+        <v>0.8781817233840129</v>
       </c>
       <c r="E327" s="18" t="n">
-        <v>9.451936694501377e-09</v>
+        <v>9.451936694502102e-09</v>
       </c>
     </row>
     <row r="328">
@@ -7291,7 +7291,7 @@
         <v>1.190883108567978</v>
       </c>
       <c r="E328" s="18" t="n">
-        <v>1.702073040213412e-06</v>
+        <v>1.702073040213375e-06</v>
       </c>
     </row>
     <row r="329"/>
@@ -7309,58 +7309,58 @@
   {
     "stratum": "N0",
     "n": 1115,
-    "events": 29,
-    "gross_or": 1.6456763294087673,
+    "events": 48,
+    "gross_or": 1.7421713188935481,
     "gross_ci": [
-      0.7230984843626904,
-      3.7453412498343917
+      0.9150293348882349,
+      3.3170093992079615
     ],
-    "gross_p": 0.23512401713133035,
-    "noneg_or": 1.8260044626521499,
+    "gross_p": 0.09108883680757478,
+    "noneg_or": 2.293075597896284,
     "noneg_ci": [
-      0.18779197285420526,
-      17.755243991255092
+      0.4235269520255555,
+      12.415256390460184
     ],
-    "noneg_p": 0.6038644472897627
+    "noneg_p": 0.335540277757003
   },
   {
     "stratum": "N1a",
     "n": 2372,
-    "events": 92,
-    "gross_or": 1.9512850044893086,
+    "events": 139,
+    "gross_or": 2.2269640252099565,
     "gross_ci": [
-      1.2099148754955298,
-      3.1469264870269864
+      1.4880118984911306,
+      3.3328824686201877
     ],
-    "gross_p": 0.006118067426023935,
-    "noneg_or": 0.7178066325740156,
+    "gross_p": 9.944536741874531e-05,
+    "noneg_or": 0.9879226962736362,
     "noneg_ci": [
-      0.25687898360070915,
-      2.0057941468973697
+      0.4391121362608433,
+      2.2226469578440633
     ],
-    "noneg_p": 0.527135184857838
+    "noneg_p": 0.9765689783345083
   },
   {
     "stratum": "N1b",
     "n": 76,
-    "events": 16,
-    "gross_or": 1.241207693829348,
+    "events": 24,
+    "gross_or": 3.5715281270451715,
     "gross_ci": [
-      0.07204442242452243,
-      21.38398070766935
+      0.5662808533458451,
+      22.525595006272308
     ],
-    "gross_p": 0.8817250858670671,
-    "noneg_or": 0.04467295075675648,
+    "gross_p": 0.17549126296160633,
+    "noneg_or": 0.32796964811688367,
     "noneg_ci": [
-      0.0010542234750577167,
-      1.8930260770434177
+      0.020565003775729306,
+      5.230443488313822
     ],
-    "noneg_p": 0.10392614431984755
+    "noneg_p": 0.43010497656729707
   },
   {
     "stratum": "Nx",
     "n": 193,
-    "events": 2,
+    "events": 4,
     "note": "skipped_sparse_events_for_stable_GLMs"
   },
   {
@@ -7386,13 +7386,13 @@
         <is>
           <t>{
   "n_obs": 192,
-  "n_events": 29,
-  "llf": -54.05824166134959,
-  "aic": 130.1164833226992,
-  "pseudo_r2_mcfadden": 0.3367595502439821,
-  "lr_vs_null_chi2": 54.89601593374893,
-  "lr_vs_null_pvalue": 3.302489481882276e-08,
-  "events": 29,
+  "n_events": 25,
+  "llf": -50.76913286348494,
+  "aic": 123.53826572696988,
+  "pseudo_r2_mcfadden": 0.3163534170389164,
+  "lr_vs_null_chi2": 46.986232541091994,
+  "lr_vs_null_pvalue": 9.497317765561064e-07,
+  "events": 25,
   "formula": "y_comp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + rai_received_flag + ge2 + days_per_100"
 }</t>
         </is>
@@ -7405,16 +7405,16 @@
         </is>
       </c>
       <c r="B335" s="18" t="n">
-        <v>0.01652051389901669</v>
+        <v>0.02189189522595962</v>
       </c>
       <c r="C335" s="18" t="n">
-        <v>0.00204712285400636</v>
+        <v>0.002919882348109686</v>
       </c>
       <c r="D335" s="18" t="n">
-        <v>0.1333224232016492</v>
+        <v>0.1641350641729317</v>
       </c>
       <c r="E335" s="18" t="n">
-        <v>0.0001175220550730235</v>
+        <v>0.0002007702298282295</v>
       </c>
     </row>
     <row r="336">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="B336" s="18" t="n">
-        <v>0.9137041746177371</v>
+        <v>0.713938991900435</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>0.103182513496247</v>
+        <v>0.0804701851183153</v>
       </c>
       <c r="D336" s="18" t="n">
-        <v>8.091054292297756</v>
+        <v>6.334133361398194</v>
       </c>
       <c r="E336" s="18" t="n">
-        <v>0.9353609862144666</v>
+        <v>0.7622379101762229</v>
       </c>
     </row>
     <row r="337">
@@ -7443,16 +7443,16 @@
         </is>
       </c>
       <c r="B337" s="18" t="n">
-        <v>2.030051996958279</v>
+        <v>2.110248850498374</v>
       </c>
       <c r="C337" s="18" t="n">
-        <v>0.1045557549793948</v>
+        <v>0.1117284883516169</v>
       </c>
       <c r="D337" s="18" t="n">
-        <v>39.41544022293616</v>
+        <v>39.85689126138853</v>
       </c>
       <c r="E337" s="18" t="n">
-        <v>0.6398709470246355</v>
+        <v>0.6184013196124551</v>
       </c>
     </row>
     <row r="338">
@@ -7462,16 +7462,16 @@
         </is>
       </c>
       <c r="B338" s="18" t="n">
-        <v>1.796187301528384</v>
+        <v>1.081093800927344</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>0.1911136343597722</v>
+        <v>0.105973500598352</v>
       </c>
       <c r="D338" s="18" t="n">
-        <v>16.8815209494594</v>
+        <v>11.02883079075815</v>
       </c>
       <c r="E338" s="18" t="n">
-        <v>0.6084256719305787</v>
+        <v>0.9475364482141719</v>
       </c>
     </row>
     <row r="339">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="B339" s="18" t="n">
-        <v>3.035829393563344e-09</v>
+        <v>3.040645514937959e-09</v>
       </c>
       <c r="C339" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7490,7 +7490,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E339" s="18" t="n">
-        <v>0.9991222694924246</v>
+        <v>0.9991383315982408</v>
       </c>
     </row>
     <row r="340">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="B340" s="18" t="n">
-        <v>1.055587646281052</v>
+        <v>1.019843474764976</v>
       </c>
       <c r="C340" s="18" t="n">
-        <v>0.9083864295117884</v>
+        <v>0.8653368672411085</v>
       </c>
       <c r="D340" s="18" t="n">
-        <v>1.226642365826659</v>
+        <v>1.201937363811525</v>
       </c>
       <c r="E340" s="18" t="n">
-        <v>0.4801874233652046</v>
+        <v>0.8146597719616457</v>
       </c>
     </row>
     <row r="341">
@@ -7519,16 +7519,16 @@
         </is>
       </c>
       <c r="B341" s="18" t="n">
-        <v>1.36921802700435</v>
+        <v>1.423683579331101</v>
       </c>
       <c r="C341" s="18" t="n">
-        <v>0.4144862618993693</v>
+        <v>0.4171512768475497</v>
       </c>
       <c r="D341" s="18" t="n">
-        <v>4.523088405590743</v>
+        <v>4.858848687637478</v>
       </c>
       <c r="E341" s="18" t="n">
-        <v>0.6062625723199878</v>
+        <v>0.5727474114189575</v>
       </c>
     </row>
     <row r="342">
@@ -7538,16 +7538,16 @@
         </is>
       </c>
       <c r="B342" s="18" t="n">
-        <v>4.796367595255639</v>
+        <v>4.787340098009687</v>
       </c>
       <c r="C342" s="18" t="n">
-        <v>1.294072005033071</v>
+        <v>1.227157671653344</v>
       </c>
       <c r="D342" s="18" t="n">
-        <v>17.77732770614295</v>
+        <v>18.67618623378138</v>
       </c>
       <c r="E342" s="18" t="n">
-        <v>0.018994211201836</v>
+        <v>0.02415265670134026</v>
       </c>
     </row>
     <row r="343">
@@ -7557,16 +7557,16 @@
         </is>
       </c>
       <c r="B343" s="18" t="n">
-        <v>15.91850505630185</v>
+        <v>11.10702938789088</v>
       </c>
       <c r="C343" s="18" t="n">
-        <v>5.601241949901238</v>
+        <v>3.856000646325888</v>
       </c>
       <c r="D343" s="18" t="n">
-        <v>45.23975316438092</v>
+        <v>31.99327830533911</v>
       </c>
       <c r="E343" s="18" t="n">
-        <v>2.068165598651878e-07</v>
+        <v>8.184404216167702e-06</v>
       </c>
     </row>
     <row r="344">
@@ -7576,16 +7576,16 @@
         </is>
       </c>
       <c r="B344" s="18" t="n">
-        <v>3.31101568344958</v>
+        <v>2.359810708189639</v>
       </c>
       <c r="C344" s="18" t="n">
-        <v>0.7158630096050405</v>
+        <v>0.4641645183839509</v>
       </c>
       <c r="D344" s="18" t="n">
-        <v>15.31413791319872</v>
+        <v>11.99726898099549</v>
       </c>
       <c r="E344" s="18" t="n">
-        <v>0.1254763905358094</v>
+        <v>0.300732791861349</v>
       </c>
     </row>
     <row r="345">
@@ -7595,16 +7595,16 @@
         </is>
       </c>
       <c r="B345" s="18" t="n">
-        <v>1.03165389352651</v>
+        <v>1.078646964101498</v>
       </c>
       <c r="C345" s="18" t="n">
-        <v>0.896601232573869</v>
+        <v>0.9327891499309621</v>
       </c>
       <c r="D345" s="18" t="n">
-        <v>1.187049177897178</v>
+        <v>1.247312185451009</v>
       </c>
       <c r="E345" s="18" t="n">
-        <v>0.6633289121046677</v>
+        <v>0.3070934650209499</v>
       </c>
     </row>
     <row r="346"/>
@@ -7620,13 +7620,13 @@
         <is>
           <t>{
   "n_obs": 171,
-  "n_events": 11,
-  "llf": -27.093819271894198,
-  "aic": 72.1876385437884,
-  "pseudo_r2_mcfadden": 0.3362580704014553,
-  "lr_vs_null_chi2": 27.451980903732505,
-  "lr_vs_null_pvalue": 0.0005904940071913556,
-  "events": 11,
+  "n_events": 23,
+  "llf": -53.77127960034672,
+  "aic": 125.54255920069345,
+  "pseudo_r2_mcfadden": 0.20363248897160058,
+  "lr_vs_null_chi2": 27.49881015629724,
+  "lr_vs_null_pvalue": 0.0005795575307342427,
+  "events": 23,
   "formula": "y_pp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + ge2 + days_per_100"
 }</t>
         </is>
@@ -7639,16 +7639,16 @@
         </is>
       </c>
       <c r="B349" s="18" t="n">
-        <v>0.01413021552788013</v>
+        <v>0.05500423195487584</v>
       </c>
       <c r="C349" s="18" t="n">
-        <v>0.001068060180277012</v>
+        <v>0.0103820772812532</v>
       </c>
       <c r="D349" s="18" t="n">
-        <v>0.186939832184887</v>
+        <v>0.291412349473533</v>
       </c>
       <c r="E349" s="18" t="n">
-        <v>0.001226273475024972</v>
+        <v>0.0006510879774404757</v>
       </c>
     </row>
     <row r="350">
@@ -7658,16 +7658,16 @@
         </is>
       </c>
       <c r="B350" s="18" t="n">
-        <v>0.5689880035875439</v>
+        <v>0.5560929342658829</v>
       </c>
       <c r="C350" s="18" t="n">
-        <v>0.03005726534141062</v>
+        <v>0.07402177141912585</v>
       </c>
       <c r="D350" s="18" t="n">
-        <v>10.7710180733077</v>
+        <v>4.177681047234947</v>
       </c>
       <c r="E350" s="18" t="n">
-        <v>0.7070453614462671</v>
+        <v>0.5684431747800904</v>
       </c>
     </row>
     <row r="351">
@@ -7677,16 +7677,16 @@
         </is>
       </c>
       <c r="B351" s="18" t="n">
-        <v>0.4799986868471415</v>
+        <v>4.218268766623468</v>
       </c>
       <c r="C351" s="18" t="n">
-        <v>0.001897303751580615</v>
+        <v>0.304009145880805</v>
       </c>
       <c r="D351" s="18" t="n">
-        <v>121.4348199032646</v>
+        <v>58.53044761504511</v>
       </c>
       <c r="E351" s="18" t="n">
-        <v>0.7948794393251363</v>
+        <v>0.2834247538466057</v>
       </c>
     </row>
     <row r="352">
@@ -7696,16 +7696,16 @@
         </is>
       </c>
       <c r="B352" s="18" t="n">
-        <v>0.6528464689608987</v>
+        <v>0.3072213141749107</v>
       </c>
       <c r="C352" s="18" t="n">
-        <v>0.02841986932470952</v>
+        <v>0.02260894619838982</v>
       </c>
       <c r="D352" s="18" t="n">
-        <v>14.99684981535608</v>
+        <v>4.174672054820546</v>
       </c>
       <c r="E352" s="18" t="n">
-        <v>0.7897371772286217</v>
+        <v>0.3753382685222088</v>
       </c>
     </row>
     <row r="353">
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="B353" s="18" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="C353" s="18" t="n">
-        <v>0.9999999999999919</v>
+        <v>0.9999999999999983</v>
       </c>
       <c r="D353" s="18" t="n">
-        <v>1.000000000000008</v>
+        <v>1</v>
       </c>
       <c r="E353" s="18" t="n">
-        <v>0.9760210680852576</v>
+        <v>0.2617501767237684</v>
       </c>
     </row>
     <row r="354">
@@ -7734,16 +7734,16 @@
         </is>
       </c>
       <c r="B354" s="18" t="n">
-        <v>0.9161328106597636</v>
+        <v>1.025924666274582</v>
       </c>
       <c r="C354" s="18" t="n">
-        <v>0.6771543318825255</v>
+        <v>0.8858459944846289</v>
       </c>
       <c r="D354" s="18" t="n">
-        <v>1.239450576110266</v>
+        <v>1.188153953874287</v>
       </c>
       <c r="E354" s="18" t="n">
-        <v>0.5700438043393028</v>
+        <v>0.7325758077557561</v>
       </c>
     </row>
     <row r="355">
@@ -7753,16 +7753,16 @@
         </is>
       </c>
       <c r="B355" s="18" t="n">
-        <v>2.746920567150571</v>
+        <v>1.724460765005128</v>
       </c>
       <c r="C355" s="18" t="n">
-        <v>0.5191680013353923</v>
+        <v>0.5427951324328287</v>
       </c>
       <c r="D355" s="18" t="n">
-        <v>14.53397085880921</v>
+        <v>5.478613849600199</v>
       </c>
       <c r="E355" s="18" t="n">
-        <v>0.2345290624516244</v>
+        <v>0.355519580485365</v>
       </c>
     </row>
     <row r="356">
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="B356" s="18" t="n">
-        <v>4.769593548838072</v>
+        <v>4.850204437151219</v>
       </c>
       <c r="C356" s="18" t="n">
-        <v>0.7207462802354819</v>
+        <v>1.346207961219806</v>
       </c>
       <c r="D356" s="18" t="n">
-        <v>31.56314953673463</v>
+        <v>17.47462781370399</v>
       </c>
       <c r="E356" s="18" t="n">
-        <v>0.1051624795233546</v>
+        <v>0.01575381934340091</v>
       </c>
     </row>
     <row r="357">
@@ -7791,16 +7791,16 @@
         </is>
       </c>
       <c r="B357" s="18" t="n">
-        <v>11.56308962388755</v>
+        <v>3.144653282826895</v>
       </c>
       <c r="C357" s="18" t="n">
-        <v>1.588019908436875</v>
+        <v>0.6455444607144427</v>
       </c>
       <c r="D357" s="18" t="n">
-        <v>84.196073953295</v>
+        <v>15.31861067826327</v>
       </c>
       <c r="E357" s="18" t="n">
-        <v>0.01566868583656499</v>
+        <v>0.1561305634242252</v>
       </c>
     </row>
     <row r="358">
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="B358" s="18" t="n">
-        <v>1.088665125354509</v>
+        <v>1.09766527781081</v>
       </c>
       <c r="C358" s="18" t="n">
-        <v>0.9371042249758985</v>
+        <v>0.9438585982007791</v>
       </c>
       <c r="D358" s="18" t="n">
-        <v>1.264738460861844</v>
+        <v>1.276535557771316</v>
       </c>
       <c r="E358" s="18" t="n">
-        <v>0.2667118841834567</v>
+        <v>0.2263469061098112</v>
       </c>
     </row>
     <row r="359"/>
@@ -7834,21 +7834,21 @@
       <c r="A361" s="18" t="inlineStr">
         <is>
           <t>{
-  "n": 2018,
-  "events": 75,
-  "coef_table_path": "/Users/loganglosser/THYROID_2026/data/m044/m044_cox_primary_summary.csv",
+  "n": 2490,
+  "events": 178,
+  "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 2.336985915027275,
-    "hr_ci_low": 1.34525980475537,
-    "hr_ci_high": 4.059812942994325,
-    "p": 0.0025908850199651574,
+    "hr": 0.9207134290233506,
+    "hr_ci_low": 0.3187748300232398,
+    "hr_ci_high": 2.6592852965277567,
+    "p": 0.8786777742766193,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 1.636551906943798,
-    "hr_ci_low": 0.5754754163628808,
-    "hr_ci_high": 4.654068736852017,
-    "p": 0.3556144639726625,
+    "hr": 2.491912091949067,
+    "hr_ci_low": 0.42177403127977414,
+    "hr_ci_high": 14.722636799521121,
+    "p": 0.31372502440826494,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -7862,16 +7862,16 @@
         </is>
       </c>
       <c r="B362" s="18" t="n">
-        <v>2.336985915027275</v>
+        <v>0.9207134290233506</v>
       </c>
       <c r="C362" s="18" t="n">
-        <v>1.34525980475537</v>
+        <v>0.3187748300232398</v>
       </c>
       <c r="D362" s="18" t="n">
-        <v>4.059812942994325</v>
+        <v>2.659285296527757</v>
       </c>
       <c r="E362" s="18" t="n">
-        <v>0.0025908850199651</v>
+        <v>0.8786777742766193</v>
       </c>
     </row>
     <row r="363">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="B363" s="18" t="n">
-        <v>1.636551906943798</v>
+        <v>2.491912091949067</v>
       </c>
       <c r="C363" s="18" t="n">
-        <v>0.5754754163628808</v>
+        <v>0.4217740312797741</v>
       </c>
       <c r="D363" s="18" t="n">
-        <v>4.654068736852017</v>
+        <v>14.72263679952112</v>
       </c>
       <c r="E363" s="18" t="n">
-        <v>0.3556144639726625</v>
+        <v>0.3137250244082649</v>
       </c>
     </row>
     <row r="364">
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="B364" s="18" t="n">
-        <v>1.158617020926911</v>
+        <v>0.9530274399939724</v>
       </c>
       <c r="C364" s="18" t="n">
-        <v>0.9999632083001412</v>
+        <v>0.7383245610382265</v>
       </c>
       <c r="D364" s="18" t="n">
-        <v>1.342442791933829</v>
+        <v>1.230165362647932</v>
       </c>
       <c r="E364" s="18" t="n">
-        <v>0.0500572658919229</v>
+        <v>0.7118183373326477</v>
       </c>
     </row>
     <row r="365">
@@ -7919,16 +7919,16 @@
         </is>
       </c>
       <c r="B365" s="18" t="n">
-        <v>1.321970007016731</v>
+        <v>1.511125773440816</v>
       </c>
       <c r="C365" s="18" t="n">
-        <v>0.8046282650464566</v>
+        <v>0.7691636205731284</v>
       </c>
       <c r="D365" s="18" t="n">
-        <v>2.171940479061987</v>
+        <v>2.968810591244025</v>
       </c>
       <c r="E365" s="18" t="n">
-        <v>0.2705226219105537</v>
+        <v>0.2308227130393119</v>
       </c>
     </row>
     <row r="366">
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="B366" s="18" t="n">
-        <v>1.043016202186432</v>
+        <v>0.9549538558441968</v>
       </c>
       <c r="C366" s="18" t="n">
-        <v>0.9397772649081764</v>
+        <v>0.7746995301598357</v>
       </c>
       <c r="D366" s="18" t="n">
-        <v>1.157596420604731</v>
+        <v>1.17714911561073</v>
       </c>
       <c r="E366" s="18" t="n">
-        <v>0.4283730261365798</v>
+        <v>0.6658454763304931</v>
       </c>
     </row>
     <row r="367">
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="B367" s="18" t="n">
-        <v>0.8260676260869619</v>
+        <v>0.8495761106162246</v>
       </c>
       <c r="C367" s="18" t="n">
-        <v>0.4531774800447917</v>
+        <v>0.3165938649071141</v>
       </c>
       <c r="D367" s="18" t="n">
-        <v>1.505784715519187</v>
+        <v>2.279828031227185</v>
       </c>
       <c r="E367" s="18" t="n">
-        <v>0.5327783961091432</v>
+        <v>0.746181360222352</v>
       </c>
     </row>
     <row r="368">
@@ -7976,16 +7976,16 @@
         </is>
       </c>
       <c r="B368" s="18" t="n">
-        <v>3.588078269865836</v>
+        <v>1.013909509753326e-121</v>
       </c>
       <c r="C368" s="18" t="n">
-        <v>1.319050158960856</v>
+        <v>6.207002134025062e-133</v>
       </c>
       <c r="D368" s="18" t="n">
-        <v>9.760285143990091</v>
+        <v>1.656214178392097e-110</v>
       </c>
       <c r="E368" s="18" t="n">
-        <v>0.0123382677681206</v>
+        <v>2.83099454212172e-99</v>
       </c>
     </row>
     <row r="369">
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B369" s="18" t="n">
-        <v>0.4819838004331586</v>
+        <v>0.1445514683827354</v>
       </c>
       <c r="C369" s="18" t="n">
-        <v>0.1073871454994997</v>
+        <v>0.0018958169837232</v>
       </c>
       <c r="D369" s="18" t="n">
-        <v>2.163279252832669</v>
+        <v>11.02170050748709</v>
       </c>
       <c r="E369" s="18" t="n">
-        <v>0.3407356845310225</v>
+        <v>0.3817537968799872</v>
       </c>
     </row>
     <row r="370">
@@ -8014,16 +8014,16 @@
         </is>
       </c>
       <c r="B370" s="18" t="n">
-        <v>0.2287495351664525</v>
+        <v>1.493323172693511</v>
       </c>
       <c r="C370" s="18" t="n">
-        <v>0.0649027164141687</v>
+        <v>0.4216881375836718</v>
       </c>
       <c r="D370" s="18" t="n">
-        <v>0.8062274235943206</v>
+        <v>5.288301707706757</v>
       </c>
       <c r="E370" s="18" t="n">
-        <v>0.0217286742916431</v>
+        <v>0.53423387639814</v>
       </c>
     </row>
     <row r="371">
@@ -8033,16 +8033,16 @@
         </is>
       </c>
       <c r="B371" s="18" t="n">
-        <v>0.018349163767719</v>
+        <v>0.0007746695383867</v>
       </c>
       <c r="C371" s="18" t="n">
-        <v>1.540628529751637e-40</v>
+        <v>5.856899820766708e-34</v>
       </c>
       <c r="D371" s="18" t="n">
-        <v>2.185418512461601e+36</v>
+        <v>1.024625505077809e+27</v>
       </c>
       <c r="E371" s="18" t="n">
-        <v>0.928779417045652</v>
+        <v>0.8395874595221252</v>
       </c>
     </row>
     <row r="372">
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B372" s="18" t="n">
-        <v>3.514639213512396</v>
+        <v>9.356914717049548</v>
       </c>
       <c r="C372" s="18" t="n">
-        <v>1.630572377118862</v>
+        <v>1.491262170362916</v>
       </c>
       <c r="D372" s="18" t="n">
-        <v>7.575676476861211</v>
+        <v>58.70990008472595</v>
       </c>
       <c r="E372" s="18" t="n">
-        <v>0.0013378954753054</v>
+        <v>0.0170117208168996</v>
       </c>
     </row>
     <row r="373">
@@ -8071,16 +8071,16 @@
         </is>
       </c>
       <c r="B373" s="18" t="n">
-        <v>0.8842763523212634</v>
+        <v>247.1013368624319</v>
       </c>
       <c r="C373" s="18" t="n">
-        <v>0.1720132653217445</v>
+        <v>74.17938831832048</v>
       </c>
       <c r="D373" s="18" t="n">
-        <v>4.545839332867732</v>
+        <v>823.1271794421225</v>
       </c>
       <c r="E373" s="18" t="n">
-        <v>0.8829491431072732</v>
+        <v>2.848966787248093e-19</v>
       </c>
     </row>
     <row r="374">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="B374" s="18" t="n">
-        <v>1.715137670866465</v>
+        <v>1036.47157130745</v>
       </c>
       <c r="C374" s="18" t="n">
-        <v>0.3739472067674566</v>
+        <v>198.4960009252761</v>
       </c>
       <c r="D374" s="18" t="n">
-        <v>7.866611053079932</v>
+        <v>5412.065296635097</v>
       </c>
       <c r="E374" s="18" t="n">
-        <v>0.4875453004907296</v>
+        <v>1.811220494575887e-16</v>
       </c>
     </row>
     <row r="375">
@@ -8109,16 +8109,16 @@
         </is>
       </c>
       <c r="B375" s="18" t="n">
-        <v>0.014615230783371</v>
+        <v>4.244296851840973e-05</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>3.395802415754838e-21</v>
+        <v>1.151646732286611e-47</v>
       </c>
       <c r="D375" s="18" t="n">
-        <v>6.290265000701294e+16</v>
+        <v>1.564199789876539e+38</v>
       </c>
       <c r="E375" s="18" t="n">
-        <v>0.8469346263911733</v>
+        <v>0.8404509695326154</v>
       </c>
     </row>
     <row r="376">
@@ -8128,16 +8128,16 @@
         </is>
       </c>
       <c r="B376" s="18" t="n">
-        <v>0.745308229569479</v>
+        <v>0.6765357045682888</v>
       </c>
       <c r="C376" s="18" t="n">
-        <v>0.2180992952431065</v>
+        <v>0.020809886943864</v>
       </c>
       <c r="D376" s="18" t="n">
-        <v>2.546933296803251</v>
+        <v>21.99437992096674</v>
       </c>
       <c r="E376" s="18" t="n">
-        <v>0.6391763731419104</v>
+        <v>0.825881737937134</v>
       </c>
     </row>
     <row r="377">
@@ -8147,16 +8147,16 @@
         </is>
       </c>
       <c r="B377" s="18" t="n">
-        <v>0.6928470999855149</v>
+        <v>0.3152843271199199</v>
       </c>
       <c r="C377" s="18" t="n">
-        <v>0.3233685924842588</v>
+        <v>0.025332955874889</v>
       </c>
       <c r="D377" s="18" t="n">
-        <v>1.484488955066672</v>
+        <v>3.923908738419019</v>
       </c>
       <c r="E377" s="18" t="n">
-        <v>0.3452653955510509</v>
+        <v>0.3695749546185416</v>
       </c>
     </row>
     <row r="378">
@@ -8166,16 +8166,16 @@
         </is>
       </c>
       <c r="B378" s="18" t="n">
-        <v>3.689087017780136</v>
+        <v>1.701238436819411</v>
       </c>
       <c r="C378" s="18" t="n">
-        <v>1.366352867441817</v>
+        <v>0.3355450241947473</v>
       </c>
       <c r="D378" s="18" t="n">
-        <v>9.960357495523356</v>
+        <v>8.625406458812446</v>
       </c>
       <c r="E378" s="18" t="n">
-        <v>0.0099972428034937</v>
+        <v>0.5211751009883585</v>
       </c>
     </row>
     <row r="379">
@@ -8185,16 +8185,16 @@
         </is>
       </c>
       <c r="B379" s="18" t="n">
-        <v>2.304421327650905</v>
+        <v>0.6181318463741211</v>
       </c>
       <c r="C379" s="18" t="n">
-        <v>0.9679050526160932</v>
+        <v>0.1192201269837055</v>
       </c>
       <c r="D379" s="18" t="n">
-        <v>5.486444812927993</v>
+        <v>3.204886533580876</v>
       </c>
       <c r="E379" s="18" t="n">
-        <v>0.0592602299466661</v>
+        <v>0.5667088203104669</v>
       </c>
     </row>
     <row r="380">
@@ -8204,16 +8204,16 @@
         </is>
       </c>
       <c r="B380" s="18" t="n">
-        <v>3.343470790546605</v>
+        <v>2.919323748504034</v>
       </c>
       <c r="C380" s="18" t="n">
-        <v>0.7644174376741791</v>
+        <v>0.0911085858165372</v>
       </c>
       <c r="D380" s="18" t="n">
-        <v>14.62394285673416</v>
+        <v>93.54169063430594</v>
       </c>
       <c r="E380" s="18" t="n">
-        <v>0.1089007013777382</v>
+        <v>0.5447492371021275</v>
       </c>
     </row>
     <row r="381">
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="B381" s="18" t="n">
-        <v>2.254406466216466</v>
+        <v>1.212748212394001</v>
       </c>
       <c r="C381" s="18" t="n">
-        <v>1.102378435740078</v>
+        <v>0.2565096603518608</v>
       </c>
       <c r="D381" s="18" t="n">
-        <v>4.610348270742974</v>
+        <v>5.733734256430613</v>
       </c>
       <c r="E381" s="18" t="n">
-        <v>0.0259476670977793</v>
+        <v>0.8077259509109407</v>
       </c>
     </row>
     <row r="382">
@@ -8246,21 +8246,21 @@
       <c r="A383" s="18" t="inlineStr">
         <is>
           <t>{
-  "n": 2018,
-  "events": 75,
-  "coef_table_path": "/Users/loganglosser/THYROID_2026/data/m044/m044_cox_primary_with_rai_summary.csv",
+  "n": 2490,
+  "events": 178,
+  "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_with_rai_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 2.1448815550829616,
-    "hr_ci_low": 1.2233133500485036,
-    "hr_ci_high": 3.760701937204148,
-    "p": 0.007733002062061873,
+    "hr": 0.7017060980222831,
+    "hr_ci_low": 0.14521773659990697,
+    "hr_ci_high": 3.390711489728407,
+    "p": 0.6593967380396197,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 1.7561721454500336,
-    "hr_ci_low": 0.6191617969177375,
-    "hr_ci_high": 4.981154554121071,
-    "p": 0.2897338512324168,
+    "hr": 0.6873481362213698,
+    "hr_ci_low": 0.0008412353958190951,
+    "hr_ci_high": 561.6114855782756,
+    "p": 0.9127418404708438,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -8274,16 +8274,16 @@
         </is>
       </c>
       <c r="B384" s="18" t="n">
-        <v>2.144881555082962</v>
+        <v>0.7017060980222831</v>
       </c>
       <c r="C384" s="18" t="n">
-        <v>1.223313350048504</v>
+        <v>0.1452177365999069</v>
       </c>
       <c r="D384" s="18" t="n">
-        <v>3.760701937204148</v>
+        <v>3.390711489728407</v>
       </c>
       <c r="E384" s="18" t="n">
-        <v>0.0077330020620618</v>
+        <v>0.6593967380396197</v>
       </c>
     </row>
     <row r="385">
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="B385" s="18" t="n">
-        <v>1.756172145450034</v>
+        <v>0.6873481362213698</v>
       </c>
       <c r="C385" s="18" t="n">
-        <v>0.6191617969177375</v>
+        <v>0.000841235395819</v>
       </c>
       <c r="D385" s="18" t="n">
-        <v>4.981154554121071</v>
+        <v>561.6114855782756</v>
       </c>
       <c r="E385" s="18" t="n">
-        <v>0.2897338512324168</v>
+        <v>0.9127418404708438</v>
       </c>
     </row>
     <row r="386">
@@ -8312,16 +8312,16 @@
         </is>
       </c>
       <c r="B386" s="18" t="n">
-        <v>1.17877590028441</v>
+        <v>0.9343948946150856</v>
       </c>
       <c r="C386" s="18" t="n">
-        <v>1.015244981136063</v>
+        <v>0.616939097732629</v>
       </c>
       <c r="D386" s="18" t="n">
-        <v>1.368647616003432</v>
+        <v>1.415202606369943</v>
       </c>
       <c r="E386" s="18" t="n">
-        <v>0.0308871739770639</v>
+        <v>0.7486865004933857</v>
       </c>
     </row>
     <row r="387">
@@ -8331,16 +8331,16 @@
         </is>
       </c>
       <c r="B387" s="18" t="n">
-        <v>1.3516446139928</v>
+        <v>0.6525749308707922</v>
       </c>
       <c r="C387" s="18" t="n">
-        <v>0.8226749616499245</v>
+        <v>0.1348418210533696</v>
       </c>
       <c r="D387" s="18" t="n">
-        <v>2.220735099159576</v>
+        <v>3.158174793801314</v>
       </c>
       <c r="E387" s="18" t="n">
-        <v>0.2342632235265646</v>
+        <v>0.5957366618877946</v>
       </c>
     </row>
     <row r="388">
@@ -8350,16 +8350,16 @@
         </is>
       </c>
       <c r="B388" s="18" t="n">
-        <v>1.044204056762613</v>
+        <v>1.483588542782323</v>
       </c>
       <c r="C388" s="18" t="n">
-        <v>0.9404854035297732</v>
+        <v>1.273988560504973</v>
       </c>
       <c r="D388" s="18" t="n">
-        <v>1.159361015138797</v>
+        <v>1.727672470938474</v>
       </c>
       <c r="E388" s="18" t="n">
-        <v>0.4177166289184749</v>
+        <v>3.854241464279303e-07</v>
       </c>
     </row>
     <row r="389">
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="B389" s="18" t="n">
-        <v>0.8153820803804007</v>
+        <v>4632872374.787572</v>
       </c>
       <c r="C389" s="18" t="n">
-        <v>0.4469217868053021</v>
+        <v>1282630.534952183</v>
       </c>
       <c r="D389" s="18" t="n">
-        <v>1.487615857257605</v>
+        <v>16733974325560.56</v>
       </c>
       <c r="E389" s="18" t="n">
-        <v>0.5058601450053158</v>
+        <v>1.009988849570074e-07</v>
       </c>
     </row>
     <row r="390">
@@ -8388,16 +8388,16 @@
         </is>
       </c>
       <c r="B390" s="18" t="n">
-        <v>3.103797084173702</v>
+        <v>1.038412319059901e-76</v>
       </c>
       <c r="C390" s="18" t="n">
-        <v>1.123755759637267</v>
+        <v>6.357004662054911e-88</v>
       </c>
       <c r="D390" s="18" t="n">
-        <v>8.572642459990375</v>
+        <v>1.696239348087564e-65</v>
       </c>
       <c r="E390" s="18" t="n">
-        <v>0.0288847828622335</v>
+        <v>2.970465418296967e-40</v>
       </c>
     </row>
     <row r="391">
@@ -8407,16 +8407,16 @@
         </is>
       </c>
       <c r="B391" s="18" t="n">
-        <v>0.4795134452400519</v>
+        <v>0.7671387688587653</v>
       </c>
       <c r="C391" s="18" t="n">
-        <v>0.1064045541050051</v>
+        <v>7.764454875472284e-09</v>
       </c>
       <c r="D391" s="18" t="n">
-        <v>2.160933299331108</v>
+        <v>75794360.34140719</v>
       </c>
       <c r="E391" s="18" t="n">
-        <v>0.3386494524908224</v>
+        <v>0.9774836194506896</v>
       </c>
     </row>
     <row r="392">
@@ -8426,16 +8426,16 @@
         </is>
       </c>
       <c r="B392" s="18" t="n">
-        <v>0.2336321355555456</v>
+        <v>8.161371361443207</v>
       </c>
       <c r="C392" s="18" t="n">
-        <v>0.0662312278521123</v>
+        <v>1.276059885032733</v>
       </c>
       <c r="D392" s="18" t="n">
-        <v>0.8241425764614443</v>
+        <v>52.19816348797514</v>
       </c>
       <c r="E392" s="18" t="n">
-        <v>0.0237791434100632</v>
+        <v>0.0265925666535809</v>
       </c>
     </row>
     <row r="393">
@@ -8445,16 +8445,16 @@
         </is>
       </c>
       <c r="B393" s="18" t="n">
-        <v>0.0148850604299785</v>
+        <v>0.0005455036111687</v>
       </c>
       <c r="C393" s="18" t="n">
-        <v>7.40266054577302e-40</v>
+        <v>3.980019740488559e-34</v>
       </c>
       <c r="D393" s="18" t="n">
-        <v>2.993045846612945e+35</v>
+        <v>7.476701353286075e+26</v>
       </c>
       <c r="E393" s="18" t="n">
-        <v>0.9235158846632324</v>
+        <v>0.8319327233716071</v>
       </c>
     </row>
     <row r="394">
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="B394" s="18" t="n">
-        <v>3.41760281481349</v>
+        <v>3.112074062776549e-09</v>
       </c>
       <c r="C394" s="18" t="n">
-        <v>1.587604175234166</v>
+        <v>2.925329949753643e-17</v>
       </c>
       <c r="D394" s="18" t="n">
-        <v>7.357003201442401</v>
+        <v>0.3310739348572341</v>
       </c>
       <c r="E394" s="18" t="n">
-        <v>0.0016804957078762</v>
+        <v>0.0377843580871332</v>
       </c>
     </row>
     <row r="395">
@@ -8483,16 +8483,16 @@
         </is>
       </c>
       <c r="B395" s="18" t="n">
-        <v>0.9478323738393744</v>
+        <v>35980.66176387949</v>
       </c>
       <c r="C395" s="18" t="n">
-        <v>0.1868224435604148</v>
+        <v>4026.899773790985</v>
       </c>
       <c r="D395" s="18" t="n">
-        <v>4.808770251457837</v>
+        <v>321490.0031514656</v>
       </c>
       <c r="E395" s="18" t="n">
-        <v>0.9484441605720668</v>
+        <v>6.065169422017391e-21</v>
       </c>
     </row>
     <row r="396">
@@ -8502,16 +8502,16 @@
         </is>
       </c>
       <c r="B396" s="18" t="n">
-        <v>1.538214247890503</v>
+        <v>0.1435709970893622</v>
       </c>
       <c r="C396" s="18" t="n">
-        <v>0.9380071784980222</v>
+        <v>0.0304249841541261</v>
       </c>
       <c r="D396" s="18" t="n">
-        <v>2.522478640517499</v>
+        <v>0.6774902856420456</v>
       </c>
       <c r="E396" s="18" t="n">
-        <v>0.0879394102750915</v>
+        <v>0.0142139598141684</v>
       </c>
     </row>
     <row r="397">
@@ -8521,16 +8521,16 @@
         </is>
       </c>
       <c r="B397" s="18" t="n">
-        <v>1.728581031556822</v>
+        <v>6.141659658158964e-61</v>
       </c>
       <c r="C397" s="18" t="n">
-        <v>0.3783747100406021</v>
+        <v>1.129533267671667e-74</v>
       </c>
       <c r="D397" s="18" t="n">
-        <v>7.896913571040236</v>
+        <v>3.339430934549663e-47</v>
       </c>
       <c r="E397" s="18" t="n">
-        <v>0.4801246285767084</v>
+        <v>8.555788618982091e-18</v>
       </c>
     </row>
     <row r="398">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="B398" s="18" t="n">
-        <v>0.0169759177456619</v>
+        <v>1.811161376009843e-05</v>
       </c>
       <c r="C398" s="18" t="n">
-        <v>2.104095110674682e-21</v>
+        <v>4.701739275523831e-48</v>
       </c>
       <c r="D398" s="18" t="n">
-        <v>1.369623368475357e+17</v>
+        <v>6.976791646075267e+37</v>
       </c>
       <c r="E398" s="18" t="n">
-        <v>0.8544027665567406</v>
+        <v>0.8272360770559199</v>
       </c>
     </row>
     <row r="399">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="B399" s="18" t="n">
-        <v>0.7411259167422359</v>
+        <v>25.80374360020472</v>
       </c>
       <c r="C399" s="18" t="n">
-        <v>0.2164486557617133</v>
+        <v>2.641588639158246</v>
       </c>
       <c r="D399" s="18" t="n">
-        <v>2.537634722350525</v>
+        <v>252.0578616651215</v>
       </c>
       <c r="E399" s="18" t="n">
-        <v>0.6333184372976174</v>
+        <v>0.0051849897478857</v>
       </c>
     </row>
     <row r="400">
@@ -8578,16 +8578,16 @@
         </is>
       </c>
       <c r="B400" s="18" t="n">
-        <v>0.6626635950125537</v>
+        <v>146.2372272103068</v>
       </c>
       <c r="C400" s="18" t="n">
-        <v>0.3069980350935222</v>
+        <v>26.25302125711041</v>
       </c>
       <c r="D400" s="18" t="n">
-        <v>1.430377363885048</v>
+        <v>814.5853542996256</v>
       </c>
       <c r="E400" s="18" t="n">
-        <v>0.294553149327239</v>
+        <v>1.276531873048788e-08</v>
       </c>
     </row>
     <row r="401">
@@ -8597,16 +8597,16 @@
         </is>
       </c>
       <c r="B401" s="18" t="n">
-        <v>3.614488882206021</v>
+        <v>1.381613121902114</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>1.346833172214343</v>
+        <v>0.0004651318543957</v>
       </c>
       <c r="D401" s="18" t="n">
-        <v>9.700184216662411</v>
+        <v>4103.90043290372</v>
       </c>
       <c r="E401" s="18" t="n">
-        <v>0.0107375727030134</v>
+        <v>0.9368493121857931</v>
       </c>
     </row>
     <row r="402">
@@ -8616,16 +8616,16 @@
         </is>
       </c>
       <c r="B402" s="18" t="n">
-        <v>2.23915037115549</v>
+        <v>0.0122541834910511</v>
       </c>
       <c r="C402" s="18" t="n">
-        <v>0.9459890676746848</v>
+        <v>3.561946129919399e-09</v>
       </c>
       <c r="D402" s="18" t="n">
-        <v>5.300055313503852</v>
+        <v>42158.13702824013</v>
       </c>
       <c r="E402" s="18" t="n">
-        <v>0.0667043809638897</v>
+        <v>0.5664972341472885</v>
       </c>
     </row>
     <row r="403">
@@ -8635,16 +8635,16 @@
         </is>
       </c>
       <c r="B403" s="18" t="n">
-        <v>3.09018590983374</v>
+        <v>6.698968898109763e-12</v>
       </c>
       <c r="C403" s="18" t="n">
-        <v>0.7041375675163155</v>
+        <v>4.485854086524094e-28</v>
       </c>
       <c r="D403" s="18" t="n">
-        <v>13.56162403181778</v>
+        <v>100039.3312672697</v>
       </c>
       <c r="E403" s="18" t="n">
-        <v>0.1348847104905876</v>
+        <v>0.1757204896450104</v>
       </c>
     </row>
     <row r="404">
@@ -8654,16 +8654,16 @@
         </is>
       </c>
       <c r="B404" s="18" t="n">
-        <v>2.270670195340035</v>
+        <v>597.3338430777812</v>
       </c>
       <c r="C404" s="18" t="n">
-        <v>1.10788812835044</v>
+        <v>0.2226726927440854</v>
       </c>
       <c r="D404" s="18" t="n">
-        <v>4.653848167578396</v>
+        <v>1602386.514884182</v>
       </c>
       <c r="E404" s="18" t="n">
-        <v>0.0251044927096117</v>
+        <v>0.1125009879682974</v>
       </c>
     </row>
   </sheetData>
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -9250,26 +9250,120 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>S4 pooled-LVI artifact check</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>OR pooled=1.7980684439311188 p=0.004004853466394754</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT QA: within ±0.5 ppt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
         </is>
       </c>
     </row>
@@ -11023,16 +11117,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01413021552788013</v>
+        <v>0.05500423195487584</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001068060180277012</v>
+        <v>0.0103820772812532</v>
       </c>
       <c r="D4" t="n">
-        <v>0.186939832184887</v>
+        <v>0.291412349473533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001226273475024972</v>
+        <v>0.0006510879774404757</v>
       </c>
     </row>
     <row r="5">
@@ -11042,16 +11136,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5689880035875439</v>
+        <v>0.5560929342658829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03005726534141062</v>
+        <v>0.07402177141912585</v>
       </c>
       <c r="D5" t="n">
-        <v>10.7710180733077</v>
+        <v>4.177681047234947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7070453614462671</v>
+        <v>0.5684431747800904</v>
       </c>
     </row>
     <row r="6">
@@ -11061,16 +11155,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4799986868471415</v>
+        <v>4.218268766623468</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001897303751580615</v>
+        <v>0.304009145880805</v>
       </c>
       <c r="D6" t="n">
-        <v>121.4348199032646</v>
+        <v>58.53044761504511</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7948794393251363</v>
+        <v>0.2834247538466057</v>
       </c>
     </row>
     <row r="7">
@@ -11080,16 +11174,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6528464689608987</v>
+        <v>0.3072213141749107</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02841986932470952</v>
+        <v>0.02260894619838982</v>
       </c>
       <c r="D7" t="n">
-        <v>14.99684981535608</v>
+        <v>4.174672054820546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7897371772286217</v>
+        <v>0.3753382685222088</v>
       </c>
     </row>
     <row r="8">
@@ -11099,16 +11193,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9999999999999919</v>
+        <v>0.9999999999999983</v>
       </c>
       <c r="D8" t="n">
-        <v>1.000000000000008</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9760210680852576</v>
+        <v>0.2617501767237684</v>
       </c>
     </row>
     <row r="9">
@@ -11118,16 +11212,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9161328106597636</v>
+        <v>1.025924666274582</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6771543318825255</v>
+        <v>0.8858459944846289</v>
       </c>
       <c r="D9" t="n">
-        <v>1.239450576110266</v>
+        <v>1.188153953874287</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5700438043393028</v>
+        <v>0.7325758077557561</v>
       </c>
     </row>
     <row r="10">
@@ -11137,16 +11231,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.746920567150571</v>
+        <v>1.724460765005128</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5191680013353923</v>
+        <v>0.5427951324328287</v>
       </c>
       <c r="D10" t="n">
-        <v>14.53397085880921</v>
+        <v>5.478613849600199</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2345290624516244</v>
+        <v>0.355519580485365</v>
       </c>
     </row>
     <row r="11">
@@ -11156,16 +11250,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.769593548838072</v>
+        <v>4.850204437151219</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7207462802354819</v>
+        <v>1.346207961219806</v>
       </c>
       <c r="D11" t="n">
-        <v>31.56314953673463</v>
+        <v>17.47462781370399</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1051624795233546</v>
+        <v>0.01575381934340091</v>
       </c>
     </row>
     <row r="12">
@@ -11175,16 +11269,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11.56308962388755</v>
+        <v>3.144653282826895</v>
       </c>
       <c r="C12" t="n">
-        <v>1.588019908436875</v>
+        <v>0.6455444607144427</v>
       </c>
       <c r="D12" t="n">
-        <v>84.196073953295</v>
+        <v>15.31861067826327</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01566868583656499</v>
+        <v>0.1561305634242252</v>
       </c>
     </row>
     <row r="13">
@@ -11194,16 +11288,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.088665125354509</v>
+        <v>1.09766527781081</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9371042249758985</v>
+        <v>0.9438585982007791</v>
       </c>
       <c r="D13" t="n">
-        <v>1.264738460861844</v>
+        <v>1.276535557771316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2667118841834567</v>
+        <v>0.2263469061098112</v>
       </c>
     </row>
   </sheetData>
@@ -12327,16 +12421,16 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>0.5206463545221218</v>
+        <v>0.8679286099430543</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>0.2208502401334555</v>
+        <v>0.4371570253485023</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1.227404716940181</v>
+        <v>1.723179608876583</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>0.1357850626236083</v>
+        <v>0.6856224175786536</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
@@ -12351,16 +12445,16 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>1.803142473049095</v>
+        <v>2.123642026911864</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>1.216513912993914</v>
+        <v>1.533370870140629</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>2.672655646092781</v>
+        <v>2.941138080999752</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>0.003324166076161699</v>
+        <v>5.825549371409613e-06</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
@@ -12375,16 +12469,16 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>0.959087647158345</v>
+        <v>0.9896872203242973</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>0.8558577777367269</v>
+        <v>0.9020897724978332</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>1.074768657666727</v>
+        <v>1.085790820309502</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>0.4721693311377841</v>
+        <v>0.8264666665097463</v>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
@@ -12399,16 +12493,16 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>1.415612656293561</v>
+        <v>1.16544897652856</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.9581423942358207</v>
+        <v>0.8398800321125361</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>2.091504566246436</v>
+        <v>1.617220632659917</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>0.08094065547071114</v>
+        <v>0.3596684419975973</v>
       </c>
       <c r="F8" s="28" t="n"/>
     </row>
@@ -12419,16 +12513,16 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>1.05396825090431</v>
+        <v>1.056396758774761</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>0.9751068751851637</v>
+        <v>0.9897420624996792</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>1.139207508616274</v>
+        <v>1.127540350393245</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.1852806869483936</v>
+        <v>0.09896551303985371</v>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
@@ -12443,16 +12537,16 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>0.9499944309815281</v>
+        <v>0.8690043784773853</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.6030069709102067</v>
+        <v>0.6042699958265132</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>1.496648401151413</v>
+        <v>1.2497205140559</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>0.8249314914809697</v>
+        <v>0.4487954545213408</v>
       </c>
       <c r="F10" s="28" t="n"/>
     </row>
@@ -12463,16 +12557,16 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>4.064670487927987</v>
+        <v>4.397015389057731</v>
       </c>
       <c r="C11" s="28" t="n">
-        <v>1.916630062128161</v>
+        <v>2.326080233319977</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>8.620101761885014</v>
+        <v>8.311727194386481</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>0.0002560862557023112</v>
+        <v>5.152961060231732e-06</v>
       </c>
       <c r="F11" s="28" t="n"/>
     </row>
@@ -12483,16 +12577,16 @@
         </is>
       </c>
       <c r="B12" s="28" t="n">
-        <v>0.4032548237157969</v>
+        <v>0.4294096849113297</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.09349528866863331</v>
+        <v>0.1483860822294949</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>1.739279648907205</v>
+        <v>1.242654801078072</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>0.223298329848847</v>
+        <v>0.1189385695345342</v>
       </c>
       <c r="F12" s="28" t="n"/>
     </row>
@@ -12503,16 +12597,16 @@
         </is>
       </c>
       <c r="B13" s="28" t="n">
-        <v>0.9999999999688559</v>
+        <v>1.000000000077513</v>
       </c>
       <c r="C13" s="28" t="n">
-        <v>0.9999997709597415</v>
+        <v>0.9999996684323157</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>1.000000228978023</v>
+        <v>1.00000033172282</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>0.9997873278281352</v>
+        <v>0.9996344992021077</v>
       </c>
       <c r="F13" s="28" t="n"/>
     </row>
@@ -12523,16 +12617,16 @@
         </is>
       </c>
       <c r="B14" s="28" t="n">
-        <v>0.4025658212119963</v>
+        <v>0.4981391512004436</v>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.1790133646743263</v>
+        <v>0.2688062120348371</v>
       </c>
       <c r="D14" s="28" t="n">
-        <v>0.905291293211088</v>
+        <v>0.9231282717772138</v>
       </c>
       <c r="E14" s="28" t="n">
-        <v>0.02776413268177217</v>
+        <v>0.0268221065984008</v>
       </c>
       <c r="F14" s="28" t="n"/>
     </row>
@@ -12543,16 +12637,16 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>9.263262405819596</v>
+        <v>9.179036364441508</v>
       </c>
       <c r="C15" s="28" t="n">
-        <v>4.810900420995349</v>
+        <v>5.174699297923713</v>
       </c>
       <c r="D15" s="28" t="n">
-        <v>17.83616846954347</v>
+        <v>16.28204920304177</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>2.751261191735409e-11</v>
+        <v>3.424138831731132e-14</v>
       </c>
       <c r="F15" s="28" t="n"/>
     </row>
@@ -12563,16 +12657,16 @@
         </is>
       </c>
       <c r="B16" s="28" t="n">
-        <v>1.865793604816147</v>
+        <v>1.529009881734143</v>
       </c>
       <c r="C16" s="28" t="n">
-        <v>0.5997323531271759</v>
+        <v>0.5494736550444274</v>
       </c>
       <c r="D16" s="28" t="n">
-        <v>5.804565582665226</v>
+        <v>4.254746696184426</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>0.2814594132836437</v>
+        <v>0.4161035542764218</v>
       </c>
       <c r="F16" s="28" t="n"/>
     </row>
@@ -12583,7 +12677,7 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>8.234027567608161e-10</v>
+        <v>4.753608602848542e-10</v>
       </c>
       <c r="C17" s="28" t="n">
         <v>1.388794386496402e-11</v>
@@ -12592,7 +12686,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>0.9992368963221444</v>
+        <v>0.9992050878233492</v>
       </c>
       <c r="F17" s="28" t="n"/>
     </row>
@@ -12603,16 +12697,16 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>0.8900578758120722</v>
+        <v>0.8869742759961744</v>
       </c>
       <c r="C18" s="28" t="n">
-        <v>0.4972517251809978</v>
+        <v>0.547161887363565</v>
       </c>
       <c r="D18" s="28" t="n">
-        <v>1.593162943792179</v>
+        <v>1.437825595034902</v>
       </c>
       <c r="E18" s="28" t="n">
-        <v>0.6949870010775374</v>
+        <v>0.6265209498249684</v>
       </c>
       <c r="F18" s="28" t="n"/>
     </row>
@@ -12623,16 +12717,16 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>2.47107536511665</v>
+        <v>1.871844245674674</v>
       </c>
       <c r="C19" s="28" t="n">
-        <v>0.9552563654630051</v>
+        <v>0.7807492309684739</v>
       </c>
       <c r="D19" s="28" t="n">
-        <v>6.392224831840564</v>
+        <v>4.487741698725889</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>0.06210208227991191</v>
+        <v>0.1599597164104432</v>
       </c>
       <c r="F19" s="28" t="n"/>
     </row>
@@ -12643,7 +12737,7 @@
         </is>
       </c>
       <c r="B20" s="28" t="n">
-        <v>1.149473429389386e-09</v>
+        <v>7.024314372146672e-10</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>1.388794386496402e-11</v>
@@ -12652,7 +12746,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>0.9994853005318667</v>
+        <v>0.9994713992834721</v>
       </c>
       <c r="F20" s="28" t="n"/>
     </row>
@@ -12663,16 +12757,16 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>0.8994143043047916</v>
+        <v>0.6314560528350701</v>
       </c>
       <c r="C21" s="28" t="n">
-        <v>0.3327371250746828</v>
+        <v>0.2568131584400292</v>
       </c>
       <c r="D21" s="28" t="n">
-        <v>2.431186753226003</v>
+        <v>1.552633630940525</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>0.8344867055868793</v>
+        <v>0.316574843170173</v>
       </c>
       <c r="F21" s="28" t="n"/>
     </row>
@@ -12683,16 +12777,16 @@
         </is>
       </c>
       <c r="B22" s="28" t="n">
-        <v>1.730704538765681</v>
+        <v>1.750121052252119</v>
       </c>
       <c r="C22" s="28" t="n">
-        <v>0.9825439306167997</v>
+        <v>1.088258406762066</v>
       </c>
       <c r="D22" s="28" t="n">
-        <v>3.048553970125062</v>
+        <v>2.814518756302825</v>
       </c>
       <c r="E22" s="28" t="n">
-        <v>0.05756478400617664</v>
+        <v>0.02095037504959985</v>
       </c>
       <c r="F22" s="28" t="n"/>
     </row>
@@ -12703,16 +12797,16 @@
         </is>
       </c>
       <c r="B23" s="28" t="n">
-        <v>2.295459213080083</v>
+        <v>2.061082258861333</v>
       </c>
       <c r="C23" s="28" t="n">
-        <v>1.149102116321469</v>
+        <v>1.141426139715414</v>
       </c>
       <c r="D23" s="28" t="n">
-        <v>4.585434944443316</v>
+        <v>3.721712627723844</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>0.01859114256048079</v>
+        <v>0.0164542393137029</v>
       </c>
       <c r="F23" s="28" t="n"/>
     </row>
@@ -12723,16 +12817,16 @@
         </is>
       </c>
       <c r="B24" s="28" t="n">
-        <v>2.426078408991358</v>
+        <v>2.351957211059262</v>
       </c>
       <c r="C24" s="28" t="n">
-        <v>1.06057102469977</v>
+        <v>1.168892655195049</v>
       </c>
       <c r="D24" s="28" t="n">
-        <v>5.549705120635581</v>
+        <v>4.732430046564549</v>
       </c>
       <c r="E24" s="28" t="n">
-        <v>0.03579426143389201</v>
+        <v>0.01651095330410831</v>
       </c>
       <c r="F24" s="28" t="n"/>
     </row>
@@ -12743,16 +12837,16 @@
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>1.123627441098395</v>
+        <v>1.202640879497502</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>0.2422511546911807</v>
+        <v>0.3351725935101096</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>5.211692914317777</v>
+        <v>4.315224791775526</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0.8816355286876478</v>
+        <v>0.7771269536574649</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="19">
@@ -12769,16 +12863,16 @@
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>1.393944822862141</v>
+        <v>1.635941570677835</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>0.9410113793459441</v>
+        <v>1.183517106772544</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>2.064887005441653</v>
+        <v>2.261314861743028</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0.09758118595054122</v>
+        <v>0.002881862436851421</v>
       </c>
     </row>
     <row r="28">
@@ -12788,16 +12882,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>1.025049938589366</v>
+        <v>1.564216493991319</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.4683176194958094</v>
+        <v>0.8457991913982197</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2.243621279364367</v>
+        <v>2.892853605156147</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.9506396590407793</v>
+        <v>0.1538352161719879</v>
       </c>
     </row>
     <row r="29">
@@ -12807,16 +12901,16 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>1.39918097065779</v>
+        <v>1.627832921137797</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>0.9319903090618363</v>
+        <v>1.161546625310144</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>2.10056625011643</v>
+        <v>2.281303187835856</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.1051856235318323</v>
+        <v>0.004660208861568816</v>
       </c>
     </row>
     <row r="30">
@@ -12826,16 +12920,16 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>0.5247295914671045</v>
+        <v>0.8698697087040531</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.219558917888193</v>
+        <v>0.4314830892472102</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>1.254064953542209</v>
+        <v>1.753656931123325</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.1468679320291506</v>
+        <v>0.6967398108202889</v>
       </c>
     </row>
     <row r="31">
@@ -12845,16 +12939,16 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>4.045155914882584</v>
+        <v>4.422065465782088</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>2.780534009197924</v>
+        <v>3.24361725881098</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>5.884943799133652</v>
+        <v>6.028659186142928</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>2.739210328395782e-13</v>
+        <v>5.378356570327354e-21</v>
       </c>
     </row>
     <row r="32"/>
@@ -12866,7 +12960,7 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>LR χ²=6.30, df=6, p=0.3909</t>
+          <t>LR χ²=3.65, df=6, p=0.7237</t>
         </is>
       </c>
     </row>
@@ -12878,16 +12972,16 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>1.645676329408767</v>
+        <v>1.742171318893548</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.7230984843626904</v>
+        <v>0.9150293348882349</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>3.745341249834392</v>
+        <v>3.317009399207961</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.2351240171313304</v>
+        <v>0.09108883680757478</v>
       </c>
     </row>
     <row r="36">
@@ -12897,16 +12991,16 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>1.951285004489309</v>
+        <v>2.226964025209957</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>1.20991487549553</v>
+        <v>1.488011898491131</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>3.146926487026986</v>
+        <v>3.332882468620188</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.006118067426023935</v>
+        <v>9.944536741874531e-05</v>
       </c>
     </row>
     <row r="37">
@@ -12916,16 +13010,16 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>1.241207693829348</v>
+        <v>3.571528127045172</v>
       </c>
       <c r="C37" s="18" t="n">
-        <v>0.07204442242452243</v>
+        <v>0.5662808533458451</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>21.38398070766935</v>
+        <v>22.52559500627231</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.8817250858670671</v>
+        <v>0.1754912629616063</v>
       </c>
     </row>
     <row r="38">

--- a/M044_ETE_tables.xlsx
+++ b/M044_ETE_tables.xlsx
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -9274,97 +9274,1921 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>S4 pooled-LVI artifact check</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
         </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>339</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>Sex known (female/male — multivariable frame)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>Positive follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D80" s="18" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E80" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>Finite positive Cox duration (days; event-time or censored PY)</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D82" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D103" s="18" t="n">
+        <v>339</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D104" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>Sex known (female/male — multivariable frame)</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>Positive follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D106" s="18" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>Finite positive Cox duration (days; event-time or censored PY)</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D108" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D109" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D110" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D128" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D129" s="18" t="n">
+        <v>339</v>
+      </c>
+      <c r="E129" s="18" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D130" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E130" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>Sex known (female/male — multivariable frame)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D131" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>Positive follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D132" s="18" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E132" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D133" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>Finite positive Cox duration (days; event-time or censored PY)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D134" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E134" s="18" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D135" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E135" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D136" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D153" s="18" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D154" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D155" s="18" t="n">
+        <v>339</v>
+      </c>
+      <c r="E155" s="18" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D156" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E156" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>Sex known (female/male — multivariable frame)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D157" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t>Positive follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D158" s="18" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E158" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D159" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>Finite positive Cox duration (days; event-time or censored PY)</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D160" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E160" s="18" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D161" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E161" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D162" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="18" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B178" s="18" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B179" s="18" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B180" s="18" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D180" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B181" s="18" t="inlineStr">
+        <is>
+          <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D181" s="18" t="n">
+        <v>339</v>
+      </c>
+      <c r="E181" s="18" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B182" s="18" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C182" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D182" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E182" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>Sex known (female/male — multivariable frame)</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D183" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="18" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B184" s="18" t="inlineStr">
+        <is>
+          <t>Positive follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D184" s="18" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E184" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B185" s="18" t="inlineStr">
+        <is>
+          <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D185" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="18" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B186" s="18" t="inlineStr">
+        <is>
+          <t>Finite positive Cox duration (days; event-time or censored PY)</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D186" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E186" s="18" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B187" s="18" t="inlineStr">
+        <is>
+          <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D187" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B188" s="18" t="inlineStr">
+        <is>
+          <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D188" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="18" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>0</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D207" t="n">
+        <v>339</v>
+      </c>
+      <c r="E207" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D208" t="n">
+        <v>33</v>
+      </c>
+      <c r="E208" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sex known (female/male — multivariable frame)</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Positive follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>5</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>6</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Finite positive Cox duration (days; event-time or censored PY)</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D212" t="n">
+        <v>31</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>7</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D213" t="n">
+        <v>4</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>8</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1638</v>
       </c>
     </row>
   </sheetData>
@@ -12036,7 +13860,7 @@
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Person-years</t>
+          <t>Person-years (FU&gt;0)</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
@@ -12070,27 +13894,27 @@
         <v>2576</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="I5" s="28" t="n">
@@ -12100,7 +13924,7 @@
         <v>8137.3</v>
       </c>
       <c r="K5" s="28" t="n">
-        <v>0.73</v>
+        <v>1.03</v>
       </c>
       <c r="L5" s="28" t="n">
         <v>1.78</v>
@@ -12124,27 +13948,27 @@
         <v>1266</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>9.16%</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>12.88%</t>
+          <t>9.79%</t>
         </is>
       </c>
       <c r="I6" s="28" t="n">
@@ -12154,7 +13978,7 @@
         <v>4138.3</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="L6" s="28" t="n">
         <v>3.94</v>
@@ -12178,27 +14002,27 @@
         <v>192</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="E7" s="28" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>8.85%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>15.10%</t>
+          <t>13.02%</t>
         </is>
       </c>
       <c r="I7" s="28" t="n">
@@ -12208,7 +14032,7 @@
         <v>700.8</v>
       </c>
       <c r="K7" s="28" t="n">
-        <v>1.71</v>
+        <v>3.28</v>
       </c>
       <c r="L7" s="28" t="n">
         <v>4.14</v>
@@ -12333,7 +14157,7 @@
     <row r="11" ht="15" customHeight="1" s="19">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Notes: Person-years use all follow-up time (incl zero-FU). Restricted to FU&gt;0 in Supp Table S3.</t>
+          <t>Notes: Col J sums follow-up years among patients with FU&gt;0 only (PY-rate denominator). Col K = 100 × (path-proven events among FU&gt;0) / col J. Path-proven n and Path-proven % include all patients (zero-FU retained in denominator for proportions).</t>
         </is>
       </c>
     </row>

--- a/M044_ETE_tables.xlsx
+++ b/M044_ETE_tables.xlsx
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -10888,94 +10888,94 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="18" t="inlineStr">
         <is>
           <t>S4 pooled-LVI artifact check</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="18" t="inlineStr">
         <is>
           <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C190" s="18" t="inlineStr">
         <is>
           <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="18" t="inlineStr">
         <is>
           <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
         </is>
@@ -10987,208 +10987,539 @@
           <t>Strict-DTC Cox/KM inclusion flow</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="18" t="inlineStr">
         <is>
           <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="18" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="18" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="18" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="18" t="inlineStr">
         <is>
           <t>excluded_at_step</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" s="18" t="inlineStr">
         <is>
           <t>cum_excluded_from_cohort</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="18" t="inlineStr">
         <is>
           <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
         </is>
       </c>
-      <c r="C206" t="n">
+      <c r="C206" s="18" t="n">
         <v>4128</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="18" t="inlineStr">
         <is>
           <t>Strict-DTC (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list per script)</t>
         </is>
       </c>
-      <c r="C207" t="n">
+      <c r="C207" s="18" t="n">
         <v>3789</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="18" t="n">
         <v>339</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207" s="18" t="n">
         <v>339</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="18" t="inlineStr">
         <is>
           <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
         </is>
       </c>
-      <c r="C208" t="n">
+      <c r="C208" s="18" t="n">
         <v>3756</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208" s="18" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="18" t="inlineStr">
         <is>
           <t>Sex known (female/male — multivariable frame)</t>
         </is>
       </c>
-      <c r="C209" t="n">
+      <c r="C209" s="18" t="n">
         <v>3756</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" s="18" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="18" t="inlineStr">
         <is>
           <t>Positive follow-up (followup_years &gt; 0)</t>
         </is>
       </c>
-      <c r="C210" t="n">
+      <c r="C210" s="18" t="n">
         <v>2525</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="18" t="n">
         <v>1231</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210" s="18" t="n">
         <v>1603</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="18" t="inlineStr">
         <is>
           <t>Known surgery date (surg_first_date non-null — CPM SSOT lineage)</t>
         </is>
       </c>
-      <c r="C211" t="n">
+      <c r="C211" s="18" t="n">
         <v>2525</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211" s="18" t="n">
         <v>1603</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="18" t="inlineStr">
         <is>
           <t>Finite positive Cox duration (days; event-time or censored PY)</t>
         </is>
       </c>
-      <c r="C212" t="n">
+      <c r="C212" s="18" t="n">
         <v>2494</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" s="18" t="n">
         <v>1634</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="18" t="inlineStr">
         <is>
           <t>Age + tumor size non-missing (Cox covariate complete-case)</t>
         </is>
       </c>
-      <c r="C213" t="n">
+      <c r="C213" s="18" t="n">
         <v>2490</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" s="18" t="n">
         <v>1638</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="18" t="inlineStr">
         <is>
           <t>Final Cox PH / KM analytic rows (= step 7; lifelines fitted sample)</t>
         </is>
       </c>
-      <c r="C214" t="n">
+      <c r="C214" s="18" t="n">
         <v>2490</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" s="18" t="n">
         <v>1638</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>OR pooled=1.7360199189525616 p=0.0010321630526339087</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 6.29% expected 4.1% (n=318)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 12.5% expected 7.0% (n=344)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 4.48% expected 2.6% (n=268)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 12.2% expected 8.6% (n=336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.65% expected 2.7% (n=712)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.58% expected 2.3% (n=642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 2.01% expected 1.1% (n=947)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 7.06% expected 5.6% (n=269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 22.73% expected 11.4% (n=44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 11.63% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 13.21% expected 3.8% (n=53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="31" t="inlineStr">
+        <is>
+          <t>Strict-DTC Cox/KM inclusion flow</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>excluded_at_step</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>cum_excluded_from_cohort</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>path_proven_events_final_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>0</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>1</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D233" t="n">
+        <v>339</v>
+      </c>
+      <c r="E233" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D234" t="n">
+        <v>33</v>
+      </c>
+      <c r="E234" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>3756</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>4</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1231</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>5</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>6</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D238" t="n">
+        <v>31</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>7</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Tumor size known (cm; Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D239" t="n">
+        <v>4</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>8</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Age at surgery known (Cox covariate complete-case)</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>9</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1638</v>
+      </c>
+      <c r="F241" t="n">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -13918,7 +14249,7 @@
         </is>
       </c>
       <c r="I5" s="28" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J5" s="28" t="n">
         <v>8137.3</v>
@@ -13972,7 +14303,7 @@
         </is>
       </c>
       <c r="I6" s="28" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>4138.3</v>
@@ -14026,7 +14357,7 @@
         </is>
       </c>
       <c r="I7" s="28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" s="28" t="n">
         <v>700.8</v>

--- a/M044_ETE_tables.xlsx
+++ b/M044_ETE_tables.xlsx
@@ -2273,12 +2273,12 @@
       <c r="A53" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 4028,
-  "n_events": 203,
-  "llf": -668.4548944332049,
-  "aic": 1380.9097888664098,
-  "pseudo_r2_mcfadden": 0.16924339565274382,
-  "lr_vs_null_chi2": 272.3579339184719,
+  "n_obs": 3963,
+  "n_events": 202,
+  "llf": -664.8694686549093,
+  "aic": 1373.7389373098185,
+  "pseudo_r2_mcfadden": 0.16717101382841393,
+  "lr_vs_null_chi2": 266.91410838023035,
   "lr_vs_null_pvalue": 0.0,
   "formula": "y_pp ~ C(ete_group, Treatment(reference='Microscopic ETE')) + age10 + C(sex_lc, Treatment(reference='female')) + tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + C(histology_fac, Treatment(reference='PTC')) + rai_received_flag + C(lvi_clean, Treatment(reference='missing')) + C(vasc_clean, Treatment(reference='missing'))",
   "label": "full cohort sensitivity \u2014 includes non-DTC histologies (RAI covariate)"
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B54" s="18" t="n">
-        <v>0.01820768988501063</v>
+        <v>0.01881692303623327</v>
       </c>
       <c r="C54" s="18" t="n">
-        <v>0.009912962075123204</v>
+        <v>0.01023808127512506</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>0.03344307871213138</v>
+        <v>0.03458427248588151</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>3.775467573871243e-38</v>
+        <v>1.772547926417216e-37</v>
       </c>
     </row>
     <row r="55">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B55" s="18" t="n">
-        <v>1.224487779211359</v>
+        <v>1.234036811889456</v>
       </c>
       <c r="C55" s="18" t="n">
-        <v>0.6249861848359756</v>
+        <v>0.6296290952169418</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2.39904554343304</v>
+        <v>2.418641172504247</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.5550575699205013</v>
+        <v>0.5402052351946247</v>
       </c>
     </row>
     <row r="56">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B56" s="18" t="n">
-        <v>1.590964961232916</v>
+        <v>1.605347833573521</v>
       </c>
       <c r="C56" s="18" t="n">
-        <v>1.134847190953743</v>
+        <v>1.144503489899247</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2.23040558063471</v>
+        <v>2.251755184238075</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0.007063602444180204</v>
+        <v>0.006110978617229343</v>
       </c>
     </row>
     <row r="57">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B57" s="18" t="n">
-        <v>1.285465042605963</v>
+        <v>1.30074903442832</v>
       </c>
       <c r="C57" s="18" t="n">
-        <v>0.9203333460739046</v>
+        <v>0.9308559060649149</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1.795458550764341</v>
+        <v>1.817626164847276</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.140751701646049</v>
+        <v>0.1234997267822623</v>
       </c>
     </row>
     <row r="58">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B58" s="18" t="n">
-        <v>1.246981532406513</v>
+        <v>1.230139271573314</v>
       </c>
       <c r="C58" s="18" t="n">
-        <v>0.8471999299335975</v>
+        <v>0.8353077310506075</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1.83541438947566</v>
+        <v>1.81159897270871</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0.2630612138995111</v>
+        <v>0.2942819158437429</v>
       </c>
     </row>
     <row r="59">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B59" s="18" t="n">
-        <v>5.235949933040403</v>
+        <v>5.185237994209519</v>
       </c>
       <c r="C59" s="18" t="n">
-        <v>2.713948858097169</v>
+        <v>2.689349157916357</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>10.1015800719721</v>
+        <v>9.997472056557029</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>7.902637423371317e-07</v>
+        <v>8.950254840615399e-07</v>
       </c>
     </row>
     <row r="60">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B60" s="18" t="n">
-        <v>0.4856241442953312</v>
+        <v>0.4818062924969674</v>
       </c>
       <c r="C60" s="18" t="n">
-        <v>0.1440922993926894</v>
+        <v>0.1429702388002312</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1.636664905179087</v>
+        <v>1.623675706480655</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>0.243929361824139</v>
+        <v>0.2387859210607071</v>
       </c>
     </row>
     <row r="61">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B61" s="18" t="n">
-        <v>2.087527512272552e-09</v>
+        <v>1.275475206682042e-09</v>
       </c>
       <c r="C61" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2439,7 +2439,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0.9988791109878108</v>
+        <v>0.9992146353933082</v>
       </c>
     </row>
     <row r="62">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B62" s="18" t="n">
-        <v>0.6797721604528594</v>
+        <v>0.6703448943879612</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>0.3781808465470493</v>
+        <v>0.3661342037083442</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1.221876238169718</v>
+        <v>1.22731575712047</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0.196988782715572</v>
+        <v>0.19491739581879</v>
       </c>
     </row>
     <row r="63">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B63" s="18" t="n">
-        <v>1.802192782210647</v>
+        <v>1.778439644995289</v>
       </c>
       <c r="C63" s="18" t="n">
-        <v>0.8581125686501837</v>
+        <v>0.8471264195793732</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>3.784933286038587</v>
+        <v>3.733619325037023</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.1197602232866131</v>
+        <v>0.1281294442203</v>
       </c>
     </row>
     <row r="64">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B64" s="18" t="n">
-        <v>3.319979904968426</v>
+        <v>3.333027731194698</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1.984907808615645</v>
+        <v>1.991611142896396</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>5.553037033534335</v>
+        <v>5.577933170607278</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4.826342779005567e-06</v>
+        <v>4.600306701175059e-06</v>
       </c>
     </row>
     <row r="65">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B65" s="18" t="n">
-        <v>0.6883312598936068</v>
+        <v>0.6877617653898112</v>
       </c>
       <c r="C65" s="18" t="n">
-        <v>0.4232788864596663</v>
+        <v>0.4227728699706244</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>1.119356382997544</v>
+        <v>1.118842479095161</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0.1322037264095022</v>
+        <v>0.1316410384497489</v>
       </c>
     </row>
     <row r="66">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B66" s="18" t="n">
-        <v>1.474355572683133</v>
+        <v>1.468070655857398</v>
       </c>
       <c r="C66" s="18" t="n">
-        <v>0.6089309908457249</v>
+        <v>0.6064738063648494</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>3.569738422547343</v>
+        <v>3.55370904393685</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0.3895236467276599</v>
+        <v>0.3946399821179301</v>
       </c>
     </row>
     <row r="67">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1.519426391063587e-09</v>
+        <v>1.500093204321947e-09</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -2553,7 +2553,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.9994983792860411</v>
+        <v>0.9994978399243757</v>
       </c>
     </row>
     <row r="68">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B68" s="18" t="n">
-        <v>0.7729909728052788</v>
+        <v>0.7778941343935867</v>
       </c>
       <c r="C68" s="18" t="n">
-        <v>0.3310228843539463</v>
+        <v>0.3328212674043152</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>1.805056605692428</v>
+        <v>1.8181508923492</v>
       </c>
       <c r="E68" s="18" t="n">
-        <v>0.5517965668261866</v>
+        <v>0.5620235742756428</v>
       </c>
     </row>
     <row r="69">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1.767254545007356</v>
+        <v>1.77562931311392</v>
       </c>
       <c r="C69" s="18" t="n">
-        <v>1.097064020587842</v>
+        <v>1.101148072875106</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>2.846860865217009</v>
+        <v>2.863247491645033</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>0.0192438176112148</v>
+        <v>0.01851225008280269</v>
       </c>
     </row>
     <row r="70">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1.895292977177866</v>
+        <v>1.91641428573758</v>
       </c>
       <c r="C70" s="18" t="n">
-        <v>1.066053509139101</v>
+        <v>1.075665388581756</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>3.369563946410716</v>
+        <v>3.414299422073429</v>
       </c>
       <c r="E70" s="18" t="n">
-        <v>0.0294181865662252</v>
+        <v>0.02727883903234741</v>
       </c>
     </row>
     <row r="71">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>1.889931828279741</v>
+        <v>1.90470910031505</v>
       </c>
       <c r="C71" s="18" t="n">
-        <v>0.9813552951043095</v>
+        <v>0.9868548096287644</v>
       </c>
       <c r="D71" s="18" t="n">
-        <v>3.639703513461096</v>
+        <v>3.676241653205013</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.05695218216704147</v>
+        <v>0.05479188168837221</v>
       </c>
     </row>
     <row r="72">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>1.175760709576873</v>
+        <v>1.178180598970277</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>0.3201459619406088</v>
+        <v>0.3209764511859936</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>4.318071787646562</v>
+        <v>4.324645994000363</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0.8072723661594022</v>
+        <v>0.8047955297569923</v>
       </c>
     </row>
     <row r="73">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>0.9373124632003611</v>
+        <v>0.9334958671328363</v>
       </c>
       <c r="C73" s="18" t="n">
-        <v>0.8513049699952649</v>
+        <v>0.8475742387320844</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1.032009308809292</v>
+        <v>1.028127677945551</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.1873899203736279</v>
+        <v>0.1624428836647294</v>
       </c>
     </row>
     <row r="74">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>1.061823647341721</v>
+        <v>1.059716424637732</v>
       </c>
       <c r="C74" s="18" t="n">
-        <v>0.9914338598591365</v>
+        <v>0.9891913739424952</v>
       </c>
       <c r="D74" s="18" t="n">
-        <v>1.137210966563384</v>
+        <v>1.135269605284955</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0.08650398849992604</v>
+        <v>0.09880338997329706</v>
       </c>
     </row>
     <row r="75">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B75" s="18" t="n">
-        <v>4.741474162290238</v>
+        <v>4.648297307741951</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3.458823434089347</v>
+        <v>3.388276890214176</v>
       </c>
       <c r="D75" s="18" t="n">
-        <v>6.499775909372186</v>
+        <v>6.376889658446803</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>4.009029942074579e-22</v>
+        <v>1.65661107990849e-21</v>
       </c>
     </row>
     <row r="76">
@@ -7385,13 +7385,13 @@
       <c r="A334" s="18" t="inlineStr">
         <is>
           <t>{
-  "n_obs": 192,
+  "n_obs": 190,
   "n_events": 19,
-  "llf": -44.26887111171082,
-  "aic": 110.53774222342165,
-  "pseudo_r2_mcfadden": 0.2857016703325118,
-  "lr_vs_null_chi2": 35.41290773069025,
-  "lr_vs_null_pvalue": 0.00010613916145962854,
+  "llf": -44.268871112647304,
+  "aic": 110.53774222529461,
+  "pseudo_r2_mcfadden": 0.2832781856985851,
+  "lr_vs_null_chi2": 34.993787663455734,
+  "lr_vs_null_pvalue": 0.0001251704165162737,
   "events": 19,
   "formula": "y_comp ~ tumor_size_cm + C(ajcc8_n_fac, Treatment(reference='N0')) + central_pos_flag + lateral_pos_flag + rai_received_flag + ge2 + days_per_100"
 }</t>
@@ -7405,16 +7405,16 @@
         </is>
       </c>
       <c r="B335" s="18" t="n">
-        <v>0.02411789512997224</v>
+        <v>0.02411789512997222</v>
       </c>
       <c r="C335" s="18" t="n">
-        <v>0.003095426568018558</v>
+        <v>0.003095426568054629</v>
       </c>
       <c r="D335" s="18" t="n">
-        <v>0.187913637335186</v>
+        <v>0.1879136373329959</v>
       </c>
       <c r="E335" s="18" t="n">
-        <v>0.0003766088038290857</v>
+        <v>0.0003766088038001654</v>
       </c>
     </row>
     <row r="336">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="B336" s="18" t="n">
-        <v>0.8040871828013445</v>
+        <v>0.8040871828013403</v>
       </c>
       <c r="C336" s="18" t="n">
-        <v>0.08807263284511103</v>
+        <v>0.08807263284518131</v>
       </c>
       <c r="D336" s="18" t="n">
-        <v>7.341170312036306</v>
+        <v>7.34117031203037</v>
       </c>
       <c r="E336" s="18" t="n">
-        <v>0.8467687891007277</v>
+        <v>0.8467687891006692</v>
       </c>
     </row>
     <row r="337">
@@ -7443,16 +7443,16 @@
         </is>
       </c>
       <c r="B337" s="18" t="n">
-        <v>1.215463783755382</v>
+        <v>1.215463783755397</v>
       </c>
       <c r="C337" s="18" t="n">
-        <v>0.05425189302773018</v>
+        <v>0.05425189302784397</v>
       </c>
       <c r="D337" s="18" t="n">
-        <v>27.23134857000878</v>
+        <v>27.23134856995235</v>
       </c>
       <c r="E337" s="18" t="n">
-        <v>0.9021064666247514</v>
+        <v>0.90210646662468</v>
       </c>
     </row>
     <row r="338">
@@ -7462,16 +7462,16 @@
         </is>
       </c>
       <c r="B338" s="18" t="n">
-        <v>1.094107558560965</v>
+        <v>1.094107558560973</v>
       </c>
       <c r="C338" s="18" t="n">
-        <v>0.1059296698753412</v>
+        <v>0.1059296698756102</v>
       </c>
       <c r="D338" s="18" t="n">
-        <v>11.30062381114711</v>
+        <v>11.3006238111186</v>
       </c>
       <c r="E338" s="18" t="n">
-        <v>0.9398200139471643</v>
+        <v>0.9398200139470939</v>
       </c>
     </row>
     <row r="339">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="B339" s="18" t="n">
-        <v>3.674513475945357e-09</v>
+        <v>7.731246178897265e-09</v>
       </c>
       <c r="C339" s="18" t="n">
         <v>1.388794386496402e-11</v>
@@ -7490,7 +7490,7 @@
         <v>72004899337.38588</v>
       </c>
       <c r="E339" s="18" t="n">
-        <v>0.9991500083918476</v>
+        <v>0.9988893345361833</v>
       </c>
     </row>
     <row r="340">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="B340" s="18" t="n">
-        <v>0.9516299292814673</v>
+        <v>0.9516299292814678</v>
       </c>
       <c r="C340" s="18" t="n">
-        <v>0.7675933343346527</v>
+        <v>0.7675933343348874</v>
       </c>
       <c r="D340" s="18" t="n">
-        <v>1.179790758721506</v>
+        <v>1.179790758721146</v>
       </c>
       <c r="E340" s="18" t="n">
-        <v>0.6511648987738741</v>
+        <v>0.6511648987734149</v>
       </c>
     </row>
     <row r="341">
@@ -7519,16 +7519,16 @@
         </is>
       </c>
       <c r="B341" s="18" t="n">
-        <v>1.376884772637383</v>
+        <v>1.376884772637402</v>
       </c>
       <c r="C341" s="18" t="n">
-        <v>0.357345754615485</v>
+        <v>0.3573457546158765</v>
       </c>
       <c r="D341" s="18" t="n">
-        <v>5.305258709903101</v>
+        <v>5.305258709897432</v>
       </c>
       <c r="E341" s="18" t="n">
-        <v>0.6421354769371461</v>
+        <v>0.642135476936865</v>
       </c>
     </row>
     <row r="342">
@@ -7538,16 +7538,16 @@
         </is>
       </c>
       <c r="B342" s="18" t="n">
-        <v>2.524185711263298</v>
+        <v>2.524185711263305</v>
       </c>
       <c r="C342" s="18" t="n">
-        <v>0.6101216624634135</v>
+        <v>0.6101216624634787</v>
       </c>
       <c r="D342" s="18" t="n">
-        <v>10.44302128073985</v>
+        <v>10.44302128073879</v>
       </c>
       <c r="E342" s="18" t="n">
-        <v>0.2012525917948234</v>
+        <v>0.2012525917947889</v>
       </c>
     </row>
     <row r="343">
@@ -7557,16 +7557,16 @@
         </is>
       </c>
       <c r="B343" s="18" t="n">
-        <v>8.843888533396331</v>
+        <v>8.843888533396296</v>
       </c>
       <c r="C343" s="18" t="n">
-        <v>2.771343352101149</v>
+        <v>2.771343352277366</v>
       </c>
       <c r="D343" s="18" t="n">
-        <v>28.22254569497472</v>
+        <v>28.22254569317995</v>
       </c>
       <c r="E343" s="18" t="n">
-        <v>0.0002317142156747089</v>
+        <v>0.0002317142154913127</v>
       </c>
     </row>
     <row r="344">
@@ -7576,16 +7576,16 @@
         </is>
       </c>
       <c r="B344" s="18" t="n">
-        <v>3.308184753372749</v>
+        <v>3.308184753372745</v>
       </c>
       <c r="C344" s="18" t="n">
-        <v>0.6587459583166945</v>
+        <v>0.6587459583168344</v>
       </c>
       <c r="D344" s="18" t="n">
-        <v>16.61351576321401</v>
+        <v>16.61351576321043</v>
       </c>
       <c r="E344" s="18" t="n">
-        <v>0.1462195968306</v>
+        <v>0.1462195968305471</v>
       </c>
     </row>
     <row r="345">
@@ -7598,13 +7598,13 @@
         <v>1.088031671121559</v>
       </c>
       <c r="C345" s="18" t="n">
-        <v>0.9466969428212387</v>
+        <v>0.9466969428213032</v>
       </c>
       <c r="D345" s="18" t="n">
-        <v>1.250466610608996</v>
+        <v>1.25046661060891</v>
       </c>
       <c r="E345" s="18" t="n">
-        <v>0.2346731667026427</v>
+        <v>0.2346731667024146</v>
       </c>
     </row>
     <row r="346"/>
@@ -7838,17 +7838,17 @@
   "events": 178,
   "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 0.9102808635560813,
-    "hr_ci_low": 0.47913333888681914,
-    "hr_ci_high": 1.7293959390960676,
-    "p": 0.7740508906797761,
+    "hr": 0.9103037356162789,
+    "hr_ci_low": 0.47923951497127887,
+    "hr_ci_high": 1.729099678115261,
+    "p": 0.7740423569506414,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 2.443225068198415,
-    "hr_ci_low": 0.6478494195146004,
-    "hr_ci_high": 9.214099070036475,
-    "p": 0.18716625998772768,
+    "hr": 2.443341372260798,
+    "hr_ci_low": 0.6480998157458978,
+    "hr_ci_high": 9.21141607567116,
+    "p": 0.18703020836101486,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -7862,16 +7862,16 @@
         </is>
       </c>
       <c r="B362" s="18" t="n">
-        <v>0.9102808635560812</v>
+        <v>0.9103037356162788</v>
       </c>
       <c r="C362" s="18" t="n">
-        <v>0.4791333388868191</v>
+        <v>0.4792395149712788</v>
       </c>
       <c r="D362" s="18" t="n">
-        <v>1.729395939096068</v>
+        <v>1.729099678115261</v>
       </c>
       <c r="E362" s="18" t="n">
-        <v>0.7740508906797761</v>
+        <v>0.7740423569506414</v>
       </c>
     </row>
     <row r="363">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="B363" s="18" t="n">
-        <v>2.443225068198415</v>
+        <v>2.443341372260798</v>
       </c>
       <c r="C363" s="18" t="n">
-        <v>0.6478494195146004</v>
+        <v>0.6480998157458978</v>
       </c>
       <c r="D363" s="18" t="n">
-        <v>9.214099070036475</v>
+        <v>9.21141607567116</v>
       </c>
       <c r="E363" s="18" t="n">
-        <v>0.1871662599877276</v>
+        <v>0.1870302083610148</v>
       </c>
     </row>
     <row r="364">
@@ -7900,16 +7900,16 @@
         </is>
       </c>
       <c r="B364" s="18" t="n">
-        <v>0.936808739475723</v>
+        <v>0.936808656010379</v>
       </c>
       <c r="C364" s="18" t="n">
-        <v>0.7873212832297154</v>
+        <v>0.7873572846824738</v>
       </c>
       <c r="D364" s="18" t="n">
-        <v>1.114679144399598</v>
+        <v>1.114627977729191</v>
       </c>
       <c r="E364" s="18" t="n">
-        <v>0.4617635228405863</v>
+        <v>0.4616448505866697</v>
       </c>
     </row>
     <row r="365">
@@ -7919,16 +7919,16 @@
         </is>
       </c>
       <c r="B365" s="18" t="n">
-        <v>1.292591248233988</v>
+        <v>1.292464933823215</v>
       </c>
       <c r="C365" s="18" t="n">
-        <v>0.7674327357304391</v>
+        <v>0.7674325569331557</v>
       </c>
       <c r="D365" s="18" t="n">
-        <v>2.177118667502301</v>
+        <v>2.176693691284387</v>
       </c>
       <c r="E365" s="18" t="n">
-        <v>0.3346248968410373</v>
+        <v>0.3347185829241387</v>
       </c>
     </row>
     <row r="366">
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="B366" s="18" t="n">
-        <v>0.9684720408602407</v>
+        <v>0.9684746094521792</v>
       </c>
       <c r="C366" s="18" t="n">
-        <v>0.8403166642816156</v>
+        <v>0.8403511120544364</v>
       </c>
       <c r="D366" s="18" t="n">
-        <v>1.116172192931388</v>
+        <v>1.116132359080871</v>
       </c>
       <c r="E366" s="18" t="n">
-        <v>0.658229676744901</v>
+        <v>0.6581697063897802</v>
       </c>
     </row>
     <row r="367">
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="B367" s="18" t="n">
-        <v>0.6913177685676808</v>
+        <v>0.6912735971194832</v>
       </c>
       <c r="C367" s="18" t="n">
-        <v>0.3652127171363888</v>
+        <v>0.3652516338182929</v>
       </c>
       <c r="D367" s="18" t="n">
-        <v>1.308607928236294</v>
+        <v>1.308301296503542</v>
       </c>
       <c r="E367" s="18" t="n">
-        <v>0.2568575144361521</v>
+        <v>0.2566481166469044</v>
       </c>
     </row>
     <row r="368">
@@ -7976,16 +7976,16 @@
         </is>
       </c>
       <c r="B368" s="18" t="n">
-        <v>1.669305268165391e-120</v>
+        <v>1.735444020336766e-120</v>
       </c>
       <c r="C368" s="18" t="n">
-        <v>1.265014436368057e-131</v>
+        <v>1.315134973274594e-131</v>
       </c>
       <c r="D368" s="18" t="n">
-        <v>2.202804962704766e-109</v>
+        <v>2.290081253199094e-109</v>
       </c>
       <c r="E368" s="18" t="n">
-        <v>6.351843715822425e-99</v>
+        <v>6.764359580967242e-99</v>
       </c>
     </row>
     <row r="369">
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="B369" s="18" t="n">
-        <v>0.0926611428602198</v>
+        <v>0.0926517228106373</v>
       </c>
       <c r="C369" s="18" t="n">
-        <v>0.0025158197320641</v>
+        <v>0.0025175244798904</v>
       </c>
       <c r="D369" s="18" t="n">
-        <v>3.412838879802226</v>
+        <v>3.409834465702075</v>
       </c>
       <c r="E369" s="18" t="n">
-        <v>0.1960721582196949</v>
+        <v>0.195956430476354</v>
       </c>
     </row>
     <row r="370">
@@ -8014,16 +8014,16 @@
         </is>
       </c>
       <c r="B370" s="18" t="n">
-        <v>0.8226508028771761</v>
+        <v>0.8224286004197328</v>
       </c>
       <c r="C370" s="18" t="n">
-        <v>0.3030914664962339</v>
+        <v>0.3030537526080663</v>
       </c>
       <c r="D370" s="18" t="n">
-        <v>2.232838658566692</v>
+        <v>2.231910335930145</v>
       </c>
       <c r="E370" s="18" t="n">
-        <v>0.7015663976844336</v>
+        <v>0.7011317863804092</v>
       </c>
     </row>
     <row r="371">
@@ -8033,16 +8033,16 @@
         </is>
       </c>
       <c r="B371" s="18" t="n">
-        <v>0.0009814849519229</v>
+        <v>0.0009815781044031999</v>
       </c>
       <c r="C371" s="18" t="n">
-        <v>1.593797932419506e-33</v>
+        <v>1.596000780572613e-33</v>
       </c>
       <c r="D371" s="18" t="n">
-        <v>6.044133269697347e+26</v>
+        <v>6.036936740709404e+26</v>
       </c>
       <c r="E371" s="18" t="n">
-        <v>0.8431110258271137</v>
+        <v>0.8431102437330177</v>
       </c>
     </row>
     <row r="372">
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B372" s="18" t="n">
-        <v>4.525643291271133</v>
+        <v>4.524320048617943</v>
       </c>
       <c r="C372" s="18" t="n">
-        <v>1.182715803554595</v>
+        <v>1.18278999739249</v>
       </c>
       <c r="D372" s="18" t="n">
-        <v>17.31730238005733</v>
+        <v>17.30609148492299</v>
       </c>
       <c r="E372" s="18" t="n">
-        <v>0.0274497615896922</v>
+        <v>0.0274387810476094</v>
       </c>
     </row>
     <row r="373">
@@ -8071,16 +8071,16 @@
         </is>
       </c>
       <c r="B373" s="18" t="n">
-        <v>82.59421045665907</v>
+        <v>82.52812661832206</v>
       </c>
       <c r="C373" s="18" t="n">
-        <v>36.94479353587479</v>
+        <v>36.92243205135421</v>
       </c>
       <c r="D373" s="18" t="n">
-        <v>184.6485782721904</v>
+        <v>184.4648714812922</v>
       </c>
       <c r="E373" s="18" t="n">
-        <v>5.719938258257363e-27</v>
+        <v>5.679377375479022e-27</v>
       </c>
     </row>
     <row r="374">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="B374" s="18" t="n">
-        <v>168.1113399897766</v>
+        <v>167.9575168918756</v>
       </c>
       <c r="C374" s="18" t="n">
-        <v>65.31641294157042</v>
+        <v>65.27575447295933</v>
       </c>
       <c r="D374" s="18" t="n">
-        <v>432.6848545470469</v>
+        <v>432.1624117293142</v>
       </c>
       <c r="E374" s="18" t="n">
-        <v>2.296010445246175e-26</v>
+        <v>2.26199839463582e-26</v>
       </c>
     </row>
     <row r="375">
@@ -8109,16 +8109,16 @@
         </is>
       </c>
       <c r="B375" s="18" t="n">
-        <v>6.799822934266519e-05</v>
+        <v>6.800892356123554e-05</v>
       </c>
       <c r="C375" s="18" t="n">
-        <v>2.377172731334699e-47</v>
+        <v>2.378212457213654e-47</v>
       </c>
       <c r="D375" s="18" t="n">
-        <v>1.945066562807834e+38</v>
+        <v>1.94482779279398e+38</v>
       </c>
       <c r="E375" s="18" t="n">
-        <v>0.8474374497066779</v>
+        <v>0.8474394875745951</v>
       </c>
     </row>
     <row r="376">
@@ -8128,16 +8128,16 @@
         </is>
       </c>
       <c r="B376" s="18" t="n">
-        <v>0.3712996489567189</v>
+        <v>0.3712374815082589</v>
       </c>
       <c r="C376" s="18" t="n">
-        <v>0.0250670217806946</v>
+        <v>0.0250800268175174</v>
       </c>
       <c r="D376" s="18" t="n">
-        <v>5.499792935974478</v>
+        <v>5.495100490894795</v>
       </c>
       <c r="E376" s="18" t="n">
-        <v>0.4712743001833367</v>
+        <v>0.4710864563016359</v>
       </c>
     </row>
     <row r="377">
@@ -8147,16 +8147,16 @@
         </is>
       </c>
       <c r="B377" s="18" t="n">
-        <v>0.2729965144346066</v>
+        <v>0.2729954301672874</v>
       </c>
       <c r="C377" s="18" t="n">
-        <v>0.0591620977775801</v>
+        <v>0.0591887523669318</v>
       </c>
       <c r="D377" s="18" t="n">
-        <v>1.259710180893667</v>
+        <v>1.259132891164969</v>
       </c>
       <c r="E377" s="18" t="n">
-        <v>0.096104351105412</v>
+        <v>0.0960045354923339</v>
       </c>
     </row>
     <row r="378">
@@ -8166,16 +8166,16 @@
         </is>
       </c>
       <c r="B378" s="18" t="n">
-        <v>1.838452428514997</v>
+        <v>1.838518534199694</v>
       </c>
       <c r="C378" s="18" t="n">
-        <v>0.6299890245754654</v>
+        <v>0.6301882818520425</v>
       </c>
       <c r="D378" s="18" t="n">
-        <v>5.365025738647318</v>
+        <v>5.363715095847168</v>
       </c>
       <c r="E378" s="18" t="n">
-        <v>0.2651185955914953</v>
+        <v>0.2649653065047122</v>
       </c>
     </row>
     <row r="379">
@@ -8185,16 +8185,16 @@
         </is>
       </c>
       <c r="B379" s="18" t="n">
-        <v>0.7805127177967276</v>
+        <v>0.7805629636388375</v>
       </c>
       <c r="C379" s="18" t="n">
-        <v>0.2417986199502257</v>
+        <v>0.2418644301979245</v>
       </c>
       <c r="D379" s="18" t="n">
-        <v>2.519452355715835</v>
+        <v>2.519091127645579</v>
       </c>
       <c r="E379" s="18" t="n">
-        <v>0.6785346416122111</v>
+        <v>0.6785596777827072</v>
       </c>
     </row>
     <row r="380">
@@ -8204,16 +8204,16 @@
         </is>
       </c>
       <c r="B380" s="18" t="n">
-        <v>2.227850675343217</v>
+        <v>2.227525371486014</v>
       </c>
       <c r="C380" s="18" t="n">
-        <v>0.1778621678789783</v>
+        <v>0.1779417025391863</v>
       </c>
       <c r="D380" s="18" t="n">
-        <v>27.90542075819289</v>
+        <v>27.88480277421873</v>
       </c>
       <c r="E380" s="18" t="n">
-        <v>0.5345343965720899</v>
+        <v>0.534513006589991</v>
       </c>
     </row>
     <row r="381">
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="B381" s="18" t="n">
-        <v>1.479844528005039</v>
+        <v>1.479952097268279</v>
       </c>
       <c r="C381" s="18" t="n">
-        <v>0.5348540887333044</v>
+        <v>0.5350423956356825</v>
       </c>
       <c r="D381" s="18" t="n">
-        <v>4.094462159301975</v>
+        <v>4.093616184576434</v>
       </c>
       <c r="E381" s="18" t="n">
-        <v>0.4503549791478004</v>
+        <v>0.4501466216197959</v>
       </c>
     </row>
     <row r="382">
@@ -8250,17 +8250,17 @@
   "events": 178,
   "coef_table_path": "/Users/ros/THyroid 2026/data/m044/m044_cox_primary_with_rai_summary.csv",
   "gross_vs_microscopic_hr": {
-    "hr": 0.6195366880806339,
-    "hr_ci_low": 0.2885784687778236,
-    "hr_ci_high": 1.3300566376399614,
-    "p": 0.2193486452707155,
+    "hr": 0.6195679029743909,
+    "hr_ci_low": 0.2887910192490381,
+    "hr_ci_high": 1.3292116472121316,
+    "p": 0.218983236437501,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.Gross ETE]"
   },
   "noneg_vs_microscopic_hr": {
-    "hr": 5.165307958844581,
-    "hr_ci_low": 0.6348162961236556,
-    "hr_ci_high": 42.028546640375005,
-    "p": 0.12475550364321643,
+    "hr": 5.167153773864532,
+    "hr_ci_low": 0.6368362954626577,
+    "hr_ci_high": 41.92518283425644,
+    "p": 0.12416666927802668,
     "covariate_row": "C(ete_group, Treatment(reference='Microscopic ETE'))[T.No/negative ETE]"
   }
 }</t>
@@ -8274,16 +8274,16 @@
         </is>
       </c>
       <c r="B384" s="18" t="n">
-        <v>0.6195366880806339</v>
+        <v>0.6195679029743909</v>
       </c>
       <c r="C384" s="18" t="n">
-        <v>0.2885784687778236</v>
+        <v>0.2887910192490381</v>
       </c>
       <c r="D384" s="18" t="n">
-        <v>1.330056637639961</v>
+        <v>1.329211647212132</v>
       </c>
       <c r="E384" s="18" t="n">
-        <v>0.2193486452707155</v>
+        <v>0.218983236437501</v>
       </c>
     </row>
     <row r="385">
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="B385" s="18" t="n">
-        <v>5.165307958844581</v>
+        <v>5.167153773864532</v>
       </c>
       <c r="C385" s="18" t="n">
-        <v>0.6348162961236556</v>
+        <v>0.6368362954626577</v>
       </c>
       <c r="D385" s="18" t="n">
-        <v>42.028546640375</v>
+        <v>41.92518283425644</v>
       </c>
       <c r="E385" s="18" t="n">
-        <v>0.1247555036432164</v>
+        <v>0.1241666692780266</v>
       </c>
     </row>
     <row r="386">
@@ -8312,16 +8312,16 @@
         </is>
       </c>
       <c r="B386" s="18" t="n">
-        <v>0.7862597071903951</v>
+        <v>0.7863070086627305</v>
       </c>
       <c r="C386" s="18" t="n">
-        <v>0.6238653960942784</v>
+        <v>0.6240342904607402</v>
       </c>
       <c r="D386" s="18" t="n">
-        <v>0.9909258167248997</v>
+        <v>0.9907768232025208</v>
       </c>
       <c r="E386" s="18" t="n">
-        <v>0.0416310821738029</v>
+        <v>0.0414964955672526</v>
       </c>
     </row>
     <row r="387">
@@ -8331,16 +8331,16 @@
         </is>
       </c>
       <c r="B387" s="18" t="n">
-        <v>1.797323120587958</v>
+        <v>1.797606236232786</v>
       </c>
       <c r="C387" s="18" t="n">
-        <v>0.8653448635461843</v>
+        <v>0.8660663278899774</v>
       </c>
       <c r="D387" s="18" t="n">
-        <v>3.733043941073358</v>
+        <v>3.73110935788917</v>
       </c>
       <c r="E387" s="18" t="n">
-        <v>0.1159160466304021</v>
+        <v>0.1154812929439595</v>
       </c>
     </row>
     <row r="388">
@@ -8350,16 +8350,16 @@
         </is>
       </c>
       <c r="B388" s="18" t="n">
-        <v>1.068630419767369</v>
+        <v>1.068541698187198</v>
       </c>
       <c r="C388" s="18" t="n">
-        <v>0.9630936387125496</v>
+        <v>0.9630806915513695</v>
       </c>
       <c r="D388" s="18" t="n">
-        <v>1.185732028693238</v>
+        <v>1.185551087028392</v>
       </c>
       <c r="E388" s="18" t="n">
-        <v>0.210877979077011</v>
+        <v>0.2111437289383263</v>
       </c>
     </row>
     <row r="389">
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="B389" s="18" t="n">
-        <v>118.1323653991867</v>
+        <v>117.6132179872576</v>
       </c>
       <c r="C389" s="18" t="n">
-        <v>12.10257479144966</v>
+        <v>12.10022176593432</v>
       </c>
       <c r="D389" s="18" t="n">
-        <v>1153.081554568554</v>
+        <v>1143.191365654286</v>
       </c>
       <c r="E389" s="18" t="n">
-        <v>4.044786956070582e-05</v>
+        <v>3.978763320899973e-05</v>
       </c>
     </row>
     <row r="390">
@@ -8388,16 +8388,16 @@
         </is>
       </c>
       <c r="B390" s="18" t="n">
-        <v>2.159390070958419e-100</v>
+        <v>2.121731602928528e-100</v>
       </c>
       <c r="C390" s="18" t="n">
-        <v>1.636405075577344e-111</v>
+        <v>1.607867152276966e-111</v>
       </c>
       <c r="D390" s="18" t="n">
-        <v>2.849517853584423e-89</v>
+        <v>2.799823970836494e-89</v>
       </c>
       <c r="E390" s="18" t="n">
-        <v>4.49095631820043e-69</v>
+        <v>4.385630028864638e-69</v>
       </c>
     </row>
     <row r="391">
@@ -8407,16 +8407,16 @@
         </is>
       </c>
       <c r="B391" s="18" t="n">
-        <v>0.5174942401844203</v>
+        <v>0.51667350299869</v>
       </c>
       <c r="C391" s="18" t="n">
-        <v>1.00833663938705e-06</v>
+        <v>1.022602544094179e-06</v>
       </c>
       <c r="D391" s="18" t="n">
-        <v>265586.1923125609</v>
+        <v>261051.0899299618</v>
       </c>
       <c r="E391" s="18" t="n">
-        <v>0.9217757881419042</v>
+        <v>0.9214948614902508</v>
       </c>
     </row>
     <row r="392">
@@ -8426,16 +8426,16 @@
         </is>
       </c>
       <c r="B392" s="18" t="n">
-        <v>5.28000955338478</v>
+        <v>5.275814328773673</v>
       </c>
       <c r="C392" s="18" t="n">
-        <v>1.734006595622719</v>
+        <v>1.734829405598675</v>
       </c>
       <c r="D392" s="18" t="n">
-        <v>16.07750567628192</v>
+        <v>16.04435383782778</v>
       </c>
       <c r="E392" s="18" t="n">
-        <v>0.0034023415240864</v>
+        <v>0.0033811494546532</v>
       </c>
     </row>
     <row r="393">
@@ -8445,16 +8445,16 @@
         </is>
       </c>
       <c r="B393" s="18" t="n">
-        <v>0.0007538458202525999</v>
+        <v>0.0007539449476274</v>
       </c>
       <c r="C393" s="18" t="n">
-        <v>7.87370023106309e-34</v>
+        <v>7.885724289615266e-34</v>
       </c>
       <c r="D393" s="18" t="n">
-        <v>7.217489922596581e+26</v>
+        <v>7.208380145898187e+26</v>
       </c>
       <c r="E393" s="18" t="n">
-        <v>0.8382422392940119</v>
+        <v>0.838241934116758</v>
       </c>
     </row>
     <row r="394">
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="B394" s="18" t="n">
-        <v>0.2141299452268806</v>
+        <v>0.2147113890850175</v>
       </c>
       <c r="C394" s="18" t="n">
-        <v>0.008271310808961501</v>
+        <v>0.0083525840177399</v>
       </c>
       <c r="D394" s="18" t="n">
-        <v>5.543454296650193</v>
+        <v>5.519367480159952</v>
       </c>
       <c r="E394" s="18" t="n">
-        <v>0.3532282666818117</v>
+        <v>0.3530294384880128</v>
       </c>
     </row>
     <row r="395">
@@ -8483,16 +8483,16 @@
         </is>
       </c>
       <c r="B395" s="18" t="n">
-        <v>1879.319965286519</v>
+        <v>1872.628714966891</v>
       </c>
       <c r="C395" s="18" t="n">
-        <v>708.118289554257</v>
+        <v>706.3861810513191</v>
       </c>
       <c r="D395" s="18" t="n">
-        <v>4987.646250667713</v>
+        <v>4964.335937177381</v>
       </c>
       <c r="E395" s="18" t="n">
-        <v>9.092997502793388e-52</v>
+        <v>7.788175008546828e-52</v>
       </c>
     </row>
     <row r="396">
@@ -8502,16 +8502,16 @@
         </is>
       </c>
       <c r="B396" s="18" t="n">
-        <v>1.503034356645002</v>
+        <v>1.503991751504678</v>
       </c>
       <c r="C396" s="18" t="n">
-        <v>0.9162695004306858</v>
+        <v>0.9170436666850992</v>
       </c>
       <c r="D396" s="18" t="n">
-        <v>2.465554376952824</v>
+        <v>2.46661230077591</v>
       </c>
       <c r="E396" s="18" t="n">
-        <v>0.1065977172144751</v>
+        <v>0.1059049444034784</v>
       </c>
     </row>
     <row r="397">
@@ -8521,16 +8521,16 @@
         </is>
       </c>
       <c r="B397" s="18" t="n">
-        <v>0.09762202898769851</v>
+        <v>0.0996147536797593</v>
       </c>
       <c r="C397" s="18" t="n">
-        <v>0.0156870030163558</v>
+        <v>0.0162759499609488</v>
       </c>
       <c r="D397" s="18" t="n">
-        <v>0.6075131453559768</v>
+        <v>0.6096786469906684</v>
       </c>
       <c r="E397" s="18" t="n">
-        <v>0.0126225496879036</v>
+        <v>0.0125848832600914</v>
       </c>
     </row>
     <row r="398">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="B398" s="18" t="n">
-        <v>3.183808411155286e-05</v>
+        <v>3.184477097328247e-05</v>
       </c>
       <c r="C398" s="18" t="n">
-        <v>8.276780346535801e-48</v>
+        <v>8.278552790267166e-48</v>
       </c>
       <c r="D398" s="18" t="n">
-        <v>1.224707624769307e+38</v>
+        <v>1.224959801588808e+38</v>
       </c>
       <c r="E398" s="18" t="n">
-        <v>0.836029126257533</v>
+        <v>0.8360323977225377</v>
       </c>
     </row>
     <row r="399">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="B399" s="18" t="n">
-        <v>4.352903403823486</v>
+        <v>4.349421678705429</v>
       </c>
       <c r="C399" s="18" t="n">
-        <v>2.086236680262511</v>
+        <v>2.085509217147165</v>
       </c>
       <c r="D399" s="18" t="n">
-        <v>9.082271547748787</v>
+        <v>9.070911211349411</v>
       </c>
       <c r="E399" s="18" t="n">
-        <v>8.869250150454874e-05</v>
+        <v>8.859188475476247e-05</v>
       </c>
     </row>
     <row r="400">
@@ -8578,16 +8578,16 @@
         </is>
       </c>
       <c r="B400" s="18" t="n">
-        <v>1.256411627150506</v>
+        <v>1.255370520701112</v>
       </c>
       <c r="C400" s="18" t="n">
-        <v>0.6555007012144456</v>
+        <v>0.6551809314904289</v>
       </c>
       <c r="D400" s="18" t="n">
-        <v>2.408189913320256</v>
+        <v>2.405373948628728</v>
       </c>
       <c r="E400" s="18" t="n">
-        <v>0.4916877121378405</v>
+        <v>0.4930353877669128</v>
       </c>
     </row>
     <row r="401">
@@ -8597,16 +8597,16 @@
         </is>
       </c>
       <c r="B401" s="18" t="n">
-        <v>2.286425471636428</v>
+        <v>2.286744666806819</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>0.8913158978824999</v>
+        <v>0.8921604001332837</v>
       </c>
       <c r="D401" s="18" t="n">
-        <v>5.865194876213264</v>
+        <v>5.861279171759041</v>
       </c>
       <c r="E401" s="18" t="n">
-        <v>0.08532621888335901</v>
+        <v>0.0850058938994806</v>
       </c>
     </row>
     <row r="402">
@@ -8616,16 +8616,16 @@
         </is>
       </c>
       <c r="B402" s="18" t="n">
-        <v>0.1766024486089431</v>
+        <v>0.1767500360564004</v>
       </c>
       <c r="C402" s="18" t="n">
-        <v>0.0327714753260228</v>
+        <v>0.0328444541491056</v>
       </c>
       <c r="D402" s="18" t="n">
-        <v>0.951694256801084</v>
+        <v>0.9511674361861652</v>
       </c>
       <c r="E402" s="18" t="n">
-        <v>0.0436352966560586</v>
+        <v>0.0435631735366287</v>
       </c>
     </row>
     <row r="403">
@@ -8635,16 +8635,16 @@
         </is>
       </c>
       <c r="B403" s="18" t="n">
-        <v>0.0629578538984947</v>
+        <v>0.0630401414450845</v>
       </c>
       <c r="C403" s="18" t="n">
-        <v>1.631278642615491e-09</v>
+        <v>1.682742170756617e-09</v>
       </c>
       <c r="D403" s="18" t="n">
-        <v>2429806.449956992</v>
+        <v>2361656.766246844</v>
       </c>
       <c r="E403" s="18" t="n">
-        <v>0.7563607739507602</v>
+        <v>0.7560698860865616</v>
       </c>
     </row>
     <row r="404">
@@ -8654,16 +8654,16 @@
         </is>
       </c>
       <c r="B404" s="18" t="n">
-        <v>0.521537506501187</v>
+        <v>0.5213933439270377</v>
       </c>
       <c r="C404" s="18" t="n">
-        <v>0.1897718262966125</v>
+        <v>0.1898912323532288</v>
       </c>
       <c r="D404" s="18" t="n">
-        <v>1.433307440812309</v>
+        <v>1.431614381151262</v>
       </c>
       <c r="E404" s="18" t="n">
-        <v>0.2069289207676676</v>
+        <v>0.2063294534311404</v>
       </c>
     </row>
   </sheetData>
@@ -8679,7 +8679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="70" customWidth="1" style="18" min="1" max="1"/>
@@ -9107,322 +9107,304 @@
       </c>
     </row>
     <row r="25"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S4 pooled-LVI artifact check</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>OR pooled=1.720509958843602 p=0.001948210925390039</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 5.35% expected 4.1% (n=318)</t>
+          <t>S4 pooled-LVI artifact check</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OR pooled=1.720509958843602 p=0.001948210925390039</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>protective_sig=False; pooled_OR&gt;1_sig=True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 11.34% expected 7.0% (n=344)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '1.1-2'): got 5.35% expected 4.1% (n=318)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 3.73% expected 2.6% (n=268)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '2.1-4'): got 11.44% expected 7.0% (n=341)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 11.61% expected 8.6% (n=336)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&lt;=1'): got 3.75% expected 2.6% (n=267)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.51% expected 2.7% (n=712)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Gross ETE', '&gt;4'): got 11.61% expected 8.6% (n=336)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.27% expected 2.3% (n=642)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '1.1-2'): got 3.56% expected 2.7% (n=702)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 1.69% expected 1.1% (n=947)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '2.1-4'): got 3.2% expected 2.3% (n=625)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 6.69% expected 5.6% (n=269)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&lt;=1'): got 1.73% expected 1.1% (n=924)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 18.18% expected 11.4% (n=44)</t>
+          <t>SIZE_STRAT_MISMATCH: ('Microscopic ETE', '&gt;4'): got 6.92% expected 5.6% (n=260)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 9.3% expected 7.0% (n=43)</t>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '1.1-2'): got 18.18% expected 11.4% (n=44)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 7.55% expected 3.8% (n=53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '2.1-4'): got 9.3% expected 7.0% (n=43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SIZE_STRAT_MISMATCH: ('No/negative ETE', '&gt;4'): got 7.84% expected 3.8% (n=51)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>Strict-DTC Cox/KM inclusion flow</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>/Users/ros/THyroid 2026/data/m044/m044_inclusion_flow_qc.csv</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>excluded_at_step</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>cum_excluded_from_cohort</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>path_proven_events_final_only</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>4128</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
+          <t>M044 analytic extract (cohort_m044_ajcc_ete_v1 + recurrence join)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3789</v>
+        <v>4012</v>
       </c>
       <c r="D44" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
+          <t>Strict-DTC histology (exclude MTC/anaplastic/NIFTP/FTUMP/benign-neoplasm list)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3756</v>
+        <v>3789</v>
       </c>
       <c r="D45" t="n">
-        <v>33</v>
+        <v>223</v>
       </c>
       <c r="E45" t="n">
-        <v>372</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
+          <t>Three-level ETE (No/negative vs Microscopic vs Gross)</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>3756</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E46" t="n">
-        <v>372</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
+          <t>Sex known female/male (same frame as primary logistic/Cox categoricals)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2525</v>
+        <v>3756</v>
       </c>
       <c r="D47" t="n">
-        <v>1231</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1603</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
+          <t>Positive analytic follow-up (followup_years &gt; 0)</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2525</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1231</v>
       </c>
       <c r="E48" t="n">
-        <v>1603</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
+          <t>Known surgery date (CPM surg_first_date; mig_258/mig_254 lineage)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2515</v>
+        <v>2525</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1613</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tumor size known (cm; Cox covariate complete-case)</t>
+          <t>Finite positive Cox time_days (path-proven TTE if event else censor at FU×365.25)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>1617</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Age at surgery known (Cox covariate complete-case)</t>
+          <t>Tumor size known (cm; Cox covariate complete-case)</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2511</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>1617</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
+          <t>Age at surgery known (Cox covariate complete-case)</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -9432,9 +9414,28 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1617</v>
-      </c>
-      <c r="F52" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Final Cox PH + Kaplan–Meier rows (lifelines sample; aligns Figure 6)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2511</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1501</v>
+      </c>
+      <c r="F53" t="n">
         <v>178</v>
       </c>
     </row>
@@ -12138,37 +12139,37 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>2576</v>
+        <v>2517</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="I5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="28" t="n">
-        <v>8137.3</v>
+        <v>8050.9</v>
       </c>
       <c r="K5" s="28" t="n">
         <v>0.96</v>
@@ -12192,37 +12193,37 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C6" s="28" t="n">
         <v>105</v>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>8.29%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H6" s="28" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.87%</t>
         </is>
       </c>
       <c r="I6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>4138.3</v>
+        <v>4135.6</v>
       </c>
       <c r="K6" s="28" t="n">
         <v>2.49</v>
@@ -12246,14 +12247,14 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C7" s="28" t="n">
         <v>18</v>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>9.38%</t>
+          <t>9.47%</t>
         </is>
       </c>
       <c r="E7" s="28" t="n">
@@ -12261,7 +12262,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="G7" s="28" t="n">
@@ -12269,7 +12270,7 @@
       </c>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="I7" s="28" t="n">
@@ -12354,7 +12355,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C9" s="28" t="n">
         <v>0</v>
@@ -12365,26 +12366,26 @@
         </is>
       </c>
       <c r="E9" s="28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="28" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="I9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="28" t="n">
-        <v>99.3</v>
+        <v>35.5</v>
       </c>
       <c r="K9" s="28" t="n">
         <v>0</v>
@@ -12934,16 +12935,16 @@
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>1.590964961232916</v>
+        <v>1.605347833573521</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1.134847190953743</v>
+        <v>1.144503489899247</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>2.23040558063471</v>
+        <v>2.251755184238075</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0.007063602444180204</v>
+        <v>0.006110978617229343</v>
       </c>
     </row>
     <row r="28">
@@ -12953,16 +12954,16 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>1.224487779211359</v>
+        <v>1.234036811889456</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.6249861848359756</v>
+        <v>0.6296290952169418</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>2.39904554343304</v>
+        <v>2.418641172504247</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0.5550575699205013</v>
+        <v>0.5402052351946247</v>
       </c>
     </row>
     <row r="29">
